--- a/Output/holdings_snapshot.xlsx
+++ b/Output/holdings_snapshot.xlsx
@@ -682,7 +682,7 @@
     <row r="2" ht="22" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Long signal: Shareholder Yield + Gross Profitability + ROIC  |  Short signal: Net Ext. Financing + Leverage + F-Score + Gross Profitability  |  130% long top-100 / w_short = 130% × β_long/β_short (Vasicek-adj, 12m trailing)  |  Monthly rebalancing, ±5 pp sector neutrality, beta-neutral</t>
+          <t>Long signal: Shareholder Yield + Gross Profitability + ROIC  |  Short signal: Net Ext. Financing + Leverage + F-Score + Gross Profitability  |  175% long top-100 / w_short = 175% × β_long/β_short (Vasicek-adj, 12m trailing)  |  Monthly rebalancing, ±5% sector neutrality, beta-neutral</t>
         </is>
       </c>
     </row>
@@ -822,7 +822,7 @@
       </c>
       <c r="C6" s="16" t="inlineStr">
         <is>
-          <t>1.30%</t>
+          <t>1.75%</t>
         </is>
       </c>
       <c r="D6" s="16" t="inlineStr">
@@ -900,7 +900,7 @@
       </c>
       <c r="C7" s="20" t="inlineStr">
         <is>
-          <t>1.30%</t>
+          <t>1.75%</t>
         </is>
       </c>
       <c r="D7" s="20" t="inlineStr">
@@ -978,7 +978,7 @@
       </c>
       <c r="C8" s="16" t="inlineStr">
         <is>
-          <t>1.30%</t>
+          <t>1.75%</t>
         </is>
       </c>
       <c r="D8" s="16" t="inlineStr">
@@ -1056,7 +1056,7 @@
       </c>
       <c r="C9" s="20" t="inlineStr">
         <is>
-          <t>1.30%</t>
+          <t>1.75%</t>
         </is>
       </c>
       <c r="D9" s="20" t="inlineStr">
@@ -1134,7 +1134,7 @@
       </c>
       <c r="C10" s="16" t="inlineStr">
         <is>
-          <t>1.30%</t>
+          <t>1.75%</t>
         </is>
       </c>
       <c r="D10" s="16" t="inlineStr">
@@ -1212,7 +1212,7 @@
       </c>
       <c r="C11" s="20" t="inlineStr">
         <is>
-          <t>1.30%</t>
+          <t>1.75%</t>
         </is>
       </c>
       <c r="D11" s="20" t="inlineStr">
@@ -1290,7 +1290,7 @@
       </c>
       <c r="C12" s="16" t="inlineStr">
         <is>
-          <t>1.30%</t>
+          <t>1.75%</t>
         </is>
       </c>
       <c r="D12" s="16" t="inlineStr">
@@ -1368,7 +1368,7 @@
       </c>
       <c r="C13" s="20" t="inlineStr">
         <is>
-          <t>1.30%</t>
+          <t>1.75%</t>
         </is>
       </c>
       <c r="D13" s="20" t="inlineStr">
@@ -1446,7 +1446,7 @@
       </c>
       <c r="C14" s="16" t="inlineStr">
         <is>
-          <t>1.30%</t>
+          <t>1.75%</t>
         </is>
       </c>
       <c r="D14" s="16" t="inlineStr">
@@ -1524,7 +1524,7 @@
       </c>
       <c r="C15" s="20" t="inlineStr">
         <is>
-          <t>1.30%</t>
+          <t>1.75%</t>
         </is>
       </c>
       <c r="D15" s="20" t="inlineStr">
@@ -1602,7 +1602,7 @@
       </c>
       <c r="C16" s="16" t="inlineStr">
         <is>
-          <t>1.30%</t>
+          <t>1.75%</t>
         </is>
       </c>
       <c r="D16" s="16" t="inlineStr">
@@ -1680,7 +1680,7 @@
       </c>
       <c r="C17" s="20" t="inlineStr">
         <is>
-          <t>1.30%</t>
+          <t>1.75%</t>
         </is>
       </c>
       <c r="D17" s="20" t="inlineStr">
@@ -1758,7 +1758,7 @@
       </c>
       <c r="C18" s="16" t="inlineStr">
         <is>
-          <t>1.30%</t>
+          <t>1.75%</t>
         </is>
       </c>
       <c r="D18" s="16" t="inlineStr">
@@ -1836,7 +1836,7 @@
       </c>
       <c r="C19" s="20" t="inlineStr">
         <is>
-          <t>1.30%</t>
+          <t>1.75%</t>
         </is>
       </c>
       <c r="D19" s="20" t="inlineStr">
@@ -1914,7 +1914,7 @@
       </c>
       <c r="C20" s="16" t="inlineStr">
         <is>
-          <t>1.30%</t>
+          <t>1.75%</t>
         </is>
       </c>
       <c r="D20" s="16" t="inlineStr">
@@ -1992,7 +1992,7 @@
       </c>
       <c r="C21" s="20" t="inlineStr">
         <is>
-          <t>1.30%</t>
+          <t>1.75%</t>
         </is>
       </c>
       <c r="D21" s="20" t="inlineStr">
@@ -2070,7 +2070,7 @@
       </c>
       <c r="C22" s="16" t="inlineStr">
         <is>
-          <t>1.30%</t>
+          <t>1.75%</t>
         </is>
       </c>
       <c r="D22" s="16" t="inlineStr">
@@ -2148,7 +2148,7 @@
       </c>
       <c r="C23" s="20" t="inlineStr">
         <is>
-          <t>1.30%</t>
+          <t>1.75%</t>
         </is>
       </c>
       <c r="D23" s="20" t="inlineStr">
@@ -2226,7 +2226,7 @@
       </c>
       <c r="C24" s="16" t="inlineStr">
         <is>
-          <t>1.30%</t>
+          <t>1.75%</t>
         </is>
       </c>
       <c r="D24" s="16" t="inlineStr">
@@ -2304,7 +2304,7 @@
       </c>
       <c r="C25" s="20" t="inlineStr">
         <is>
-          <t>1.30%</t>
+          <t>1.75%</t>
         </is>
       </c>
       <c r="D25" s="20" t="inlineStr">
@@ -2382,7 +2382,7 @@
       </c>
       <c r="C26" s="16" t="inlineStr">
         <is>
-          <t>1.30%</t>
+          <t>1.75%</t>
         </is>
       </c>
       <c r="D26" s="16" t="inlineStr">
@@ -2460,7 +2460,7 @@
       </c>
       <c r="C27" s="20" t="inlineStr">
         <is>
-          <t>1.30%</t>
+          <t>1.75%</t>
         </is>
       </c>
       <c r="D27" s="20" t="inlineStr">
@@ -2538,7 +2538,7 @@
       </c>
       <c r="C28" s="16" t="inlineStr">
         <is>
-          <t>1.30%</t>
+          <t>1.75%</t>
         </is>
       </c>
       <c r="D28" s="16" t="inlineStr">
@@ -2616,7 +2616,7 @@
       </c>
       <c r="C29" s="20" t="inlineStr">
         <is>
-          <t>1.30%</t>
+          <t>1.75%</t>
         </is>
       </c>
       <c r="D29" s="20" t="inlineStr">
@@ -2694,7 +2694,7 @@
       </c>
       <c r="C30" s="16" t="inlineStr">
         <is>
-          <t>1.30%</t>
+          <t>1.75%</t>
         </is>
       </c>
       <c r="D30" s="16" t="inlineStr">
@@ -2772,7 +2772,7 @@
       </c>
       <c r="C31" s="20" t="inlineStr">
         <is>
-          <t>1.30%</t>
+          <t>1.75%</t>
         </is>
       </c>
       <c r="D31" s="20" t="inlineStr">
@@ -2850,7 +2850,7 @@
       </c>
       <c r="C32" s="16" t="inlineStr">
         <is>
-          <t>1.30%</t>
+          <t>1.75%</t>
         </is>
       </c>
       <c r="D32" s="16" t="inlineStr">
@@ -2928,7 +2928,7 @@
       </c>
       <c r="C33" s="20" t="inlineStr">
         <is>
-          <t>1.30%</t>
+          <t>1.75%</t>
         </is>
       </c>
       <c r="D33" s="20" t="inlineStr">
@@ -3006,7 +3006,7 @@
       </c>
       <c r="C34" s="16" t="inlineStr">
         <is>
-          <t>1.30%</t>
+          <t>1.75%</t>
         </is>
       </c>
       <c r="D34" s="16" t="inlineStr">
@@ -3084,7 +3084,7 @@
       </c>
       <c r="C35" s="20" t="inlineStr">
         <is>
-          <t>1.30%</t>
+          <t>1.75%</t>
         </is>
       </c>
       <c r="D35" s="20" t="inlineStr">
@@ -3162,7 +3162,7 @@
       </c>
       <c r="C36" s="16" t="inlineStr">
         <is>
-          <t>1.30%</t>
+          <t>1.75%</t>
         </is>
       </c>
       <c r="D36" s="16" t="inlineStr">
@@ -3240,7 +3240,7 @@
       </c>
       <c r="C37" s="20" t="inlineStr">
         <is>
-          <t>1.30%</t>
+          <t>1.75%</t>
         </is>
       </c>
       <c r="D37" s="20" t="inlineStr">
@@ -3318,7 +3318,7 @@
       </c>
       <c r="C38" s="16" t="inlineStr">
         <is>
-          <t>1.30%</t>
+          <t>1.75%</t>
         </is>
       </c>
       <c r="D38" s="16" t="inlineStr">
@@ -3396,7 +3396,7 @@
       </c>
       <c r="C39" s="20" t="inlineStr">
         <is>
-          <t>1.30%</t>
+          <t>1.75%</t>
         </is>
       </c>
       <c r="D39" s="20" t="inlineStr">
@@ -3474,7 +3474,7 @@
       </c>
       <c r="C40" s="16" t="inlineStr">
         <is>
-          <t>1.30%</t>
+          <t>1.75%</t>
         </is>
       </c>
       <c r="D40" s="16" t="inlineStr">
@@ -3552,7 +3552,7 @@
       </c>
       <c r="C41" s="20" t="inlineStr">
         <is>
-          <t>1.30%</t>
+          <t>1.75%</t>
         </is>
       </c>
       <c r="D41" s="20" t="inlineStr">
@@ -3630,7 +3630,7 @@
       </c>
       <c r="C42" s="16" t="inlineStr">
         <is>
-          <t>1.30%</t>
+          <t>1.75%</t>
         </is>
       </c>
       <c r="D42" s="16" t="inlineStr">
@@ -3708,7 +3708,7 @@
       </c>
       <c r="C43" s="20" t="inlineStr">
         <is>
-          <t>1.30%</t>
+          <t>1.75%</t>
         </is>
       </c>
       <c r="D43" s="20" t="inlineStr">
@@ -3786,7 +3786,7 @@
       </c>
       <c r="C44" s="16" t="inlineStr">
         <is>
-          <t>1.30%</t>
+          <t>1.75%</t>
         </is>
       </c>
       <c r="D44" s="16" t="inlineStr">
@@ -3864,7 +3864,7 @@
       </c>
       <c r="C45" s="20" t="inlineStr">
         <is>
-          <t>1.30%</t>
+          <t>1.75%</t>
         </is>
       </c>
       <c r="D45" s="20" t="inlineStr">
@@ -3942,7 +3942,7 @@
       </c>
       <c r="C46" s="16" t="inlineStr">
         <is>
-          <t>1.30%</t>
+          <t>1.75%</t>
         </is>
       </c>
       <c r="D46" s="16" t="inlineStr">
@@ -4020,7 +4020,7 @@
       </c>
       <c r="C47" s="20" t="inlineStr">
         <is>
-          <t>1.30%</t>
+          <t>1.75%</t>
         </is>
       </c>
       <c r="D47" s="20" t="inlineStr">
@@ -4098,7 +4098,7 @@
       </c>
       <c r="C48" s="16" t="inlineStr">
         <is>
-          <t>1.30%</t>
+          <t>1.75%</t>
         </is>
       </c>
       <c r="D48" s="16" t="inlineStr">
@@ -4176,7 +4176,7 @@
       </c>
       <c r="C49" s="20" t="inlineStr">
         <is>
-          <t>1.30%</t>
+          <t>1.75%</t>
         </is>
       </c>
       <c r="D49" s="20" t="inlineStr">
@@ -4254,7 +4254,7 @@
       </c>
       <c r="C50" s="16" t="inlineStr">
         <is>
-          <t>1.30%</t>
+          <t>1.75%</t>
         </is>
       </c>
       <c r="D50" s="16" t="inlineStr">
@@ -4332,7 +4332,7 @@
       </c>
       <c r="C51" s="20" t="inlineStr">
         <is>
-          <t>1.30%</t>
+          <t>1.75%</t>
         </is>
       </c>
       <c r="D51" s="20" t="inlineStr">
@@ -4410,7 +4410,7 @@
       </c>
       <c r="C52" s="16" t="inlineStr">
         <is>
-          <t>1.30%</t>
+          <t>1.75%</t>
         </is>
       </c>
       <c r="D52" s="16" t="inlineStr">
@@ -4488,7 +4488,7 @@
       </c>
       <c r="C53" s="20" t="inlineStr">
         <is>
-          <t>1.30%</t>
+          <t>1.75%</t>
         </is>
       </c>
       <c r="D53" s="20" t="inlineStr">
@@ -4566,7 +4566,7 @@
       </c>
       <c r="C54" s="16" t="inlineStr">
         <is>
-          <t>1.30%</t>
+          <t>1.75%</t>
         </is>
       </c>
       <c r="D54" s="16" t="inlineStr">
@@ -4644,7 +4644,7 @@
       </c>
       <c r="C55" s="20" t="inlineStr">
         <is>
-          <t>1.30%</t>
+          <t>1.75%</t>
         </is>
       </c>
       <c r="D55" s="20" t="inlineStr">
@@ -4724,7 +4724,7 @@
       </c>
       <c r="C56" s="16" t="inlineStr">
         <is>
-          <t>1.30%</t>
+          <t>1.75%</t>
         </is>
       </c>
       <c r="D56" s="16" t="inlineStr">
@@ -4802,7 +4802,7 @@
       </c>
       <c r="C57" s="20" t="inlineStr">
         <is>
-          <t>1.30%</t>
+          <t>1.75%</t>
         </is>
       </c>
       <c r="D57" s="20" t="inlineStr">
@@ -4880,7 +4880,7 @@
       </c>
       <c r="C58" s="16" t="inlineStr">
         <is>
-          <t>1.30%</t>
+          <t>1.75%</t>
         </is>
       </c>
       <c r="D58" s="16" t="inlineStr">
@@ -4958,7 +4958,7 @@
       </c>
       <c r="C59" s="20" t="inlineStr">
         <is>
-          <t>1.30%</t>
+          <t>1.75%</t>
         </is>
       </c>
       <c r="D59" s="20" t="inlineStr">
@@ -5036,7 +5036,7 @@
       </c>
       <c r="C60" s="16" t="inlineStr">
         <is>
-          <t>1.30%</t>
+          <t>1.75%</t>
         </is>
       </c>
       <c r="D60" s="16" t="inlineStr">
@@ -5114,7 +5114,7 @@
       </c>
       <c r="C61" s="20" t="inlineStr">
         <is>
-          <t>1.30%</t>
+          <t>1.75%</t>
         </is>
       </c>
       <c r="D61" s="20" t="inlineStr">
@@ -5192,7 +5192,7 @@
       </c>
       <c r="C62" s="16" t="inlineStr">
         <is>
-          <t>1.30%</t>
+          <t>1.75%</t>
         </is>
       </c>
       <c r="D62" s="16" t="inlineStr">
@@ -5272,7 +5272,7 @@
       </c>
       <c r="C63" s="20" t="inlineStr">
         <is>
-          <t>1.30%</t>
+          <t>1.75%</t>
         </is>
       </c>
       <c r="D63" s="20" t="inlineStr">
@@ -5350,7 +5350,7 @@
       </c>
       <c r="C64" s="16" t="inlineStr">
         <is>
-          <t>1.30%</t>
+          <t>1.75%</t>
         </is>
       </c>
       <c r="D64" s="16" t="inlineStr">
@@ -5428,7 +5428,7 @@
       </c>
       <c r="C65" s="20" t="inlineStr">
         <is>
-          <t>1.30%</t>
+          <t>1.75%</t>
         </is>
       </c>
       <c r="D65" s="20" t="inlineStr">
@@ -5508,7 +5508,7 @@
       </c>
       <c r="C66" s="16" t="inlineStr">
         <is>
-          <t>1.30%</t>
+          <t>1.75%</t>
         </is>
       </c>
       <c r="D66" s="16" t="inlineStr">
@@ -5586,7 +5586,7 @@
       </c>
       <c r="C67" s="20" t="inlineStr">
         <is>
-          <t>1.30%</t>
+          <t>1.75%</t>
         </is>
       </c>
       <c r="D67" s="20" t="inlineStr">
@@ -5666,7 +5666,7 @@
       </c>
       <c r="C68" s="16" t="inlineStr">
         <is>
-          <t>1.30%</t>
+          <t>1.75%</t>
         </is>
       </c>
       <c r="D68" s="16" t="inlineStr">
@@ -5746,7 +5746,7 @@
       </c>
       <c r="C69" s="20" t="inlineStr">
         <is>
-          <t>1.30%</t>
+          <t>1.75%</t>
         </is>
       </c>
       <c r="D69" s="20" t="inlineStr">
@@ -5824,7 +5824,7 @@
       </c>
       <c r="C70" s="16" t="inlineStr">
         <is>
-          <t>1.30%</t>
+          <t>1.75%</t>
         </is>
       </c>
       <c r="D70" s="16" t="inlineStr">
@@ -5902,7 +5902,7 @@
       </c>
       <c r="C71" s="20" t="inlineStr">
         <is>
-          <t>1.30%</t>
+          <t>1.75%</t>
         </is>
       </c>
       <c r="D71" s="20" t="inlineStr">
@@ -5980,7 +5980,7 @@
       </c>
       <c r="C72" s="16" t="inlineStr">
         <is>
-          <t>1.30%</t>
+          <t>1.75%</t>
         </is>
       </c>
       <c r="D72" s="16" t="inlineStr">
@@ -6058,7 +6058,7 @@
       </c>
       <c r="C73" s="20" t="inlineStr">
         <is>
-          <t>1.30%</t>
+          <t>1.75%</t>
         </is>
       </c>
       <c r="D73" s="20" t="inlineStr">
@@ -6136,7 +6136,7 @@
       </c>
       <c r="C74" s="16" t="inlineStr">
         <is>
-          <t>1.30%</t>
+          <t>1.75%</t>
         </is>
       </c>
       <c r="D74" s="16" t="inlineStr">
@@ -6214,7 +6214,7 @@
       </c>
       <c r="C75" s="20" t="inlineStr">
         <is>
-          <t>1.30%</t>
+          <t>1.75%</t>
         </is>
       </c>
       <c r="D75" s="20" t="inlineStr">
@@ -6292,7 +6292,7 @@
       </c>
       <c r="C76" s="16" t="inlineStr">
         <is>
-          <t>1.30%</t>
+          <t>1.75%</t>
         </is>
       </c>
       <c r="D76" s="16" t="inlineStr">
@@ -6370,7 +6370,7 @@
       </c>
       <c r="C77" s="20" t="inlineStr">
         <is>
-          <t>1.30%</t>
+          <t>1.75%</t>
         </is>
       </c>
       <c r="D77" s="20" t="inlineStr">
@@ -6448,7 +6448,7 @@
       </c>
       <c r="C78" s="16" t="inlineStr">
         <is>
-          <t>1.30%</t>
+          <t>1.75%</t>
         </is>
       </c>
       <c r="D78" s="16" t="inlineStr">
@@ -6526,7 +6526,7 @@
       </c>
       <c r="C79" s="20" t="inlineStr">
         <is>
-          <t>1.30%</t>
+          <t>1.75%</t>
         </is>
       </c>
       <c r="D79" s="20" t="inlineStr">
@@ -6604,7 +6604,7 @@
       </c>
       <c r="C80" s="16" t="inlineStr">
         <is>
-          <t>1.30%</t>
+          <t>1.75%</t>
         </is>
       </c>
       <c r="D80" s="16" t="inlineStr">
@@ -6682,7 +6682,7 @@
       </c>
       <c r="C81" s="20" t="inlineStr">
         <is>
-          <t>1.30%</t>
+          <t>1.75%</t>
         </is>
       </c>
       <c r="D81" s="20" t="inlineStr">
@@ -6760,7 +6760,7 @@
       </c>
       <c r="C82" s="16" t="inlineStr">
         <is>
-          <t>1.30%</t>
+          <t>1.75%</t>
         </is>
       </c>
       <c r="D82" s="16" t="inlineStr">
@@ -6840,7 +6840,7 @@
       </c>
       <c r="C83" s="20" t="inlineStr">
         <is>
-          <t>1.30%</t>
+          <t>1.75%</t>
         </is>
       </c>
       <c r="D83" s="20" t="inlineStr">
@@ -6918,7 +6918,7 @@
       </c>
       <c r="C84" s="16" t="inlineStr">
         <is>
-          <t>1.30%</t>
+          <t>1.75%</t>
         </is>
       </c>
       <c r="D84" s="16" t="inlineStr">
@@ -6996,7 +6996,7 @@
       </c>
       <c r="C85" s="20" t="inlineStr">
         <is>
-          <t>1.30%</t>
+          <t>1.75%</t>
         </is>
       </c>
       <c r="D85" s="20" t="inlineStr">
@@ -7074,7 +7074,7 @@
       </c>
       <c r="C86" s="16" t="inlineStr">
         <is>
-          <t>1.30%</t>
+          <t>1.75%</t>
         </is>
       </c>
       <c r="D86" s="16" t="inlineStr">
@@ -7152,7 +7152,7 @@
       </c>
       <c r="C87" s="20" t="inlineStr">
         <is>
-          <t>1.30%</t>
+          <t>1.75%</t>
         </is>
       </c>
       <c r="D87" s="20" t="inlineStr">
@@ -7232,7 +7232,7 @@
       </c>
       <c r="C88" s="16" t="inlineStr">
         <is>
-          <t>1.30%</t>
+          <t>1.75%</t>
         </is>
       </c>
       <c r="D88" s="16" t="inlineStr">
@@ -7310,7 +7310,7 @@
       </c>
       <c r="C89" s="20" t="inlineStr">
         <is>
-          <t>1.30%</t>
+          <t>1.75%</t>
         </is>
       </c>
       <c r="D89" s="20" t="inlineStr">
@@ -7388,7 +7388,7 @@
       </c>
       <c r="C90" s="16" t="inlineStr">
         <is>
-          <t>1.30%</t>
+          <t>1.75%</t>
         </is>
       </c>
       <c r="D90" s="16" t="inlineStr">
@@ -7466,7 +7466,7 @@
       </c>
       <c r="C91" s="20" t="inlineStr">
         <is>
-          <t>1.30%</t>
+          <t>1.75%</t>
         </is>
       </c>
       <c r="D91" s="20" t="inlineStr">
@@ -7544,7 +7544,7 @@
       </c>
       <c r="C92" s="16" t="inlineStr">
         <is>
-          <t>1.30%</t>
+          <t>1.75%</t>
         </is>
       </c>
       <c r="D92" s="16" t="inlineStr">
@@ -7622,7 +7622,7 @@
       </c>
       <c r="C93" s="20" t="inlineStr">
         <is>
-          <t>1.30%</t>
+          <t>1.75%</t>
         </is>
       </c>
       <c r="D93" s="20" t="inlineStr">
@@ -7702,7 +7702,7 @@
       </c>
       <c r="C94" s="16" t="inlineStr">
         <is>
-          <t>1.30%</t>
+          <t>1.75%</t>
         </is>
       </c>
       <c r="D94" s="16" t="inlineStr">
@@ -7780,7 +7780,7 @@
       </c>
       <c r="C95" s="20" t="inlineStr">
         <is>
-          <t>1.30%</t>
+          <t>1.75%</t>
         </is>
       </c>
       <c r="D95" s="20" t="inlineStr">
@@ -7858,7 +7858,7 @@
       </c>
       <c r="C96" s="16" t="inlineStr">
         <is>
-          <t>1.30%</t>
+          <t>1.75%</t>
         </is>
       </c>
       <c r="D96" s="16" t="inlineStr">
@@ -7936,7 +7936,7 @@
       </c>
       <c r="C97" s="20" t="inlineStr">
         <is>
-          <t>1.30%</t>
+          <t>1.75%</t>
         </is>
       </c>
       <c r="D97" s="20" t="inlineStr">
@@ -8014,7 +8014,7 @@
       </c>
       <c r="C98" s="16" t="inlineStr">
         <is>
-          <t>1.30%</t>
+          <t>1.75%</t>
         </is>
       </c>
       <c r="D98" s="16" t="inlineStr">
@@ -8092,7 +8092,7 @@
       </c>
       <c r="C99" s="20" t="inlineStr">
         <is>
-          <t>1.30%</t>
+          <t>1.75%</t>
         </is>
       </c>
       <c r="D99" s="20" t="inlineStr">
@@ -8170,7 +8170,7 @@
       </c>
       <c r="C100" s="16" t="inlineStr">
         <is>
-          <t>1.30%</t>
+          <t>1.75%</t>
         </is>
       </c>
       <c r="D100" s="16" t="inlineStr">
@@ -8248,7 +8248,7 @@
       </c>
       <c r="C101" s="20" t="inlineStr">
         <is>
-          <t>1.30%</t>
+          <t>1.75%</t>
         </is>
       </c>
       <c r="D101" s="20" t="inlineStr">
@@ -8326,7 +8326,7 @@
       </c>
       <c r="C102" s="16" t="inlineStr">
         <is>
-          <t>1.30%</t>
+          <t>1.75%</t>
         </is>
       </c>
       <c r="D102" s="16" t="inlineStr">
@@ -8404,7 +8404,7 @@
       </c>
       <c r="C103" s="20" t="inlineStr">
         <is>
-          <t>1.30%</t>
+          <t>1.75%</t>
         </is>
       </c>
       <c r="D103" s="20" t="inlineStr">
@@ -8482,7 +8482,7 @@
       </c>
       <c r="C104" s="16" t="inlineStr">
         <is>
-          <t>1.30%</t>
+          <t>1.75%</t>
         </is>
       </c>
       <c r="D104" s="16" t="inlineStr">
@@ -8560,7 +8560,7 @@
       </c>
       <c r="C105" s="20" t="inlineStr">
         <is>
-          <t>1.30%</t>
+          <t>1.75%</t>
         </is>
       </c>
       <c r="D105" s="20" t="inlineStr">
@@ -8638,7 +8638,7 @@
       </c>
       <c r="C106" s="24" t="inlineStr">
         <is>
-          <t>0.30%</t>
+          <t>0.75%</t>
         </is>
       </c>
       <c r="D106" s="24" t="inlineStr">
@@ -8716,7 +8716,7 @@
       </c>
       <c r="C107" s="28" t="inlineStr">
         <is>
-          <t>0.30%</t>
+          <t>0.75%</t>
         </is>
       </c>
       <c r="D107" s="28" t="inlineStr">
@@ -8794,7 +8794,7 @@
       </c>
       <c r="C108" s="24" t="inlineStr">
         <is>
-          <t>0.30%</t>
+          <t>0.75%</t>
         </is>
       </c>
       <c r="D108" s="24" t="inlineStr">
@@ -8872,7 +8872,7 @@
       </c>
       <c r="C109" s="28" t="inlineStr">
         <is>
-          <t>0.30%</t>
+          <t>0.75%</t>
         </is>
       </c>
       <c r="D109" s="28" t="inlineStr">
@@ -8950,7 +8950,7 @@
       </c>
       <c r="C110" s="24" t="inlineStr">
         <is>
-          <t>0.30%</t>
+          <t>0.75%</t>
         </is>
       </c>
       <c r="D110" s="24" t="inlineStr">
@@ -9030,7 +9030,7 @@
       </c>
       <c r="C111" s="28" t="inlineStr">
         <is>
-          <t>0.30%</t>
+          <t>0.75%</t>
         </is>
       </c>
       <c r="D111" s="28" t="inlineStr">
@@ -9108,7 +9108,7 @@
       </c>
       <c r="C112" s="24" t="inlineStr">
         <is>
-          <t>0.30%</t>
+          <t>0.75%</t>
         </is>
       </c>
       <c r="D112" s="24" t="inlineStr">
@@ -9186,7 +9186,7 @@
       </c>
       <c r="C113" s="28" t="inlineStr">
         <is>
-          <t>0.30%</t>
+          <t>0.75%</t>
         </is>
       </c>
       <c r="D113" s="28" t="inlineStr">
@@ -9264,7 +9264,7 @@
       </c>
       <c r="C114" s="24" t="inlineStr">
         <is>
-          <t>0.30%</t>
+          <t>0.75%</t>
         </is>
       </c>
       <c r="D114" s="24" t="inlineStr">
@@ -9342,7 +9342,7 @@
       </c>
       <c r="C115" s="28" t="inlineStr">
         <is>
-          <t>0.30%</t>
+          <t>0.75%</t>
         </is>
       </c>
       <c r="D115" s="28" t="inlineStr">
@@ -9420,7 +9420,7 @@
       </c>
       <c r="C116" s="24" t="inlineStr">
         <is>
-          <t>0.30%</t>
+          <t>0.75%</t>
         </is>
       </c>
       <c r="D116" s="24" t="inlineStr">
@@ -9498,7 +9498,7 @@
       </c>
       <c r="C117" s="28" t="inlineStr">
         <is>
-          <t>0.30%</t>
+          <t>0.75%</t>
         </is>
       </c>
       <c r="D117" s="28" t="inlineStr">
@@ -9576,7 +9576,7 @@
       </c>
       <c r="C118" s="24" t="inlineStr">
         <is>
-          <t>0.30%</t>
+          <t>0.75%</t>
         </is>
       </c>
       <c r="D118" s="24" t="inlineStr">
@@ -9654,7 +9654,7 @@
       </c>
       <c r="C119" s="28" t="inlineStr">
         <is>
-          <t>0.30%</t>
+          <t>0.75%</t>
         </is>
       </c>
       <c r="D119" s="28" t="inlineStr">
@@ -9732,7 +9732,7 @@
       </c>
       <c r="C120" s="24" t="inlineStr">
         <is>
-          <t>0.30%</t>
+          <t>0.75%</t>
         </is>
       </c>
       <c r="D120" s="24" t="inlineStr">
@@ -9810,7 +9810,7 @@
       </c>
       <c r="C121" s="28" t="inlineStr">
         <is>
-          <t>0.30%</t>
+          <t>0.75%</t>
         </is>
       </c>
       <c r="D121" s="28" t="inlineStr">
@@ -9888,7 +9888,7 @@
       </c>
       <c r="C122" s="24" t="inlineStr">
         <is>
-          <t>0.30%</t>
+          <t>0.75%</t>
         </is>
       </c>
       <c r="D122" s="24" t="inlineStr">
@@ -9966,7 +9966,7 @@
       </c>
       <c r="C123" s="28" t="inlineStr">
         <is>
-          <t>0.30%</t>
+          <t>0.75%</t>
         </is>
       </c>
       <c r="D123" s="28" t="inlineStr">
@@ -10044,7 +10044,7 @@
       </c>
       <c r="C124" s="24" t="inlineStr">
         <is>
-          <t>0.30%</t>
+          <t>0.75%</t>
         </is>
       </c>
       <c r="D124" s="24" t="inlineStr">
@@ -10122,7 +10122,7 @@
       </c>
       <c r="C125" s="28" t="inlineStr">
         <is>
-          <t>0.30%</t>
+          <t>0.75%</t>
         </is>
       </c>
       <c r="D125" s="28" t="inlineStr">
@@ -10200,7 +10200,7 @@
       </c>
       <c r="C126" s="24" t="inlineStr">
         <is>
-          <t>0.30%</t>
+          <t>0.75%</t>
         </is>
       </c>
       <c r="D126" s="24" t="inlineStr">
@@ -10278,7 +10278,7 @@
       </c>
       <c r="C127" s="28" t="inlineStr">
         <is>
-          <t>0.30%</t>
+          <t>0.75%</t>
         </is>
       </c>
       <c r="D127" s="28" t="inlineStr">
@@ -10356,7 +10356,7 @@
       </c>
       <c r="C128" s="24" t="inlineStr">
         <is>
-          <t>0.30%</t>
+          <t>0.75%</t>
         </is>
       </c>
       <c r="D128" s="24" t="inlineStr">
@@ -10434,7 +10434,7 @@
       </c>
       <c r="C129" s="28" t="inlineStr">
         <is>
-          <t>0.30%</t>
+          <t>0.75%</t>
         </is>
       </c>
       <c r="D129" s="28" t="inlineStr">
@@ -10512,7 +10512,7 @@
       </c>
       <c r="C130" s="24" t="inlineStr">
         <is>
-          <t>0.30%</t>
+          <t>0.75%</t>
         </is>
       </c>
       <c r="D130" s="24" t="inlineStr">
@@ -10590,7 +10590,7 @@
       </c>
       <c r="C131" s="28" t="inlineStr">
         <is>
-          <t>0.30%</t>
+          <t>0.75%</t>
         </is>
       </c>
       <c r="D131" s="28" t="inlineStr">
@@ -10668,7 +10668,7 @@
       </c>
       <c r="C132" s="24" t="inlineStr">
         <is>
-          <t>0.30%</t>
+          <t>0.75%</t>
         </is>
       </c>
       <c r="D132" s="24" t="inlineStr">
@@ -10748,7 +10748,7 @@
       </c>
       <c r="C133" s="28" t="inlineStr">
         <is>
-          <t>0.30%</t>
+          <t>0.75%</t>
         </is>
       </c>
       <c r="D133" s="28" t="inlineStr">
@@ -10828,7 +10828,7 @@
       </c>
       <c r="C134" s="24" t="inlineStr">
         <is>
-          <t>0.30%</t>
+          <t>0.75%</t>
         </is>
       </c>
       <c r="D134" s="24" t="inlineStr">
@@ -10906,7 +10906,7 @@
       </c>
       <c r="C135" s="28" t="inlineStr">
         <is>
-          <t>0.30%</t>
+          <t>0.75%</t>
         </is>
       </c>
       <c r="D135" s="28" t="inlineStr">
@@ -10984,7 +10984,7 @@
       </c>
       <c r="C136" s="24" t="inlineStr">
         <is>
-          <t>0.30%</t>
+          <t>0.75%</t>
         </is>
       </c>
       <c r="D136" s="24" t="inlineStr">
@@ -11064,7 +11064,7 @@
       </c>
       <c r="C137" s="28" t="inlineStr">
         <is>
-          <t>0.30%</t>
+          <t>0.75%</t>
         </is>
       </c>
       <c r="D137" s="28" t="inlineStr">
@@ -11142,7 +11142,7 @@
       </c>
       <c r="C138" s="24" t="inlineStr">
         <is>
-          <t>0.30%</t>
+          <t>0.75%</t>
         </is>
       </c>
       <c r="D138" s="24" t="inlineStr">
@@ -11222,7 +11222,7 @@
       </c>
       <c r="C139" s="28" t="inlineStr">
         <is>
-          <t>0.30%</t>
+          <t>0.75%</t>
         </is>
       </c>
       <c r="D139" s="28" t="inlineStr">
@@ -11300,7 +11300,7 @@
       </c>
       <c r="C140" s="24" t="inlineStr">
         <is>
-          <t>0.30%</t>
+          <t>0.75%</t>
         </is>
       </c>
       <c r="D140" s="24" t="inlineStr">
@@ -11378,7 +11378,7 @@
       </c>
       <c r="C141" s="28" t="inlineStr">
         <is>
-          <t>0.30%</t>
+          <t>0.75%</t>
         </is>
       </c>
       <c r="D141" s="28" t="inlineStr">
@@ -11456,7 +11456,7 @@
       </c>
       <c r="C142" s="24" t="inlineStr">
         <is>
-          <t>0.30%</t>
+          <t>0.75%</t>
         </is>
       </c>
       <c r="D142" s="24" t="inlineStr">
@@ -11534,7 +11534,7 @@
       </c>
       <c r="C143" s="28" t="inlineStr">
         <is>
-          <t>0.30%</t>
+          <t>0.75%</t>
         </is>
       </c>
       <c r="D143" s="28" t="inlineStr">
@@ -11612,7 +11612,7 @@
       </c>
       <c r="C144" s="24" t="inlineStr">
         <is>
-          <t>0.30%</t>
+          <t>0.75%</t>
         </is>
       </c>
       <c r="D144" s="24" t="inlineStr">
@@ -11690,7 +11690,7 @@
       </c>
       <c r="C145" s="28" t="inlineStr">
         <is>
-          <t>0.30%</t>
+          <t>0.75%</t>
         </is>
       </c>
       <c r="D145" s="28" t="inlineStr">
@@ -11768,7 +11768,7 @@
       </c>
       <c r="C146" s="24" t="inlineStr">
         <is>
-          <t>0.30%</t>
+          <t>0.75%</t>
         </is>
       </c>
       <c r="D146" s="24" t="inlineStr">
@@ -11846,7 +11846,7 @@
       </c>
       <c r="C147" s="28" t="inlineStr">
         <is>
-          <t>0.30%</t>
+          <t>0.75%</t>
         </is>
       </c>
       <c r="D147" s="28" t="inlineStr">
@@ -11924,7 +11924,7 @@
       </c>
       <c r="C148" s="24" t="inlineStr">
         <is>
-          <t>0.30%</t>
+          <t>0.75%</t>
         </is>
       </c>
       <c r="D148" s="24" t="inlineStr">
@@ -12002,7 +12002,7 @@
       </c>
       <c r="C149" s="28" t="inlineStr">
         <is>
-          <t>0.30%</t>
+          <t>0.75%</t>
         </is>
       </c>
       <c r="D149" s="28" t="inlineStr">
@@ -12080,7 +12080,7 @@
       </c>
       <c r="C150" s="24" t="inlineStr">
         <is>
-          <t>0.30%</t>
+          <t>0.75%</t>
         </is>
       </c>
       <c r="D150" s="24" t="inlineStr">
@@ -12158,7 +12158,7 @@
       </c>
       <c r="C151" s="28" t="inlineStr">
         <is>
-          <t>0.30%</t>
+          <t>0.75%</t>
         </is>
       </c>
       <c r="D151" s="28" t="inlineStr">
@@ -12236,7 +12236,7 @@
       </c>
       <c r="C152" s="24" t="inlineStr">
         <is>
-          <t>0.30%</t>
+          <t>0.75%</t>
         </is>
       </c>
       <c r="D152" s="24" t="inlineStr">
@@ -12314,7 +12314,7 @@
       </c>
       <c r="C153" s="28" t="inlineStr">
         <is>
-          <t>0.30%</t>
+          <t>0.75%</t>
         </is>
       </c>
       <c r="D153" s="28" t="inlineStr">
@@ -12392,7 +12392,7 @@
       </c>
       <c r="C154" s="24" t="inlineStr">
         <is>
-          <t>0.30%</t>
+          <t>0.75%</t>
         </is>
       </c>
       <c r="D154" s="24" t="inlineStr">
@@ -12470,7 +12470,7 @@
       </c>
       <c r="C155" s="28" t="inlineStr">
         <is>
-          <t>0.30%</t>
+          <t>0.75%</t>
         </is>
       </c>
       <c r="D155" s="28" t="inlineStr">
@@ -12550,7 +12550,7 @@
       </c>
       <c r="C156" s="24" t="inlineStr">
         <is>
-          <t>0.30%</t>
+          <t>0.75%</t>
         </is>
       </c>
       <c r="D156" s="24" t="inlineStr">
@@ -12628,7 +12628,7 @@
       </c>
       <c r="C157" s="28" t="inlineStr">
         <is>
-          <t>0.30%</t>
+          <t>0.75%</t>
         </is>
       </c>
       <c r="D157" s="28" t="inlineStr">
@@ -12706,7 +12706,7 @@
       </c>
       <c r="C158" s="24" t="inlineStr">
         <is>
-          <t>0.30%</t>
+          <t>0.75%</t>
         </is>
       </c>
       <c r="D158" s="24" t="inlineStr">
@@ -12784,7 +12784,7 @@
       </c>
       <c r="C159" s="28" t="inlineStr">
         <is>
-          <t>0.30%</t>
+          <t>0.75%</t>
         </is>
       </c>
       <c r="D159" s="28" t="inlineStr">
@@ -12862,7 +12862,7 @@
       </c>
       <c r="C160" s="24" t="inlineStr">
         <is>
-          <t>0.30%</t>
+          <t>0.75%</t>
         </is>
       </c>
       <c r="D160" s="24" t="inlineStr">
@@ -12940,7 +12940,7 @@
       </c>
       <c r="C161" s="28" t="inlineStr">
         <is>
-          <t>0.30%</t>
+          <t>0.75%</t>
         </is>
       </c>
       <c r="D161" s="28" t="inlineStr">
@@ -13018,7 +13018,7 @@
       </c>
       <c r="C162" s="24" t="inlineStr">
         <is>
-          <t>0.30%</t>
+          <t>0.75%</t>
         </is>
       </c>
       <c r="D162" s="24" t="inlineStr">
@@ -13096,7 +13096,7 @@
       </c>
       <c r="C163" s="28" t="inlineStr">
         <is>
-          <t>0.30%</t>
+          <t>0.75%</t>
         </is>
       </c>
       <c r="D163" s="28" t="inlineStr">
@@ -13174,7 +13174,7 @@
       </c>
       <c r="C164" s="24" t="inlineStr">
         <is>
-          <t>0.30%</t>
+          <t>0.75%</t>
         </is>
       </c>
       <c r="D164" s="24" t="inlineStr">
@@ -13254,7 +13254,7 @@
       </c>
       <c r="C165" s="28" t="inlineStr">
         <is>
-          <t>0.30%</t>
+          <t>0.75%</t>
         </is>
       </c>
       <c r="D165" s="28" t="inlineStr">
@@ -13332,7 +13332,7 @@
       </c>
       <c r="C166" s="24" t="inlineStr">
         <is>
-          <t>0.30%</t>
+          <t>0.75%</t>
         </is>
       </c>
       <c r="D166" s="24" t="inlineStr">
@@ -13412,7 +13412,7 @@
       </c>
       <c r="C167" s="28" t="inlineStr">
         <is>
-          <t>0.30%</t>
+          <t>0.75%</t>
         </is>
       </c>
       <c r="D167" s="28" t="inlineStr">
@@ -13490,7 +13490,7 @@
       </c>
       <c r="C168" s="24" t="inlineStr">
         <is>
-          <t>0.30%</t>
+          <t>0.75%</t>
         </is>
       </c>
       <c r="D168" s="24" t="inlineStr">
@@ -13568,7 +13568,7 @@
       </c>
       <c r="C169" s="28" t="inlineStr">
         <is>
-          <t>0.30%</t>
+          <t>0.75%</t>
         </is>
       </c>
       <c r="D169" s="28" t="inlineStr">
@@ -13646,7 +13646,7 @@
       </c>
       <c r="C170" s="24" t="inlineStr">
         <is>
-          <t>0.30%</t>
+          <t>0.75%</t>
         </is>
       </c>
       <c r="D170" s="24" t="inlineStr">
@@ -13724,7 +13724,7 @@
       </c>
       <c r="C171" s="28" t="inlineStr">
         <is>
-          <t>0.30%</t>
+          <t>0.75%</t>
         </is>
       </c>
       <c r="D171" s="28" t="inlineStr">
@@ -13804,7 +13804,7 @@
       </c>
       <c r="C172" s="24" t="inlineStr">
         <is>
-          <t>0.30%</t>
+          <t>0.75%</t>
         </is>
       </c>
       <c r="D172" s="24" t="inlineStr">
@@ -13884,7 +13884,7 @@
       </c>
       <c r="C173" s="28" t="inlineStr">
         <is>
-          <t>0.30%</t>
+          <t>0.75%</t>
         </is>
       </c>
       <c r="D173" s="28" t="inlineStr">
@@ -13962,7 +13962,7 @@
       </c>
       <c r="C174" s="24" t="inlineStr">
         <is>
-          <t>0.30%</t>
+          <t>0.75%</t>
         </is>
       </c>
       <c r="D174" s="24" t="inlineStr">
@@ -14040,7 +14040,7 @@
       </c>
       <c r="C175" s="28" t="inlineStr">
         <is>
-          <t>0.30%</t>
+          <t>0.75%</t>
         </is>
       </c>
       <c r="D175" s="28" t="inlineStr">
@@ -14118,7 +14118,7 @@
       </c>
       <c r="C176" s="24" t="inlineStr">
         <is>
-          <t>0.30%</t>
+          <t>0.75%</t>
         </is>
       </c>
       <c r="D176" s="24" t="inlineStr">
@@ -14196,7 +14196,7 @@
       </c>
       <c r="C177" s="28" t="inlineStr">
         <is>
-          <t>0.30%</t>
+          <t>0.75%</t>
         </is>
       </c>
       <c r="D177" s="28" t="inlineStr">
@@ -14274,7 +14274,7 @@
       </c>
       <c r="C178" s="24" t="inlineStr">
         <is>
-          <t>0.30%</t>
+          <t>0.75%</t>
         </is>
       </c>
       <c r="D178" s="24" t="inlineStr">
@@ -14352,7 +14352,7 @@
       </c>
       <c r="C179" s="28" t="inlineStr">
         <is>
-          <t>0.30%</t>
+          <t>0.75%</t>
         </is>
       </c>
       <c r="D179" s="28" t="inlineStr">
@@ -14430,7 +14430,7 @@
       </c>
       <c r="C180" s="24" t="inlineStr">
         <is>
-          <t>0.30%</t>
+          <t>0.75%</t>
         </is>
       </c>
       <c r="D180" s="24" t="inlineStr">
@@ -14510,7 +14510,7 @@
       </c>
       <c r="C181" s="28" t="inlineStr">
         <is>
-          <t>0.30%</t>
+          <t>0.75%</t>
         </is>
       </c>
       <c r="D181" s="28" t="inlineStr">
@@ -14588,7 +14588,7 @@
       </c>
       <c r="C182" s="24" t="inlineStr">
         <is>
-          <t>0.30%</t>
+          <t>0.75%</t>
         </is>
       </c>
       <c r="D182" s="24" t="inlineStr">
@@ -14666,7 +14666,7 @@
       </c>
       <c r="C183" s="28" t="inlineStr">
         <is>
-          <t>0.30%</t>
+          <t>0.75%</t>
         </is>
       </c>
       <c r="D183" s="28" t="inlineStr">
@@ -14744,7 +14744,7 @@
       </c>
       <c r="C184" s="24" t="inlineStr">
         <is>
-          <t>0.30%</t>
+          <t>0.75%</t>
         </is>
       </c>
       <c r="D184" s="24" t="inlineStr">
@@ -14822,7 +14822,7 @@
       </c>
       <c r="C185" s="28" t="inlineStr">
         <is>
-          <t>0.30%</t>
+          <t>0.75%</t>
         </is>
       </c>
       <c r="D185" s="28" t="inlineStr">
@@ -14900,7 +14900,7 @@
       </c>
       <c r="C186" s="24" t="inlineStr">
         <is>
-          <t>0.30%</t>
+          <t>0.75%</t>
         </is>
       </c>
       <c r="D186" s="24" t="inlineStr">
@@ -14980,7 +14980,7 @@
       </c>
       <c r="C187" s="28" t="inlineStr">
         <is>
-          <t>0.30%</t>
+          <t>0.75%</t>
         </is>
       </c>
       <c r="D187" s="28" t="inlineStr">
@@ -15058,7 +15058,7 @@
       </c>
       <c r="C188" s="24" t="inlineStr">
         <is>
-          <t>0.30%</t>
+          <t>0.75%</t>
         </is>
       </c>
       <c r="D188" s="24" t="inlineStr">
@@ -15136,7 +15136,7 @@
       </c>
       <c r="C189" s="28" t="inlineStr">
         <is>
-          <t>0.30%</t>
+          <t>0.75%</t>
         </is>
       </c>
       <c r="D189" s="28" t="inlineStr">
@@ -15216,7 +15216,7 @@
       </c>
       <c r="C190" s="24" t="inlineStr">
         <is>
-          <t>0.30%</t>
+          <t>0.75%</t>
         </is>
       </c>
       <c r="D190" s="24" t="inlineStr">
@@ -15294,7 +15294,7 @@
       </c>
       <c r="C191" s="28" t="inlineStr">
         <is>
-          <t>0.30%</t>
+          <t>0.75%</t>
         </is>
       </c>
       <c r="D191" s="28" t="inlineStr">
@@ -15372,7 +15372,7 @@
       </c>
       <c r="C192" s="24" t="inlineStr">
         <is>
-          <t>0.30%</t>
+          <t>0.75%</t>
         </is>
       </c>
       <c r="D192" s="24" t="inlineStr">
@@ -15450,7 +15450,7 @@
       </c>
       <c r="C193" s="28" t="inlineStr">
         <is>
-          <t>0.30%</t>
+          <t>0.75%</t>
         </is>
       </c>
       <c r="D193" s="28" t="inlineStr">
@@ -15528,7 +15528,7 @@
       </c>
       <c r="C194" s="24" t="inlineStr">
         <is>
-          <t>0.30%</t>
+          <t>0.75%</t>
         </is>
       </c>
       <c r="D194" s="24" t="inlineStr">
@@ -15606,7 +15606,7 @@
       </c>
       <c r="C195" s="28" t="inlineStr">
         <is>
-          <t>0.30%</t>
+          <t>0.75%</t>
         </is>
       </c>
       <c r="D195" s="28" t="inlineStr">
@@ -15684,7 +15684,7 @@
       </c>
       <c r="C196" s="24" t="inlineStr">
         <is>
-          <t>0.30%</t>
+          <t>0.75%</t>
         </is>
       </c>
       <c r="D196" s="24" t="inlineStr">
@@ -15762,7 +15762,7 @@
       </c>
       <c r="C197" s="28" t="inlineStr">
         <is>
-          <t>0.30%</t>
+          <t>0.75%</t>
         </is>
       </c>
       <c r="D197" s="28" t="inlineStr">
@@ -15840,7 +15840,7 @@
       </c>
       <c r="C198" s="24" t="inlineStr">
         <is>
-          <t>0.30%</t>
+          <t>0.75%</t>
         </is>
       </c>
       <c r="D198" s="24" t="inlineStr">
@@ -15918,7 +15918,7 @@
       </c>
       <c r="C199" s="28" t="inlineStr">
         <is>
-          <t>0.30%</t>
+          <t>0.75%</t>
         </is>
       </c>
       <c r="D199" s="28" t="inlineStr">
@@ -15996,7 +15996,7 @@
       </c>
       <c r="C200" s="24" t="inlineStr">
         <is>
-          <t>0.30%</t>
+          <t>0.75%</t>
         </is>
       </c>
       <c r="D200" s="24" t="inlineStr">
@@ -16074,7 +16074,7 @@
       </c>
       <c r="C201" s="28" t="inlineStr">
         <is>
-          <t>0.30%</t>
+          <t>0.75%</t>
         </is>
       </c>
       <c r="D201" s="28" t="inlineStr">
@@ -16154,7 +16154,7 @@
       </c>
       <c r="C202" s="24" t="inlineStr">
         <is>
-          <t>0.30%</t>
+          <t>0.75%</t>
         </is>
       </c>
       <c r="D202" s="24" t="inlineStr">
@@ -16232,7 +16232,7 @@
       </c>
       <c r="C203" s="28" t="inlineStr">
         <is>
-          <t>0.30%</t>
+          <t>0.75%</t>
         </is>
       </c>
       <c r="D203" s="28" t="inlineStr">
@@ -16310,7 +16310,7 @@
       </c>
       <c r="C204" s="24" t="inlineStr">
         <is>
-          <t>0.30%</t>
+          <t>0.75%</t>
         </is>
       </c>
       <c r="D204" s="24" t="inlineStr">
@@ -16388,7 +16388,7 @@
       </c>
       <c r="C205" s="32" t="inlineStr">
         <is>
-          <t>0.30%</t>
+          <t>0.75%</t>
         </is>
       </c>
       <c r="D205" s="32" t="inlineStr">
@@ -16507,7 +16507,7 @@
     <row r="2" ht="22" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Long signal: Shareholder Yield + Gross Profitability + ROIC  |  Short signal: Net Ext. Financing + Leverage + F-Score + Gross Profitability  |  130% long top-100 / w_short = 130% × β_long/β_short (Vasicek-adj, 12m trailing)  |  Monthly rebalancing, ±5 pp sector neutrality, beta-neutral</t>
+          <t>Long signal: Shareholder Yield + Gross Profitability + ROIC  |  Short signal: Net Ext. Financing + Leverage + F-Score + Gross Profitability  |  175% long top-100 / w_short = 175% × β_long/β_short (Vasicek-adj, 12m trailing)  |  Monthly rebalancing, ±5% sector neutrality, beta-neutral</t>
         </is>
       </c>
     </row>
@@ -16637,7 +16637,7 @@
       </c>
       <c r="B6" s="16" t="inlineStr">
         <is>
-          <t>1.30%</t>
+          <t>1.75%</t>
         </is>
       </c>
       <c r="C6" s="16" t="inlineStr">
@@ -16710,7 +16710,7 @@
       </c>
       <c r="B7" s="20" t="inlineStr">
         <is>
-          <t>1.30%</t>
+          <t>1.75%</t>
         </is>
       </c>
       <c r="C7" s="20" t="inlineStr">
@@ -16783,7 +16783,7 @@
       </c>
       <c r="B8" s="16" t="inlineStr">
         <is>
-          <t>1.30%</t>
+          <t>1.75%</t>
         </is>
       </c>
       <c r="C8" s="16" t="inlineStr">
@@ -16856,7 +16856,7 @@
       </c>
       <c r="B9" s="20" t="inlineStr">
         <is>
-          <t>1.30%</t>
+          <t>1.75%</t>
         </is>
       </c>
       <c r="C9" s="20" t="inlineStr">
@@ -16929,7 +16929,7 @@
       </c>
       <c r="B10" s="16" t="inlineStr">
         <is>
-          <t>1.30%</t>
+          <t>1.75%</t>
         </is>
       </c>
       <c r="C10" s="16" t="inlineStr">
@@ -17002,7 +17002,7 @@
       </c>
       <c r="B11" s="20" t="inlineStr">
         <is>
-          <t>1.30%</t>
+          <t>1.75%</t>
         </is>
       </c>
       <c r="C11" s="20" t="inlineStr">
@@ -17075,7 +17075,7 @@
       </c>
       <c r="B12" s="16" t="inlineStr">
         <is>
-          <t>1.30%</t>
+          <t>1.75%</t>
         </is>
       </c>
       <c r="C12" s="16" t="inlineStr">
@@ -17148,7 +17148,7 @@
       </c>
       <c r="B13" s="20" t="inlineStr">
         <is>
-          <t>1.30%</t>
+          <t>1.75%</t>
         </is>
       </c>
       <c r="C13" s="20" t="inlineStr">
@@ -17221,7 +17221,7 @@
       </c>
       <c r="B14" s="16" t="inlineStr">
         <is>
-          <t>1.30%</t>
+          <t>1.75%</t>
         </is>
       </c>
       <c r="C14" s="16" t="inlineStr">
@@ -17294,7 +17294,7 @@
       </c>
       <c r="B15" s="20" t="inlineStr">
         <is>
-          <t>1.30%</t>
+          <t>1.75%</t>
         </is>
       </c>
       <c r="C15" s="20" t="inlineStr">
@@ -17367,7 +17367,7 @@
       </c>
       <c r="B16" s="16" t="inlineStr">
         <is>
-          <t>1.30%</t>
+          <t>1.75%</t>
         </is>
       </c>
       <c r="C16" s="16" t="inlineStr">
@@ -17440,7 +17440,7 @@
       </c>
       <c r="B17" s="20" t="inlineStr">
         <is>
-          <t>1.30%</t>
+          <t>1.75%</t>
         </is>
       </c>
       <c r="C17" s="20" t="inlineStr">
@@ -17513,7 +17513,7 @@
       </c>
       <c r="B18" s="16" t="inlineStr">
         <is>
-          <t>1.30%</t>
+          <t>1.75%</t>
         </is>
       </c>
       <c r="C18" s="16" t="inlineStr">
@@ -17586,7 +17586,7 @@
       </c>
       <c r="B19" s="20" t="inlineStr">
         <is>
-          <t>1.30%</t>
+          <t>1.75%</t>
         </is>
       </c>
       <c r="C19" s="20" t="inlineStr">
@@ -17659,7 +17659,7 @@
       </c>
       <c r="B20" s="16" t="inlineStr">
         <is>
-          <t>1.30%</t>
+          <t>1.75%</t>
         </is>
       </c>
       <c r="C20" s="16" t="inlineStr">
@@ -17732,7 +17732,7 @@
       </c>
       <c r="B21" s="20" t="inlineStr">
         <is>
-          <t>1.30%</t>
+          <t>1.75%</t>
         </is>
       </c>
       <c r="C21" s="20" t="inlineStr">
@@ -17805,7 +17805,7 @@
       </c>
       <c r="B22" s="16" t="inlineStr">
         <is>
-          <t>1.30%</t>
+          <t>1.75%</t>
         </is>
       </c>
       <c r="C22" s="16" t="inlineStr">
@@ -17878,7 +17878,7 @@
       </c>
       <c r="B23" s="20" t="inlineStr">
         <is>
-          <t>1.30%</t>
+          <t>1.75%</t>
         </is>
       </c>
       <c r="C23" s="20" t="inlineStr">
@@ -17951,7 +17951,7 @@
       </c>
       <c r="B24" s="16" t="inlineStr">
         <is>
-          <t>1.30%</t>
+          <t>1.75%</t>
         </is>
       </c>
       <c r="C24" s="16" t="inlineStr">
@@ -18024,7 +18024,7 @@
       </c>
       <c r="B25" s="20" t="inlineStr">
         <is>
-          <t>1.30%</t>
+          <t>1.75%</t>
         </is>
       </c>
       <c r="C25" s="20" t="inlineStr">
@@ -18097,7 +18097,7 @@
       </c>
       <c r="B26" s="16" t="inlineStr">
         <is>
-          <t>1.30%</t>
+          <t>1.75%</t>
         </is>
       </c>
       <c r="C26" s="16" t="inlineStr">
@@ -18170,7 +18170,7 @@
       </c>
       <c r="B27" s="20" t="inlineStr">
         <is>
-          <t>1.30%</t>
+          <t>1.75%</t>
         </is>
       </c>
       <c r="C27" s="20" t="inlineStr">
@@ -18243,7 +18243,7 @@
       </c>
       <c r="B28" s="16" t="inlineStr">
         <is>
-          <t>1.30%</t>
+          <t>1.75%</t>
         </is>
       </c>
       <c r="C28" s="16" t="inlineStr">
@@ -18316,7 +18316,7 @@
       </c>
       <c r="B29" s="20" t="inlineStr">
         <is>
-          <t>1.30%</t>
+          <t>1.75%</t>
         </is>
       </c>
       <c r="C29" s="20" t="inlineStr">
@@ -18389,7 +18389,7 @@
       </c>
       <c r="B30" s="16" t="inlineStr">
         <is>
-          <t>1.30%</t>
+          <t>1.75%</t>
         </is>
       </c>
       <c r="C30" s="16" t="inlineStr">
@@ -18462,7 +18462,7 @@
       </c>
       <c r="B31" s="20" t="inlineStr">
         <is>
-          <t>1.30%</t>
+          <t>1.75%</t>
         </is>
       </c>
       <c r="C31" s="20" t="inlineStr">
@@ -18535,7 +18535,7 @@
       </c>
       <c r="B32" s="16" t="inlineStr">
         <is>
-          <t>1.30%</t>
+          <t>1.75%</t>
         </is>
       </c>
       <c r="C32" s="16" t="inlineStr">
@@ -18608,7 +18608,7 @@
       </c>
       <c r="B33" s="20" t="inlineStr">
         <is>
-          <t>1.30%</t>
+          <t>1.75%</t>
         </is>
       </c>
       <c r="C33" s="20" t="inlineStr">
@@ -18681,7 +18681,7 @@
       </c>
       <c r="B34" s="16" t="inlineStr">
         <is>
-          <t>1.30%</t>
+          <t>1.75%</t>
         </is>
       </c>
       <c r="C34" s="16" t="inlineStr">
@@ -18754,7 +18754,7 @@
       </c>
       <c r="B35" s="20" t="inlineStr">
         <is>
-          <t>1.30%</t>
+          <t>1.75%</t>
         </is>
       </c>
       <c r="C35" s="20" t="inlineStr">
@@ -18827,7 +18827,7 @@
       </c>
       <c r="B36" s="16" t="inlineStr">
         <is>
-          <t>1.30%</t>
+          <t>1.75%</t>
         </is>
       </c>
       <c r="C36" s="16" t="inlineStr">
@@ -18900,7 +18900,7 @@
       </c>
       <c r="B37" s="20" t="inlineStr">
         <is>
-          <t>1.30%</t>
+          <t>1.75%</t>
         </is>
       </c>
       <c r="C37" s="20" t="inlineStr">
@@ -18973,7 +18973,7 @@
       </c>
       <c r="B38" s="16" t="inlineStr">
         <is>
-          <t>1.30%</t>
+          <t>1.75%</t>
         </is>
       </c>
       <c r="C38" s="16" t="inlineStr">
@@ -19046,7 +19046,7 @@
       </c>
       <c r="B39" s="20" t="inlineStr">
         <is>
-          <t>1.30%</t>
+          <t>1.75%</t>
         </is>
       </c>
       <c r="C39" s="20" t="inlineStr">
@@ -19119,7 +19119,7 @@
       </c>
       <c r="B40" s="16" t="inlineStr">
         <is>
-          <t>1.30%</t>
+          <t>1.75%</t>
         </is>
       </c>
       <c r="C40" s="16" t="inlineStr">
@@ -19192,7 +19192,7 @@
       </c>
       <c r="B41" s="20" t="inlineStr">
         <is>
-          <t>1.30%</t>
+          <t>1.75%</t>
         </is>
       </c>
       <c r="C41" s="20" t="inlineStr">
@@ -19265,7 +19265,7 @@
       </c>
       <c r="B42" s="16" t="inlineStr">
         <is>
-          <t>1.30%</t>
+          <t>1.75%</t>
         </is>
       </c>
       <c r="C42" s="16" t="inlineStr">
@@ -19338,7 +19338,7 @@
       </c>
       <c r="B43" s="20" t="inlineStr">
         <is>
-          <t>1.30%</t>
+          <t>1.75%</t>
         </is>
       </c>
       <c r="C43" s="20" t="inlineStr">
@@ -19411,7 +19411,7 @@
       </c>
       <c r="B44" s="16" t="inlineStr">
         <is>
-          <t>1.30%</t>
+          <t>1.75%</t>
         </is>
       </c>
       <c r="C44" s="16" t="inlineStr">
@@ -19484,7 +19484,7 @@
       </c>
       <c r="B45" s="20" t="inlineStr">
         <is>
-          <t>1.30%</t>
+          <t>1.75%</t>
         </is>
       </c>
       <c r="C45" s="20" t="inlineStr">
@@ -19557,7 +19557,7 @@
       </c>
       <c r="B46" s="16" t="inlineStr">
         <is>
-          <t>1.30%</t>
+          <t>1.75%</t>
         </is>
       </c>
       <c r="C46" s="16" t="inlineStr">
@@ -19630,7 +19630,7 @@
       </c>
       <c r="B47" s="20" t="inlineStr">
         <is>
-          <t>1.30%</t>
+          <t>1.75%</t>
         </is>
       </c>
       <c r="C47" s="20" t="inlineStr">
@@ -19703,7 +19703,7 @@
       </c>
       <c r="B48" s="16" t="inlineStr">
         <is>
-          <t>1.30%</t>
+          <t>1.75%</t>
         </is>
       </c>
       <c r="C48" s="16" t="inlineStr">
@@ -19776,7 +19776,7 @@
       </c>
       <c r="B49" s="20" t="inlineStr">
         <is>
-          <t>1.30%</t>
+          <t>1.75%</t>
         </is>
       </c>
       <c r="C49" s="20" t="inlineStr">
@@ -19849,7 +19849,7 @@
       </c>
       <c r="B50" s="16" t="inlineStr">
         <is>
-          <t>1.30%</t>
+          <t>1.75%</t>
         </is>
       </c>
       <c r="C50" s="16" t="inlineStr">
@@ -19922,7 +19922,7 @@
       </c>
       <c r="B51" s="20" t="inlineStr">
         <is>
-          <t>1.30%</t>
+          <t>1.75%</t>
         </is>
       </c>
       <c r="C51" s="20" t="inlineStr">
@@ -19995,7 +19995,7 @@
       </c>
       <c r="B52" s="16" t="inlineStr">
         <is>
-          <t>1.30%</t>
+          <t>1.75%</t>
         </is>
       </c>
       <c r="C52" s="16" t="inlineStr">
@@ -20068,7 +20068,7 @@
       </c>
       <c r="B53" s="20" t="inlineStr">
         <is>
-          <t>1.30%</t>
+          <t>1.75%</t>
         </is>
       </c>
       <c r="C53" s="20" t="inlineStr">
@@ -20141,7 +20141,7 @@
       </c>
       <c r="B54" s="16" t="inlineStr">
         <is>
-          <t>1.30%</t>
+          <t>1.75%</t>
         </is>
       </c>
       <c r="C54" s="16" t="inlineStr">
@@ -20214,7 +20214,7 @@
       </c>
       <c r="B55" s="20" t="inlineStr">
         <is>
-          <t>1.30%</t>
+          <t>1.75%</t>
         </is>
       </c>
       <c r="C55" s="20" t="inlineStr">
@@ -20289,7 +20289,7 @@
       </c>
       <c r="B56" s="16" t="inlineStr">
         <is>
-          <t>1.30%</t>
+          <t>1.75%</t>
         </is>
       </c>
       <c r="C56" s="16" t="inlineStr">
@@ -20362,7 +20362,7 @@
       </c>
       <c r="B57" s="20" t="inlineStr">
         <is>
-          <t>1.30%</t>
+          <t>1.75%</t>
         </is>
       </c>
       <c r="C57" s="20" t="inlineStr">
@@ -20435,7 +20435,7 @@
       </c>
       <c r="B58" s="16" t="inlineStr">
         <is>
-          <t>1.30%</t>
+          <t>1.75%</t>
         </is>
       </c>
       <c r="C58" s="16" t="inlineStr">
@@ -20508,7 +20508,7 @@
       </c>
       <c r="B59" s="20" t="inlineStr">
         <is>
-          <t>1.30%</t>
+          <t>1.75%</t>
         </is>
       </c>
       <c r="C59" s="20" t="inlineStr">
@@ -20581,7 +20581,7 @@
       </c>
       <c r="B60" s="16" t="inlineStr">
         <is>
-          <t>1.30%</t>
+          <t>1.75%</t>
         </is>
       </c>
       <c r="C60" s="16" t="inlineStr">
@@ -20654,7 +20654,7 @@
       </c>
       <c r="B61" s="20" t="inlineStr">
         <is>
-          <t>1.30%</t>
+          <t>1.75%</t>
         </is>
       </c>
       <c r="C61" s="20" t="inlineStr">
@@ -20727,7 +20727,7 @@
       </c>
       <c r="B62" s="16" t="inlineStr">
         <is>
-          <t>1.30%</t>
+          <t>1.75%</t>
         </is>
       </c>
       <c r="C62" s="16" t="inlineStr">
@@ -20802,7 +20802,7 @@
       </c>
       <c r="B63" s="20" t="inlineStr">
         <is>
-          <t>1.30%</t>
+          <t>1.75%</t>
         </is>
       </c>
       <c r="C63" s="20" t="inlineStr">
@@ -20875,7 +20875,7 @@
       </c>
       <c r="B64" s="16" t="inlineStr">
         <is>
-          <t>1.30%</t>
+          <t>1.75%</t>
         </is>
       </c>
       <c r="C64" s="16" t="inlineStr">
@@ -20948,7 +20948,7 @@
       </c>
       <c r="B65" s="20" t="inlineStr">
         <is>
-          <t>1.30%</t>
+          <t>1.75%</t>
         </is>
       </c>
       <c r="C65" s="20" t="inlineStr">
@@ -21023,7 +21023,7 @@
       </c>
       <c r="B66" s="16" t="inlineStr">
         <is>
-          <t>1.30%</t>
+          <t>1.75%</t>
         </is>
       </c>
       <c r="C66" s="16" t="inlineStr">
@@ -21096,7 +21096,7 @@
       </c>
       <c r="B67" s="20" t="inlineStr">
         <is>
-          <t>1.30%</t>
+          <t>1.75%</t>
         </is>
       </c>
       <c r="C67" s="20" t="inlineStr">
@@ -21171,7 +21171,7 @@
       </c>
       <c r="B68" s="16" t="inlineStr">
         <is>
-          <t>1.30%</t>
+          <t>1.75%</t>
         </is>
       </c>
       <c r="C68" s="16" t="inlineStr">
@@ -21246,7 +21246,7 @@
       </c>
       <c r="B69" s="20" t="inlineStr">
         <is>
-          <t>1.30%</t>
+          <t>1.75%</t>
         </is>
       </c>
       <c r="C69" s="20" t="inlineStr">
@@ -21319,7 +21319,7 @@
       </c>
       <c r="B70" s="16" t="inlineStr">
         <is>
-          <t>1.30%</t>
+          <t>1.75%</t>
         </is>
       </c>
       <c r="C70" s="16" t="inlineStr">
@@ -21392,7 +21392,7 @@
       </c>
       <c r="B71" s="20" t="inlineStr">
         <is>
-          <t>1.30%</t>
+          <t>1.75%</t>
         </is>
       </c>
       <c r="C71" s="20" t="inlineStr">
@@ -21465,7 +21465,7 @@
       </c>
       <c r="B72" s="16" t="inlineStr">
         <is>
-          <t>1.30%</t>
+          <t>1.75%</t>
         </is>
       </c>
       <c r="C72" s="16" t="inlineStr">
@@ -21538,7 +21538,7 @@
       </c>
       <c r="B73" s="20" t="inlineStr">
         <is>
-          <t>1.30%</t>
+          <t>1.75%</t>
         </is>
       </c>
       <c r="C73" s="20" t="inlineStr">
@@ -21611,7 +21611,7 @@
       </c>
       <c r="B74" s="16" t="inlineStr">
         <is>
-          <t>1.30%</t>
+          <t>1.75%</t>
         </is>
       </c>
       <c r="C74" s="16" t="inlineStr">
@@ -21684,7 +21684,7 @@
       </c>
       <c r="B75" s="20" t="inlineStr">
         <is>
-          <t>1.30%</t>
+          <t>1.75%</t>
         </is>
       </c>
       <c r="C75" s="20" t="inlineStr">
@@ -21757,7 +21757,7 @@
       </c>
       <c r="B76" s="16" t="inlineStr">
         <is>
-          <t>1.30%</t>
+          <t>1.75%</t>
         </is>
       </c>
       <c r="C76" s="16" t="inlineStr">
@@ -21830,7 +21830,7 @@
       </c>
       <c r="B77" s="20" t="inlineStr">
         <is>
-          <t>1.30%</t>
+          <t>1.75%</t>
         </is>
       </c>
       <c r="C77" s="20" t="inlineStr">
@@ -21903,7 +21903,7 @@
       </c>
       <c r="B78" s="16" t="inlineStr">
         <is>
-          <t>1.30%</t>
+          <t>1.75%</t>
         </is>
       </c>
       <c r="C78" s="16" t="inlineStr">
@@ -21976,7 +21976,7 @@
       </c>
       <c r="B79" s="20" t="inlineStr">
         <is>
-          <t>1.30%</t>
+          <t>1.75%</t>
         </is>
       </c>
       <c r="C79" s="20" t="inlineStr">
@@ -22049,7 +22049,7 @@
       </c>
       <c r="B80" s="16" t="inlineStr">
         <is>
-          <t>1.30%</t>
+          <t>1.75%</t>
         </is>
       </c>
       <c r="C80" s="16" t="inlineStr">
@@ -22122,7 +22122,7 @@
       </c>
       <c r="B81" s="20" t="inlineStr">
         <is>
-          <t>1.30%</t>
+          <t>1.75%</t>
         </is>
       </c>
       <c r="C81" s="20" t="inlineStr">
@@ -22195,7 +22195,7 @@
       </c>
       <c r="B82" s="16" t="inlineStr">
         <is>
-          <t>1.30%</t>
+          <t>1.75%</t>
         </is>
       </c>
       <c r="C82" s="16" t="inlineStr">
@@ -22270,7 +22270,7 @@
       </c>
       <c r="B83" s="20" t="inlineStr">
         <is>
-          <t>1.30%</t>
+          <t>1.75%</t>
         </is>
       </c>
       <c r="C83" s="20" t="inlineStr">
@@ -22343,7 +22343,7 @@
       </c>
       <c r="B84" s="16" t="inlineStr">
         <is>
-          <t>1.30%</t>
+          <t>1.75%</t>
         </is>
       </c>
       <c r="C84" s="16" t="inlineStr">
@@ -22416,7 +22416,7 @@
       </c>
       <c r="B85" s="20" t="inlineStr">
         <is>
-          <t>1.30%</t>
+          <t>1.75%</t>
         </is>
       </c>
       <c r="C85" s="20" t="inlineStr">
@@ -22489,7 +22489,7 @@
       </c>
       <c r="B86" s="16" t="inlineStr">
         <is>
-          <t>1.30%</t>
+          <t>1.75%</t>
         </is>
       </c>
       <c r="C86" s="16" t="inlineStr">
@@ -22562,7 +22562,7 @@
       </c>
       <c r="B87" s="20" t="inlineStr">
         <is>
-          <t>1.30%</t>
+          <t>1.75%</t>
         </is>
       </c>
       <c r="C87" s="20" t="inlineStr">
@@ -22637,7 +22637,7 @@
       </c>
       <c r="B88" s="16" t="inlineStr">
         <is>
-          <t>1.30%</t>
+          <t>1.75%</t>
         </is>
       </c>
       <c r="C88" s="16" t="inlineStr">
@@ -22710,7 +22710,7 @@
       </c>
       <c r="B89" s="20" t="inlineStr">
         <is>
-          <t>1.30%</t>
+          <t>1.75%</t>
         </is>
       </c>
       <c r="C89" s="20" t="inlineStr">
@@ -22783,7 +22783,7 @@
       </c>
       <c r="B90" s="16" t="inlineStr">
         <is>
-          <t>1.30%</t>
+          <t>1.75%</t>
         </is>
       </c>
       <c r="C90" s="16" t="inlineStr">
@@ -22856,7 +22856,7 @@
       </c>
       <c r="B91" s="20" t="inlineStr">
         <is>
-          <t>1.30%</t>
+          <t>1.75%</t>
         </is>
       </c>
       <c r="C91" s="20" t="inlineStr">
@@ -22929,7 +22929,7 @@
       </c>
       <c r="B92" s="16" t="inlineStr">
         <is>
-          <t>1.30%</t>
+          <t>1.75%</t>
         </is>
       </c>
       <c r="C92" s="16" t="inlineStr">
@@ -23002,7 +23002,7 @@
       </c>
       <c r="B93" s="20" t="inlineStr">
         <is>
-          <t>1.30%</t>
+          <t>1.75%</t>
         </is>
       </c>
       <c r="C93" s="20" t="inlineStr">
@@ -23077,7 +23077,7 @@
       </c>
       <c r="B94" s="16" t="inlineStr">
         <is>
-          <t>1.30%</t>
+          <t>1.75%</t>
         </is>
       </c>
       <c r="C94" s="16" t="inlineStr">
@@ -23150,7 +23150,7 @@
       </c>
       <c r="B95" s="20" t="inlineStr">
         <is>
-          <t>1.30%</t>
+          <t>1.75%</t>
         </is>
       </c>
       <c r="C95" s="20" t="inlineStr">
@@ -23223,7 +23223,7 @@
       </c>
       <c r="B96" s="16" t="inlineStr">
         <is>
-          <t>1.30%</t>
+          <t>1.75%</t>
         </is>
       </c>
       <c r="C96" s="16" t="inlineStr">
@@ -23296,7 +23296,7 @@
       </c>
       <c r="B97" s="20" t="inlineStr">
         <is>
-          <t>1.30%</t>
+          <t>1.75%</t>
         </is>
       </c>
       <c r="C97" s="20" t="inlineStr">
@@ -23369,7 +23369,7 @@
       </c>
       <c r="B98" s="16" t="inlineStr">
         <is>
-          <t>1.30%</t>
+          <t>1.75%</t>
         </is>
       </c>
       <c r="C98" s="16" t="inlineStr">
@@ -23442,7 +23442,7 @@
       </c>
       <c r="B99" s="20" t="inlineStr">
         <is>
-          <t>1.30%</t>
+          <t>1.75%</t>
         </is>
       </c>
       <c r="C99" s="20" t="inlineStr">
@@ -23515,7 +23515,7 @@
       </c>
       <c r="B100" s="16" t="inlineStr">
         <is>
-          <t>1.30%</t>
+          <t>1.75%</t>
         </is>
       </c>
       <c r="C100" s="16" t="inlineStr">
@@ -23588,7 +23588,7 @@
       </c>
       <c r="B101" s="20" t="inlineStr">
         <is>
-          <t>1.30%</t>
+          <t>1.75%</t>
         </is>
       </c>
       <c r="C101" s="20" t="inlineStr">
@@ -23661,7 +23661,7 @@
       </c>
       <c r="B102" s="16" t="inlineStr">
         <is>
-          <t>1.30%</t>
+          <t>1.75%</t>
         </is>
       </c>
       <c r="C102" s="16" t="inlineStr">
@@ -23734,7 +23734,7 @@
       </c>
       <c r="B103" s="20" t="inlineStr">
         <is>
-          <t>1.30%</t>
+          <t>1.75%</t>
         </is>
       </c>
       <c r="C103" s="20" t="inlineStr">
@@ -23807,7 +23807,7 @@
       </c>
       <c r="B104" s="16" t="inlineStr">
         <is>
-          <t>1.30%</t>
+          <t>1.75%</t>
         </is>
       </c>
       <c r="C104" s="16" t="inlineStr">
@@ -23880,7 +23880,7 @@
       </c>
       <c r="B105" s="36" t="inlineStr">
         <is>
-          <t>1.30%</t>
+          <t>1.75%</t>
         </is>
       </c>
       <c r="C105" s="36" t="inlineStr">
@@ -23999,7 +23999,7 @@
     <row r="2" ht="22" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Long signal: Shareholder Yield + Gross Profitability + ROIC  |  Short signal: Net Ext. Financing + Leverage + F-Score + Gross Profitability  |  130% long top-100 / w_short = 130% × β_long/β_short (Vasicek-adj, 12m trailing)  |  Monthly rebalancing, ±5 pp sector neutrality, beta-neutral</t>
+          <t>Long signal: Shareholder Yield + Gross Profitability + ROIC  |  Short signal: Net Ext. Financing + Leverage + F-Score + Gross Profitability  |  175% long top-100 / w_short = 175% × β_long/β_short (Vasicek-adj, 12m trailing)  |  Monthly rebalancing, ±5% sector neutrality, beta-neutral</t>
         </is>
       </c>
     </row>
@@ -24129,7 +24129,7 @@
       </c>
       <c r="B6" s="24" t="inlineStr">
         <is>
-          <t>0.30%</t>
+          <t>0.75%</t>
         </is>
       </c>
       <c r="C6" s="24" t="inlineStr">
@@ -24202,7 +24202,7 @@
       </c>
       <c r="B7" s="28" t="inlineStr">
         <is>
-          <t>0.30%</t>
+          <t>0.75%</t>
         </is>
       </c>
       <c r="C7" s="28" t="inlineStr">
@@ -24275,7 +24275,7 @@
       </c>
       <c r="B8" s="24" t="inlineStr">
         <is>
-          <t>0.30%</t>
+          <t>0.75%</t>
         </is>
       </c>
       <c r="C8" s="24" t="inlineStr">
@@ -24348,7 +24348,7 @@
       </c>
       <c r="B9" s="28" t="inlineStr">
         <is>
-          <t>0.30%</t>
+          <t>0.75%</t>
         </is>
       </c>
       <c r="C9" s="28" t="inlineStr">
@@ -24421,7 +24421,7 @@
       </c>
       <c r="B10" s="24" t="inlineStr">
         <is>
-          <t>0.30%</t>
+          <t>0.75%</t>
         </is>
       </c>
       <c r="C10" s="24" t="inlineStr">
@@ -24496,7 +24496,7 @@
       </c>
       <c r="B11" s="28" t="inlineStr">
         <is>
-          <t>0.30%</t>
+          <t>0.75%</t>
         </is>
       </c>
       <c r="C11" s="28" t="inlineStr">
@@ -24569,7 +24569,7 @@
       </c>
       <c r="B12" s="24" t="inlineStr">
         <is>
-          <t>0.30%</t>
+          <t>0.75%</t>
         </is>
       </c>
       <c r="C12" s="24" t="inlineStr">
@@ -24642,7 +24642,7 @@
       </c>
       <c r="B13" s="28" t="inlineStr">
         <is>
-          <t>0.30%</t>
+          <t>0.75%</t>
         </is>
       </c>
       <c r="C13" s="28" t="inlineStr">
@@ -24715,7 +24715,7 @@
       </c>
       <c r="B14" s="24" t="inlineStr">
         <is>
-          <t>0.30%</t>
+          <t>0.75%</t>
         </is>
       </c>
       <c r="C14" s="24" t="inlineStr">
@@ -24788,7 +24788,7 @@
       </c>
       <c r="B15" s="28" t="inlineStr">
         <is>
-          <t>0.30%</t>
+          <t>0.75%</t>
         </is>
       </c>
       <c r="C15" s="28" t="inlineStr">
@@ -24861,7 +24861,7 @@
       </c>
       <c r="B16" s="24" t="inlineStr">
         <is>
-          <t>0.30%</t>
+          <t>0.75%</t>
         </is>
       </c>
       <c r="C16" s="24" t="inlineStr">
@@ -24934,7 +24934,7 @@
       </c>
       <c r="B17" s="28" t="inlineStr">
         <is>
-          <t>0.30%</t>
+          <t>0.75%</t>
         </is>
       </c>
       <c r="C17" s="28" t="inlineStr">
@@ -25007,7 +25007,7 @@
       </c>
       <c r="B18" s="24" t="inlineStr">
         <is>
-          <t>0.30%</t>
+          <t>0.75%</t>
         </is>
       </c>
       <c r="C18" s="24" t="inlineStr">
@@ -25080,7 +25080,7 @@
       </c>
       <c r="B19" s="28" t="inlineStr">
         <is>
-          <t>0.30%</t>
+          <t>0.75%</t>
         </is>
       </c>
       <c r="C19" s="28" t="inlineStr">
@@ -25153,7 +25153,7 @@
       </c>
       <c r="B20" s="24" t="inlineStr">
         <is>
-          <t>0.30%</t>
+          <t>0.75%</t>
         </is>
       </c>
       <c r="C20" s="24" t="inlineStr">
@@ -25226,7 +25226,7 @@
       </c>
       <c r="B21" s="28" t="inlineStr">
         <is>
-          <t>0.30%</t>
+          <t>0.75%</t>
         </is>
       </c>
       <c r="C21" s="28" t="inlineStr">
@@ -25299,7 +25299,7 @@
       </c>
       <c r="B22" s="24" t="inlineStr">
         <is>
-          <t>0.30%</t>
+          <t>0.75%</t>
         </is>
       </c>
       <c r="C22" s="24" t="inlineStr">
@@ -25372,7 +25372,7 @@
       </c>
       <c r="B23" s="28" t="inlineStr">
         <is>
-          <t>0.30%</t>
+          <t>0.75%</t>
         </is>
       </c>
       <c r="C23" s="28" t="inlineStr">
@@ -25445,7 +25445,7 @@
       </c>
       <c r="B24" s="24" t="inlineStr">
         <is>
-          <t>0.30%</t>
+          <t>0.75%</t>
         </is>
       </c>
       <c r="C24" s="24" t="inlineStr">
@@ -25518,7 +25518,7 @@
       </c>
       <c r="B25" s="28" t="inlineStr">
         <is>
-          <t>0.30%</t>
+          <t>0.75%</t>
         </is>
       </c>
       <c r="C25" s="28" t="inlineStr">
@@ -25591,7 +25591,7 @@
       </c>
       <c r="B26" s="24" t="inlineStr">
         <is>
-          <t>0.30%</t>
+          <t>0.75%</t>
         </is>
       </c>
       <c r="C26" s="24" t="inlineStr">
@@ -25664,7 +25664,7 @@
       </c>
       <c r="B27" s="28" t="inlineStr">
         <is>
-          <t>0.30%</t>
+          <t>0.75%</t>
         </is>
       </c>
       <c r="C27" s="28" t="inlineStr">
@@ -25737,7 +25737,7 @@
       </c>
       <c r="B28" s="24" t="inlineStr">
         <is>
-          <t>0.30%</t>
+          <t>0.75%</t>
         </is>
       </c>
       <c r="C28" s="24" t="inlineStr">
@@ -25810,7 +25810,7 @@
       </c>
       <c r="B29" s="28" t="inlineStr">
         <is>
-          <t>0.30%</t>
+          <t>0.75%</t>
         </is>
       </c>
       <c r="C29" s="28" t="inlineStr">
@@ -25883,7 +25883,7 @@
       </c>
       <c r="B30" s="24" t="inlineStr">
         <is>
-          <t>0.30%</t>
+          <t>0.75%</t>
         </is>
       </c>
       <c r="C30" s="24" t="inlineStr">
@@ -25956,7 +25956,7 @@
       </c>
       <c r="B31" s="28" t="inlineStr">
         <is>
-          <t>0.30%</t>
+          <t>0.75%</t>
         </is>
       </c>
       <c r="C31" s="28" t="inlineStr">
@@ -26029,7 +26029,7 @@
       </c>
       <c r="B32" s="24" t="inlineStr">
         <is>
-          <t>0.30%</t>
+          <t>0.75%</t>
         </is>
       </c>
       <c r="C32" s="24" t="inlineStr">
@@ -26104,7 +26104,7 @@
       </c>
       <c r="B33" s="28" t="inlineStr">
         <is>
-          <t>0.30%</t>
+          <t>0.75%</t>
         </is>
       </c>
       <c r="C33" s="28" t="inlineStr">
@@ -26179,7 +26179,7 @@
       </c>
       <c r="B34" s="24" t="inlineStr">
         <is>
-          <t>0.30%</t>
+          <t>0.75%</t>
         </is>
       </c>
       <c r="C34" s="24" t="inlineStr">
@@ -26252,7 +26252,7 @@
       </c>
       <c r="B35" s="28" t="inlineStr">
         <is>
-          <t>0.30%</t>
+          <t>0.75%</t>
         </is>
       </c>
       <c r="C35" s="28" t="inlineStr">
@@ -26325,7 +26325,7 @@
       </c>
       <c r="B36" s="24" t="inlineStr">
         <is>
-          <t>0.30%</t>
+          <t>0.75%</t>
         </is>
       </c>
       <c r="C36" s="24" t="inlineStr">
@@ -26400,7 +26400,7 @@
       </c>
       <c r="B37" s="28" t="inlineStr">
         <is>
-          <t>0.30%</t>
+          <t>0.75%</t>
         </is>
       </c>
       <c r="C37" s="28" t="inlineStr">
@@ -26473,7 +26473,7 @@
       </c>
       <c r="B38" s="24" t="inlineStr">
         <is>
-          <t>0.30%</t>
+          <t>0.75%</t>
         </is>
       </c>
       <c r="C38" s="24" t="inlineStr">
@@ -26548,7 +26548,7 @@
       </c>
       <c r="B39" s="28" t="inlineStr">
         <is>
-          <t>0.30%</t>
+          <t>0.75%</t>
         </is>
       </c>
       <c r="C39" s="28" t="inlineStr">
@@ -26621,7 +26621,7 @@
       </c>
       <c r="B40" s="24" t="inlineStr">
         <is>
-          <t>0.30%</t>
+          <t>0.75%</t>
         </is>
       </c>
       <c r="C40" s="24" t="inlineStr">
@@ -26694,7 +26694,7 @@
       </c>
       <c r="B41" s="28" t="inlineStr">
         <is>
-          <t>0.30%</t>
+          <t>0.75%</t>
         </is>
       </c>
       <c r="C41" s="28" t="inlineStr">
@@ -26767,7 +26767,7 @@
       </c>
       <c r="B42" s="24" t="inlineStr">
         <is>
-          <t>0.30%</t>
+          <t>0.75%</t>
         </is>
       </c>
       <c r="C42" s="24" t="inlineStr">
@@ -26840,7 +26840,7 @@
       </c>
       <c r="B43" s="28" t="inlineStr">
         <is>
-          <t>0.30%</t>
+          <t>0.75%</t>
         </is>
       </c>
       <c r="C43" s="28" t="inlineStr">
@@ -26913,7 +26913,7 @@
       </c>
       <c r="B44" s="24" t="inlineStr">
         <is>
-          <t>0.30%</t>
+          <t>0.75%</t>
         </is>
       </c>
       <c r="C44" s="24" t="inlineStr">
@@ -26986,7 +26986,7 @@
       </c>
       <c r="B45" s="28" t="inlineStr">
         <is>
-          <t>0.30%</t>
+          <t>0.75%</t>
         </is>
       </c>
       <c r="C45" s="28" t="inlineStr">
@@ -27059,7 +27059,7 @@
       </c>
       <c r="B46" s="24" t="inlineStr">
         <is>
-          <t>0.30%</t>
+          <t>0.75%</t>
         </is>
       </c>
       <c r="C46" s="24" t="inlineStr">
@@ -27132,7 +27132,7 @@
       </c>
       <c r="B47" s="28" t="inlineStr">
         <is>
-          <t>0.30%</t>
+          <t>0.75%</t>
         </is>
       </c>
       <c r="C47" s="28" t="inlineStr">
@@ -27205,7 +27205,7 @@
       </c>
       <c r="B48" s="24" t="inlineStr">
         <is>
-          <t>0.30%</t>
+          <t>0.75%</t>
         </is>
       </c>
       <c r="C48" s="24" t="inlineStr">
@@ -27278,7 +27278,7 @@
       </c>
       <c r="B49" s="28" t="inlineStr">
         <is>
-          <t>0.30%</t>
+          <t>0.75%</t>
         </is>
       </c>
       <c r="C49" s="28" t="inlineStr">
@@ -27351,7 +27351,7 @@
       </c>
       <c r="B50" s="24" t="inlineStr">
         <is>
-          <t>0.30%</t>
+          <t>0.75%</t>
         </is>
       </c>
       <c r="C50" s="24" t="inlineStr">
@@ -27424,7 +27424,7 @@
       </c>
       <c r="B51" s="28" t="inlineStr">
         <is>
-          <t>0.30%</t>
+          <t>0.75%</t>
         </is>
       </c>
       <c r="C51" s="28" t="inlineStr">
@@ -27497,7 +27497,7 @@
       </c>
       <c r="B52" s="24" t="inlineStr">
         <is>
-          <t>0.30%</t>
+          <t>0.75%</t>
         </is>
       </c>
       <c r="C52" s="24" t="inlineStr">
@@ -27570,7 +27570,7 @@
       </c>
       <c r="B53" s="28" t="inlineStr">
         <is>
-          <t>0.30%</t>
+          <t>0.75%</t>
         </is>
       </c>
       <c r="C53" s="28" t="inlineStr">
@@ -27643,7 +27643,7 @@
       </c>
       <c r="B54" s="24" t="inlineStr">
         <is>
-          <t>0.30%</t>
+          <t>0.75%</t>
         </is>
       </c>
       <c r="C54" s="24" t="inlineStr">
@@ -27716,7 +27716,7 @@
       </c>
       <c r="B55" s="28" t="inlineStr">
         <is>
-          <t>0.30%</t>
+          <t>0.75%</t>
         </is>
       </c>
       <c r="C55" s="28" t="inlineStr">
@@ -27791,7 +27791,7 @@
       </c>
       <c r="B56" s="24" t="inlineStr">
         <is>
-          <t>0.30%</t>
+          <t>0.75%</t>
         </is>
       </c>
       <c r="C56" s="24" t="inlineStr">
@@ -27864,7 +27864,7 @@
       </c>
       <c r="B57" s="28" t="inlineStr">
         <is>
-          <t>0.30%</t>
+          <t>0.75%</t>
         </is>
       </c>
       <c r="C57" s="28" t="inlineStr">
@@ -27937,7 +27937,7 @@
       </c>
       <c r="B58" s="24" t="inlineStr">
         <is>
-          <t>0.30%</t>
+          <t>0.75%</t>
         </is>
       </c>
       <c r="C58" s="24" t="inlineStr">
@@ -28010,7 +28010,7 @@
       </c>
       <c r="B59" s="28" t="inlineStr">
         <is>
-          <t>0.30%</t>
+          <t>0.75%</t>
         </is>
       </c>
       <c r="C59" s="28" t="inlineStr">
@@ -28083,7 +28083,7 @@
       </c>
       <c r="B60" s="24" t="inlineStr">
         <is>
-          <t>0.30%</t>
+          <t>0.75%</t>
         </is>
       </c>
       <c r="C60" s="24" t="inlineStr">
@@ -28156,7 +28156,7 @@
       </c>
       <c r="B61" s="28" t="inlineStr">
         <is>
-          <t>0.30%</t>
+          <t>0.75%</t>
         </is>
       </c>
       <c r="C61" s="28" t="inlineStr">
@@ -28229,7 +28229,7 @@
       </c>
       <c r="B62" s="24" t="inlineStr">
         <is>
-          <t>0.30%</t>
+          <t>0.75%</t>
         </is>
       </c>
       <c r="C62" s="24" t="inlineStr">
@@ -28302,7 +28302,7 @@
       </c>
       <c r="B63" s="28" t="inlineStr">
         <is>
-          <t>0.30%</t>
+          <t>0.75%</t>
         </is>
       </c>
       <c r="C63" s="28" t="inlineStr">
@@ -28375,7 +28375,7 @@
       </c>
       <c r="B64" s="24" t="inlineStr">
         <is>
-          <t>0.30%</t>
+          <t>0.75%</t>
         </is>
       </c>
       <c r="C64" s="24" t="inlineStr">
@@ -28450,7 +28450,7 @@
       </c>
       <c r="B65" s="28" t="inlineStr">
         <is>
-          <t>0.30%</t>
+          <t>0.75%</t>
         </is>
       </c>
       <c r="C65" s="28" t="inlineStr">
@@ -28523,7 +28523,7 @@
       </c>
       <c r="B66" s="24" t="inlineStr">
         <is>
-          <t>0.30%</t>
+          <t>0.75%</t>
         </is>
       </c>
       <c r="C66" s="24" t="inlineStr">
@@ -28598,7 +28598,7 @@
       </c>
       <c r="B67" s="28" t="inlineStr">
         <is>
-          <t>0.30%</t>
+          <t>0.75%</t>
         </is>
       </c>
       <c r="C67" s="28" t="inlineStr">
@@ -28671,7 +28671,7 @@
       </c>
       <c r="B68" s="24" t="inlineStr">
         <is>
-          <t>0.30%</t>
+          <t>0.75%</t>
         </is>
       </c>
       <c r="C68" s="24" t="inlineStr">
@@ -28744,7 +28744,7 @@
       </c>
       <c r="B69" s="28" t="inlineStr">
         <is>
-          <t>0.30%</t>
+          <t>0.75%</t>
         </is>
       </c>
       <c r="C69" s="28" t="inlineStr">
@@ -28817,7 +28817,7 @@
       </c>
       <c r="B70" s="24" t="inlineStr">
         <is>
-          <t>0.30%</t>
+          <t>0.75%</t>
         </is>
       </c>
       <c r="C70" s="24" t="inlineStr">
@@ -28890,7 +28890,7 @@
       </c>
       <c r="B71" s="28" t="inlineStr">
         <is>
-          <t>0.30%</t>
+          <t>0.75%</t>
         </is>
       </c>
       <c r="C71" s="28" t="inlineStr">
@@ -28965,7 +28965,7 @@
       </c>
       <c r="B72" s="24" t="inlineStr">
         <is>
-          <t>0.30%</t>
+          <t>0.75%</t>
         </is>
       </c>
       <c r="C72" s="24" t="inlineStr">
@@ -29040,7 +29040,7 @@
       </c>
       <c r="B73" s="28" t="inlineStr">
         <is>
-          <t>0.30%</t>
+          <t>0.75%</t>
         </is>
       </c>
       <c r="C73" s="28" t="inlineStr">
@@ -29113,7 +29113,7 @@
       </c>
       <c r="B74" s="24" t="inlineStr">
         <is>
-          <t>0.30%</t>
+          <t>0.75%</t>
         </is>
       </c>
       <c r="C74" s="24" t="inlineStr">
@@ -29186,7 +29186,7 @@
       </c>
       <c r="B75" s="28" t="inlineStr">
         <is>
-          <t>0.30%</t>
+          <t>0.75%</t>
         </is>
       </c>
       <c r="C75" s="28" t="inlineStr">
@@ -29259,7 +29259,7 @@
       </c>
       <c r="B76" s="24" t="inlineStr">
         <is>
-          <t>0.30%</t>
+          <t>0.75%</t>
         </is>
       </c>
       <c r="C76" s="24" t="inlineStr">
@@ -29332,7 +29332,7 @@
       </c>
       <c r="B77" s="28" t="inlineStr">
         <is>
-          <t>0.30%</t>
+          <t>0.75%</t>
         </is>
       </c>
       <c r="C77" s="28" t="inlineStr">
@@ -29405,7 +29405,7 @@
       </c>
       <c r="B78" s="24" t="inlineStr">
         <is>
-          <t>0.30%</t>
+          <t>0.75%</t>
         </is>
       </c>
       <c r="C78" s="24" t="inlineStr">
@@ -29478,7 +29478,7 @@
       </c>
       <c r="B79" s="28" t="inlineStr">
         <is>
-          <t>0.30%</t>
+          <t>0.75%</t>
         </is>
       </c>
       <c r="C79" s="28" t="inlineStr">
@@ -29551,7 +29551,7 @@
       </c>
       <c r="B80" s="24" t="inlineStr">
         <is>
-          <t>0.30%</t>
+          <t>0.75%</t>
         </is>
       </c>
       <c r="C80" s="24" t="inlineStr">
@@ -29626,7 +29626,7 @@
       </c>
       <c r="B81" s="28" t="inlineStr">
         <is>
-          <t>0.30%</t>
+          <t>0.75%</t>
         </is>
       </c>
       <c r="C81" s="28" t="inlineStr">
@@ -29699,7 +29699,7 @@
       </c>
       <c r="B82" s="24" t="inlineStr">
         <is>
-          <t>0.30%</t>
+          <t>0.75%</t>
         </is>
       </c>
       <c r="C82" s="24" t="inlineStr">
@@ -29772,7 +29772,7 @@
       </c>
       <c r="B83" s="28" t="inlineStr">
         <is>
-          <t>0.30%</t>
+          <t>0.75%</t>
         </is>
       </c>
       <c r="C83" s="28" t="inlineStr">
@@ -29845,7 +29845,7 @@
       </c>
       <c r="B84" s="24" t="inlineStr">
         <is>
-          <t>0.30%</t>
+          <t>0.75%</t>
         </is>
       </c>
       <c r="C84" s="24" t="inlineStr">
@@ -29918,7 +29918,7 @@
       </c>
       <c r="B85" s="28" t="inlineStr">
         <is>
-          <t>0.30%</t>
+          <t>0.75%</t>
         </is>
       </c>
       <c r="C85" s="28" t="inlineStr">
@@ -29991,7 +29991,7 @@
       </c>
       <c r="B86" s="24" t="inlineStr">
         <is>
-          <t>0.30%</t>
+          <t>0.75%</t>
         </is>
       </c>
       <c r="C86" s="24" t="inlineStr">
@@ -30066,7 +30066,7 @@
       </c>
       <c r="B87" s="28" t="inlineStr">
         <is>
-          <t>0.30%</t>
+          <t>0.75%</t>
         </is>
       </c>
       <c r="C87" s="28" t="inlineStr">
@@ -30139,7 +30139,7 @@
       </c>
       <c r="B88" s="24" t="inlineStr">
         <is>
-          <t>0.30%</t>
+          <t>0.75%</t>
         </is>
       </c>
       <c r="C88" s="24" t="inlineStr">
@@ -30212,7 +30212,7 @@
       </c>
       <c r="B89" s="28" t="inlineStr">
         <is>
-          <t>0.30%</t>
+          <t>0.75%</t>
         </is>
       </c>
       <c r="C89" s="28" t="inlineStr">
@@ -30287,7 +30287,7 @@
       </c>
       <c r="B90" s="24" t="inlineStr">
         <is>
-          <t>0.30%</t>
+          <t>0.75%</t>
         </is>
       </c>
       <c r="C90" s="24" t="inlineStr">
@@ -30360,7 +30360,7 @@
       </c>
       <c r="B91" s="28" t="inlineStr">
         <is>
-          <t>0.30%</t>
+          <t>0.75%</t>
         </is>
       </c>
       <c r="C91" s="28" t="inlineStr">
@@ -30433,7 +30433,7 @@
       </c>
       <c r="B92" s="24" t="inlineStr">
         <is>
-          <t>0.30%</t>
+          <t>0.75%</t>
         </is>
       </c>
       <c r="C92" s="24" t="inlineStr">
@@ -30506,7 +30506,7 @@
       </c>
       <c r="B93" s="28" t="inlineStr">
         <is>
-          <t>0.30%</t>
+          <t>0.75%</t>
         </is>
       </c>
       <c r="C93" s="28" t="inlineStr">
@@ -30579,7 +30579,7 @@
       </c>
       <c r="B94" s="24" t="inlineStr">
         <is>
-          <t>0.30%</t>
+          <t>0.75%</t>
         </is>
       </c>
       <c r="C94" s="24" t="inlineStr">
@@ -30652,7 +30652,7 @@
       </c>
       <c r="B95" s="28" t="inlineStr">
         <is>
-          <t>0.30%</t>
+          <t>0.75%</t>
         </is>
       </c>
       <c r="C95" s="28" t="inlineStr">
@@ -30725,7 +30725,7 @@
       </c>
       <c r="B96" s="24" t="inlineStr">
         <is>
-          <t>0.30%</t>
+          <t>0.75%</t>
         </is>
       </c>
       <c r="C96" s="24" t="inlineStr">
@@ -30798,7 +30798,7 @@
       </c>
       <c r="B97" s="28" t="inlineStr">
         <is>
-          <t>0.30%</t>
+          <t>0.75%</t>
         </is>
       </c>
       <c r="C97" s="28" t="inlineStr">
@@ -30871,7 +30871,7 @@
       </c>
       <c r="B98" s="24" t="inlineStr">
         <is>
-          <t>0.30%</t>
+          <t>0.75%</t>
         </is>
       </c>
       <c r="C98" s="24" t="inlineStr">
@@ -30944,7 +30944,7 @@
       </c>
       <c r="B99" s="28" t="inlineStr">
         <is>
-          <t>0.30%</t>
+          <t>0.75%</t>
         </is>
       </c>
       <c r="C99" s="28" t="inlineStr">
@@ -31017,7 +31017,7 @@
       </c>
       <c r="B100" s="24" t="inlineStr">
         <is>
-          <t>0.30%</t>
+          <t>0.75%</t>
         </is>
       </c>
       <c r="C100" s="24" t="inlineStr">
@@ -31090,7 +31090,7 @@
       </c>
       <c r="B101" s="28" t="inlineStr">
         <is>
-          <t>0.30%</t>
+          <t>0.75%</t>
         </is>
       </c>
       <c r="C101" s="28" t="inlineStr">
@@ -31165,7 +31165,7 @@
       </c>
       <c r="B102" s="24" t="inlineStr">
         <is>
-          <t>0.30%</t>
+          <t>0.75%</t>
         </is>
       </c>
       <c r="C102" s="24" t="inlineStr">
@@ -31238,7 +31238,7 @@
       </c>
       <c r="B103" s="28" t="inlineStr">
         <is>
-          <t>0.30%</t>
+          <t>0.75%</t>
         </is>
       </c>
       <c r="C103" s="28" t="inlineStr">
@@ -31311,7 +31311,7 @@
       </c>
       <c r="B104" s="24" t="inlineStr">
         <is>
-          <t>0.30%</t>
+          <t>0.75%</t>
         </is>
       </c>
       <c r="C104" s="24" t="inlineStr">
@@ -31384,7 +31384,7 @@
       </c>
       <c r="B105" s="32" t="inlineStr">
         <is>
-          <t>0.30%</t>
+          <t>0.75%</t>
         </is>
       </c>
       <c r="C105" s="32" t="inlineStr">

--- a/Output/holdings_snapshot.xlsx
+++ b/Output/holdings_snapshot.xlsx
@@ -682,7 +682,7 @@
     <row r="2" ht="22" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Long signal: Shareholder Yield + Gross Profitability + ROIC  |  Short signal: Net Ext. Financing + Leverage + F-Score + Gross Profitability  |  130% long top-100 / w_short = 130% × β_long/β_short (Vasicek-adj, 12m trailing)  |  Monthly rebalancing, ±5 pp sector neutrality, beta-neutral</t>
+          <t>Long signal: Shareholder Yield + Gross Profitability + ROIC  |  Short signal: Net Ext. Financing + Leverage + F-Score + Gross Profitability  |  175% long top-100 / w_short = 175% × β_long/β_short (Vasicek-adj, 12m trailing)  |  Monthly rebalancing, ±5% sector neutrality, beta-neutral</t>
         </is>
       </c>
     </row>
@@ -822,7 +822,7 @@
       </c>
       <c r="C6" s="16" t="inlineStr">
         <is>
-          <t>1.30%</t>
+          <t>1.75%</t>
         </is>
       </c>
       <c r="D6" s="16" t="inlineStr">
@@ -900,7 +900,7 @@
       </c>
       <c r="C7" s="20" t="inlineStr">
         <is>
-          <t>1.30%</t>
+          <t>1.75%</t>
         </is>
       </c>
       <c r="D7" s="20" t="inlineStr">
@@ -978,7 +978,7 @@
       </c>
       <c r="C8" s="16" t="inlineStr">
         <is>
-          <t>1.30%</t>
+          <t>1.75%</t>
         </is>
       </c>
       <c r="D8" s="16" t="inlineStr">
@@ -1056,7 +1056,7 @@
       </c>
       <c r="C9" s="20" t="inlineStr">
         <is>
-          <t>1.30%</t>
+          <t>1.75%</t>
         </is>
       </c>
       <c r="D9" s="20" t="inlineStr">
@@ -1134,7 +1134,7 @@
       </c>
       <c r="C10" s="16" t="inlineStr">
         <is>
-          <t>1.30%</t>
+          <t>1.75%</t>
         </is>
       </c>
       <c r="D10" s="16" t="inlineStr">
@@ -1212,7 +1212,7 @@
       </c>
       <c r="C11" s="20" t="inlineStr">
         <is>
-          <t>1.30%</t>
+          <t>1.75%</t>
         </is>
       </c>
       <c r="D11" s="20" t="inlineStr">
@@ -1290,7 +1290,7 @@
       </c>
       <c r="C12" s="16" t="inlineStr">
         <is>
-          <t>1.30%</t>
+          <t>1.75%</t>
         </is>
       </c>
       <c r="D12" s="16" t="inlineStr">
@@ -1368,7 +1368,7 @@
       </c>
       <c r="C13" s="20" t="inlineStr">
         <is>
-          <t>1.30%</t>
+          <t>1.75%</t>
         </is>
       </c>
       <c r="D13" s="20" t="inlineStr">
@@ -1446,7 +1446,7 @@
       </c>
       <c r="C14" s="16" t="inlineStr">
         <is>
-          <t>1.30%</t>
+          <t>1.75%</t>
         </is>
       </c>
       <c r="D14" s="16" t="inlineStr">
@@ -1524,7 +1524,7 @@
       </c>
       <c r="C15" s="20" t="inlineStr">
         <is>
-          <t>1.30%</t>
+          <t>1.75%</t>
         </is>
       </c>
       <c r="D15" s="20" t="inlineStr">
@@ -1602,7 +1602,7 @@
       </c>
       <c r="C16" s="16" t="inlineStr">
         <is>
-          <t>1.30%</t>
+          <t>1.75%</t>
         </is>
       </c>
       <c r="D16" s="16" t="inlineStr">
@@ -1680,7 +1680,7 @@
       </c>
       <c r="C17" s="20" t="inlineStr">
         <is>
-          <t>1.30%</t>
+          <t>1.75%</t>
         </is>
       </c>
       <c r="D17" s="20" t="inlineStr">
@@ -1758,7 +1758,7 @@
       </c>
       <c r="C18" s="16" t="inlineStr">
         <is>
-          <t>1.30%</t>
+          <t>1.75%</t>
         </is>
       </c>
       <c r="D18" s="16" t="inlineStr">
@@ -1836,7 +1836,7 @@
       </c>
       <c r="C19" s="20" t="inlineStr">
         <is>
-          <t>1.30%</t>
+          <t>1.75%</t>
         </is>
       </c>
       <c r="D19" s="20" t="inlineStr">
@@ -1914,7 +1914,7 @@
       </c>
       <c r="C20" s="16" t="inlineStr">
         <is>
-          <t>1.30%</t>
+          <t>1.75%</t>
         </is>
       </c>
       <c r="D20" s="16" t="inlineStr">
@@ -1992,7 +1992,7 @@
       </c>
       <c r="C21" s="20" t="inlineStr">
         <is>
-          <t>1.30%</t>
+          <t>1.75%</t>
         </is>
       </c>
       <c r="D21" s="20" t="inlineStr">
@@ -2070,7 +2070,7 @@
       </c>
       <c r="C22" s="16" t="inlineStr">
         <is>
-          <t>1.30%</t>
+          <t>1.75%</t>
         </is>
       </c>
       <c r="D22" s="16" t="inlineStr">
@@ -2148,7 +2148,7 @@
       </c>
       <c r="C23" s="20" t="inlineStr">
         <is>
-          <t>1.30%</t>
+          <t>1.75%</t>
         </is>
       </c>
       <c r="D23" s="20" t="inlineStr">
@@ -2226,7 +2226,7 @@
       </c>
       <c r="C24" s="16" t="inlineStr">
         <is>
-          <t>1.30%</t>
+          <t>1.75%</t>
         </is>
       </c>
       <c r="D24" s="16" t="inlineStr">
@@ -2304,7 +2304,7 @@
       </c>
       <c r="C25" s="20" t="inlineStr">
         <is>
-          <t>1.30%</t>
+          <t>1.75%</t>
         </is>
       </c>
       <c r="D25" s="20" t="inlineStr">
@@ -2382,7 +2382,7 @@
       </c>
       <c r="C26" s="16" t="inlineStr">
         <is>
-          <t>1.30%</t>
+          <t>1.75%</t>
         </is>
       </c>
       <c r="D26" s="16" t="inlineStr">
@@ -2460,7 +2460,7 @@
       </c>
       <c r="C27" s="20" t="inlineStr">
         <is>
-          <t>1.30%</t>
+          <t>1.75%</t>
         </is>
       </c>
       <c r="D27" s="20" t="inlineStr">
@@ -2538,7 +2538,7 @@
       </c>
       <c r="C28" s="16" t="inlineStr">
         <is>
-          <t>1.30%</t>
+          <t>1.75%</t>
         </is>
       </c>
       <c r="D28" s="16" t="inlineStr">
@@ -2616,7 +2616,7 @@
       </c>
       <c r="C29" s="20" t="inlineStr">
         <is>
-          <t>1.30%</t>
+          <t>1.75%</t>
         </is>
       </c>
       <c r="D29" s="20" t="inlineStr">
@@ -2694,7 +2694,7 @@
       </c>
       <c r="C30" s="16" t="inlineStr">
         <is>
-          <t>1.30%</t>
+          <t>1.75%</t>
         </is>
       </c>
       <c r="D30" s="16" t="inlineStr">
@@ -2772,7 +2772,7 @@
       </c>
       <c r="C31" s="20" t="inlineStr">
         <is>
-          <t>1.30%</t>
+          <t>1.75%</t>
         </is>
       </c>
       <c r="D31" s="20" t="inlineStr">
@@ -2850,7 +2850,7 @@
       </c>
       <c r="C32" s="16" t="inlineStr">
         <is>
-          <t>1.30%</t>
+          <t>1.75%</t>
         </is>
       </c>
       <c r="D32" s="16" t="inlineStr">
@@ -2928,7 +2928,7 @@
       </c>
       <c r="C33" s="20" t="inlineStr">
         <is>
-          <t>1.30%</t>
+          <t>1.75%</t>
         </is>
       </c>
       <c r="D33" s="20" t="inlineStr">
@@ -3006,7 +3006,7 @@
       </c>
       <c r="C34" s="16" t="inlineStr">
         <is>
-          <t>1.30%</t>
+          <t>1.75%</t>
         </is>
       </c>
       <c r="D34" s="16" t="inlineStr">
@@ -3084,7 +3084,7 @@
       </c>
       <c r="C35" s="20" t="inlineStr">
         <is>
-          <t>1.30%</t>
+          <t>1.75%</t>
         </is>
       </c>
       <c r="D35" s="20" t="inlineStr">
@@ -3162,7 +3162,7 @@
       </c>
       <c r="C36" s="16" t="inlineStr">
         <is>
-          <t>1.30%</t>
+          <t>1.75%</t>
         </is>
       </c>
       <c r="D36" s="16" t="inlineStr">
@@ -3240,7 +3240,7 @@
       </c>
       <c r="C37" s="20" t="inlineStr">
         <is>
-          <t>1.30%</t>
+          <t>1.75%</t>
         </is>
       </c>
       <c r="D37" s="20" t="inlineStr">
@@ -3318,7 +3318,7 @@
       </c>
       <c r="C38" s="16" t="inlineStr">
         <is>
-          <t>1.30%</t>
+          <t>1.75%</t>
         </is>
       </c>
       <c r="D38" s="16" t="inlineStr">
@@ -3396,7 +3396,7 @@
       </c>
       <c r="C39" s="20" t="inlineStr">
         <is>
-          <t>1.30%</t>
+          <t>1.75%</t>
         </is>
       </c>
       <c r="D39" s="20" t="inlineStr">
@@ -3474,7 +3474,7 @@
       </c>
       <c r="C40" s="16" t="inlineStr">
         <is>
-          <t>1.30%</t>
+          <t>1.75%</t>
         </is>
       </c>
       <c r="D40" s="16" t="inlineStr">
@@ -3552,7 +3552,7 @@
       </c>
       <c r="C41" s="20" t="inlineStr">
         <is>
-          <t>1.30%</t>
+          <t>1.75%</t>
         </is>
       </c>
       <c r="D41" s="20" t="inlineStr">
@@ -3630,7 +3630,7 @@
       </c>
       <c r="C42" s="16" t="inlineStr">
         <is>
-          <t>1.30%</t>
+          <t>1.75%</t>
         </is>
       </c>
       <c r="D42" s="16" t="inlineStr">
@@ -3708,7 +3708,7 @@
       </c>
       <c r="C43" s="20" t="inlineStr">
         <is>
-          <t>1.30%</t>
+          <t>1.75%</t>
         </is>
       </c>
       <c r="D43" s="20" t="inlineStr">
@@ -3786,7 +3786,7 @@
       </c>
       <c r="C44" s="16" t="inlineStr">
         <is>
-          <t>1.30%</t>
+          <t>1.75%</t>
         </is>
       </c>
       <c r="D44" s="16" t="inlineStr">
@@ -3864,7 +3864,7 @@
       </c>
       <c r="C45" s="20" t="inlineStr">
         <is>
-          <t>1.30%</t>
+          <t>1.75%</t>
         </is>
       </c>
       <c r="D45" s="20" t="inlineStr">
@@ -3942,7 +3942,7 @@
       </c>
       <c r="C46" s="16" t="inlineStr">
         <is>
-          <t>1.30%</t>
+          <t>1.75%</t>
         </is>
       </c>
       <c r="D46" s="16" t="inlineStr">
@@ -4020,7 +4020,7 @@
       </c>
       <c r="C47" s="20" t="inlineStr">
         <is>
-          <t>1.30%</t>
+          <t>1.75%</t>
         </is>
       </c>
       <c r="D47" s="20" t="inlineStr">
@@ -4098,7 +4098,7 @@
       </c>
       <c r="C48" s="16" t="inlineStr">
         <is>
-          <t>1.30%</t>
+          <t>1.75%</t>
         </is>
       </c>
       <c r="D48" s="16" t="inlineStr">
@@ -4176,7 +4176,7 @@
       </c>
       <c r="C49" s="20" t="inlineStr">
         <is>
-          <t>1.30%</t>
+          <t>1.75%</t>
         </is>
       </c>
       <c r="D49" s="20" t="inlineStr">
@@ -4254,7 +4254,7 @@
       </c>
       <c r="C50" s="16" t="inlineStr">
         <is>
-          <t>1.30%</t>
+          <t>1.75%</t>
         </is>
       </c>
       <c r="D50" s="16" t="inlineStr">
@@ -4332,7 +4332,7 @@
       </c>
       <c r="C51" s="20" t="inlineStr">
         <is>
-          <t>1.30%</t>
+          <t>1.75%</t>
         </is>
       </c>
       <c r="D51" s="20" t="inlineStr">
@@ -4410,7 +4410,7 @@
       </c>
       <c r="C52" s="16" t="inlineStr">
         <is>
-          <t>1.30%</t>
+          <t>1.75%</t>
         </is>
       </c>
       <c r="D52" s="16" t="inlineStr">
@@ -4488,7 +4488,7 @@
       </c>
       <c r="C53" s="20" t="inlineStr">
         <is>
-          <t>1.30%</t>
+          <t>1.75%</t>
         </is>
       </c>
       <c r="D53" s="20" t="inlineStr">
@@ -4566,7 +4566,7 @@
       </c>
       <c r="C54" s="16" t="inlineStr">
         <is>
-          <t>1.30%</t>
+          <t>1.75%</t>
         </is>
       </c>
       <c r="D54" s="16" t="inlineStr">
@@ -4644,7 +4644,7 @@
       </c>
       <c r="C55" s="20" t="inlineStr">
         <is>
-          <t>1.30%</t>
+          <t>1.75%</t>
         </is>
       </c>
       <c r="D55" s="20" t="inlineStr">
@@ -4724,7 +4724,7 @@
       </c>
       <c r="C56" s="16" t="inlineStr">
         <is>
-          <t>1.30%</t>
+          <t>1.75%</t>
         </is>
       </c>
       <c r="D56" s="16" t="inlineStr">
@@ -4802,7 +4802,7 @@
       </c>
       <c r="C57" s="20" t="inlineStr">
         <is>
-          <t>1.30%</t>
+          <t>1.75%</t>
         </is>
       </c>
       <c r="D57" s="20" t="inlineStr">
@@ -4880,7 +4880,7 @@
       </c>
       <c r="C58" s="16" t="inlineStr">
         <is>
-          <t>1.30%</t>
+          <t>1.75%</t>
         </is>
       </c>
       <c r="D58" s="16" t="inlineStr">
@@ -4958,7 +4958,7 @@
       </c>
       <c r="C59" s="20" t="inlineStr">
         <is>
-          <t>1.30%</t>
+          <t>1.75%</t>
         </is>
       </c>
       <c r="D59" s="20" t="inlineStr">
@@ -5036,7 +5036,7 @@
       </c>
       <c r="C60" s="16" t="inlineStr">
         <is>
-          <t>1.30%</t>
+          <t>1.75%</t>
         </is>
       </c>
       <c r="D60" s="16" t="inlineStr">
@@ -5114,7 +5114,7 @@
       </c>
       <c r="C61" s="20" t="inlineStr">
         <is>
-          <t>1.30%</t>
+          <t>1.75%</t>
         </is>
       </c>
       <c r="D61" s="20" t="inlineStr">
@@ -5192,7 +5192,7 @@
       </c>
       <c r="C62" s="16" t="inlineStr">
         <is>
-          <t>1.30%</t>
+          <t>1.75%</t>
         </is>
       </c>
       <c r="D62" s="16" t="inlineStr">
@@ -5272,7 +5272,7 @@
       </c>
       <c r="C63" s="20" t="inlineStr">
         <is>
-          <t>1.30%</t>
+          <t>1.75%</t>
         </is>
       </c>
       <c r="D63" s="20" t="inlineStr">
@@ -5350,7 +5350,7 @@
       </c>
       <c r="C64" s="16" t="inlineStr">
         <is>
-          <t>1.30%</t>
+          <t>1.75%</t>
         </is>
       </c>
       <c r="D64" s="16" t="inlineStr">
@@ -5428,7 +5428,7 @@
       </c>
       <c r="C65" s="20" t="inlineStr">
         <is>
-          <t>1.30%</t>
+          <t>1.75%</t>
         </is>
       </c>
       <c r="D65" s="20" t="inlineStr">
@@ -5508,7 +5508,7 @@
       </c>
       <c r="C66" s="16" t="inlineStr">
         <is>
-          <t>1.30%</t>
+          <t>1.75%</t>
         </is>
       </c>
       <c r="D66" s="16" t="inlineStr">
@@ -5586,7 +5586,7 @@
       </c>
       <c r="C67" s="20" t="inlineStr">
         <is>
-          <t>1.30%</t>
+          <t>1.75%</t>
         </is>
       </c>
       <c r="D67" s="20" t="inlineStr">
@@ -5666,7 +5666,7 @@
       </c>
       <c r="C68" s="16" t="inlineStr">
         <is>
-          <t>1.30%</t>
+          <t>1.75%</t>
         </is>
       </c>
       <c r="D68" s="16" t="inlineStr">
@@ -5746,7 +5746,7 @@
       </c>
       <c r="C69" s="20" t="inlineStr">
         <is>
-          <t>1.30%</t>
+          <t>1.75%</t>
         </is>
       </c>
       <c r="D69" s="20" t="inlineStr">
@@ -5824,7 +5824,7 @@
       </c>
       <c r="C70" s="16" t="inlineStr">
         <is>
-          <t>1.30%</t>
+          <t>1.75%</t>
         </is>
       </c>
       <c r="D70" s="16" t="inlineStr">
@@ -5902,7 +5902,7 @@
       </c>
       <c r="C71" s="20" t="inlineStr">
         <is>
-          <t>1.30%</t>
+          <t>1.75%</t>
         </is>
       </c>
       <c r="D71" s="20" t="inlineStr">
@@ -5980,7 +5980,7 @@
       </c>
       <c r="C72" s="16" t="inlineStr">
         <is>
-          <t>1.30%</t>
+          <t>1.75%</t>
         </is>
       </c>
       <c r="D72" s="16" t="inlineStr">
@@ -6058,7 +6058,7 @@
       </c>
       <c r="C73" s="20" t="inlineStr">
         <is>
-          <t>1.30%</t>
+          <t>1.75%</t>
         </is>
       </c>
       <c r="D73" s="20" t="inlineStr">
@@ -6136,7 +6136,7 @@
       </c>
       <c r="C74" s="16" t="inlineStr">
         <is>
-          <t>1.30%</t>
+          <t>1.75%</t>
         </is>
       </c>
       <c r="D74" s="16" t="inlineStr">
@@ -6214,7 +6214,7 @@
       </c>
       <c r="C75" s="20" t="inlineStr">
         <is>
-          <t>1.30%</t>
+          <t>1.75%</t>
         </is>
       </c>
       <c r="D75" s="20" t="inlineStr">
@@ -6292,7 +6292,7 @@
       </c>
       <c r="C76" s="16" t="inlineStr">
         <is>
-          <t>1.30%</t>
+          <t>1.75%</t>
         </is>
       </c>
       <c r="D76" s="16" t="inlineStr">
@@ -6370,7 +6370,7 @@
       </c>
       <c r="C77" s="20" t="inlineStr">
         <is>
-          <t>1.30%</t>
+          <t>1.75%</t>
         </is>
       </c>
       <c r="D77" s="20" t="inlineStr">
@@ -6448,7 +6448,7 @@
       </c>
       <c r="C78" s="16" t="inlineStr">
         <is>
-          <t>1.30%</t>
+          <t>1.75%</t>
         </is>
       </c>
       <c r="D78" s="16" t="inlineStr">
@@ -6526,7 +6526,7 @@
       </c>
       <c r="C79" s="20" t="inlineStr">
         <is>
-          <t>1.30%</t>
+          <t>1.75%</t>
         </is>
       </c>
       <c r="D79" s="20" t="inlineStr">
@@ -6604,7 +6604,7 @@
       </c>
       <c r="C80" s="16" t="inlineStr">
         <is>
-          <t>1.30%</t>
+          <t>1.75%</t>
         </is>
       </c>
       <c r="D80" s="16" t="inlineStr">
@@ -6682,7 +6682,7 @@
       </c>
       <c r="C81" s="20" t="inlineStr">
         <is>
-          <t>1.30%</t>
+          <t>1.75%</t>
         </is>
       </c>
       <c r="D81" s="20" t="inlineStr">
@@ -6760,7 +6760,7 @@
       </c>
       <c r="C82" s="16" t="inlineStr">
         <is>
-          <t>1.30%</t>
+          <t>1.75%</t>
         </is>
       </c>
       <c r="D82" s="16" t="inlineStr">
@@ -6840,7 +6840,7 @@
       </c>
       <c r="C83" s="20" t="inlineStr">
         <is>
-          <t>1.30%</t>
+          <t>1.75%</t>
         </is>
       </c>
       <c r="D83" s="20" t="inlineStr">
@@ -6918,7 +6918,7 @@
       </c>
       <c r="C84" s="16" t="inlineStr">
         <is>
-          <t>1.30%</t>
+          <t>1.75%</t>
         </is>
       </c>
       <c r="D84" s="16" t="inlineStr">
@@ -6996,7 +6996,7 @@
       </c>
       <c r="C85" s="20" t="inlineStr">
         <is>
-          <t>1.30%</t>
+          <t>1.75%</t>
         </is>
       </c>
       <c r="D85" s="20" t="inlineStr">
@@ -7074,7 +7074,7 @@
       </c>
       <c r="C86" s="16" t="inlineStr">
         <is>
-          <t>1.30%</t>
+          <t>1.75%</t>
         </is>
       </c>
       <c r="D86" s="16" t="inlineStr">
@@ -7152,7 +7152,7 @@
       </c>
       <c r="C87" s="20" t="inlineStr">
         <is>
-          <t>1.30%</t>
+          <t>1.75%</t>
         </is>
       </c>
       <c r="D87" s="20" t="inlineStr">
@@ -7232,7 +7232,7 @@
       </c>
       <c r="C88" s="16" t="inlineStr">
         <is>
-          <t>1.30%</t>
+          <t>1.75%</t>
         </is>
       </c>
       <c r="D88" s="16" t="inlineStr">
@@ -7310,7 +7310,7 @@
       </c>
       <c r="C89" s="20" t="inlineStr">
         <is>
-          <t>1.30%</t>
+          <t>1.75%</t>
         </is>
       </c>
       <c r="D89" s="20" t="inlineStr">
@@ -7388,7 +7388,7 @@
       </c>
       <c r="C90" s="16" t="inlineStr">
         <is>
-          <t>1.30%</t>
+          <t>1.75%</t>
         </is>
       </c>
       <c r="D90" s="16" t="inlineStr">
@@ -7466,7 +7466,7 @@
       </c>
       <c r="C91" s="20" t="inlineStr">
         <is>
-          <t>1.30%</t>
+          <t>1.75%</t>
         </is>
       </c>
       <c r="D91" s="20" t="inlineStr">
@@ -7544,7 +7544,7 @@
       </c>
       <c r="C92" s="16" t="inlineStr">
         <is>
-          <t>1.30%</t>
+          <t>1.75%</t>
         </is>
       </c>
       <c r="D92" s="16" t="inlineStr">
@@ -7622,7 +7622,7 @@
       </c>
       <c r="C93" s="20" t="inlineStr">
         <is>
-          <t>1.30%</t>
+          <t>1.75%</t>
         </is>
       </c>
       <c r="D93" s="20" t="inlineStr">
@@ -7702,7 +7702,7 @@
       </c>
       <c r="C94" s="16" t="inlineStr">
         <is>
-          <t>1.30%</t>
+          <t>1.75%</t>
         </is>
       </c>
       <c r="D94" s="16" t="inlineStr">
@@ -7780,7 +7780,7 @@
       </c>
       <c r="C95" s="20" t="inlineStr">
         <is>
-          <t>1.30%</t>
+          <t>1.75%</t>
         </is>
       </c>
       <c r="D95" s="20" t="inlineStr">
@@ -7858,7 +7858,7 @@
       </c>
       <c r="C96" s="16" t="inlineStr">
         <is>
-          <t>1.30%</t>
+          <t>1.75%</t>
         </is>
       </c>
       <c r="D96" s="16" t="inlineStr">
@@ -7936,7 +7936,7 @@
       </c>
       <c r="C97" s="20" t="inlineStr">
         <is>
-          <t>1.30%</t>
+          <t>1.75%</t>
         </is>
       </c>
       <c r="D97" s="20" t="inlineStr">
@@ -8014,7 +8014,7 @@
       </c>
       <c r="C98" s="16" t="inlineStr">
         <is>
-          <t>1.30%</t>
+          <t>1.75%</t>
         </is>
       </c>
       <c r="D98" s="16" t="inlineStr">
@@ -8092,7 +8092,7 @@
       </c>
       <c r="C99" s="20" t="inlineStr">
         <is>
-          <t>1.30%</t>
+          <t>1.75%</t>
         </is>
       </c>
       <c r="D99" s="20" t="inlineStr">
@@ -8170,7 +8170,7 @@
       </c>
       <c r="C100" s="16" t="inlineStr">
         <is>
-          <t>1.30%</t>
+          <t>1.75%</t>
         </is>
       </c>
       <c r="D100" s="16" t="inlineStr">
@@ -8248,7 +8248,7 @@
       </c>
       <c r="C101" s="20" t="inlineStr">
         <is>
-          <t>1.30%</t>
+          <t>1.75%</t>
         </is>
       </c>
       <c r="D101" s="20" t="inlineStr">
@@ -8326,7 +8326,7 @@
       </c>
       <c r="C102" s="16" t="inlineStr">
         <is>
-          <t>1.30%</t>
+          <t>1.75%</t>
         </is>
       </c>
       <c r="D102" s="16" t="inlineStr">
@@ -8404,7 +8404,7 @@
       </c>
       <c r="C103" s="20" t="inlineStr">
         <is>
-          <t>1.30%</t>
+          <t>1.75%</t>
         </is>
       </c>
       <c r="D103" s="20" t="inlineStr">
@@ -8482,7 +8482,7 @@
       </c>
       <c r="C104" s="16" t="inlineStr">
         <is>
-          <t>1.30%</t>
+          <t>1.75%</t>
         </is>
       </c>
       <c r="D104" s="16" t="inlineStr">
@@ -8560,7 +8560,7 @@
       </c>
       <c r="C105" s="20" t="inlineStr">
         <is>
-          <t>1.30%</t>
+          <t>1.75%</t>
         </is>
       </c>
       <c r="D105" s="20" t="inlineStr">
@@ -8638,7 +8638,7 @@
       </c>
       <c r="C106" s="24" t="inlineStr">
         <is>
-          <t>0.30%</t>
+          <t>0.75%</t>
         </is>
       </c>
       <c r="D106" s="24" t="inlineStr">
@@ -8716,7 +8716,7 @@
       </c>
       <c r="C107" s="28" t="inlineStr">
         <is>
-          <t>0.30%</t>
+          <t>0.75%</t>
         </is>
       </c>
       <c r="D107" s="28" t="inlineStr">
@@ -8794,7 +8794,7 @@
       </c>
       <c r="C108" s="24" t="inlineStr">
         <is>
-          <t>0.30%</t>
+          <t>0.75%</t>
         </is>
       </c>
       <c r="D108" s="24" t="inlineStr">
@@ -8872,7 +8872,7 @@
       </c>
       <c r="C109" s="28" t="inlineStr">
         <is>
-          <t>0.30%</t>
+          <t>0.75%</t>
         </is>
       </c>
       <c r="D109" s="28" t="inlineStr">
@@ -8950,7 +8950,7 @@
       </c>
       <c r="C110" s="24" t="inlineStr">
         <is>
-          <t>0.30%</t>
+          <t>0.75%</t>
         </is>
       </c>
       <c r="D110" s="24" t="inlineStr">
@@ -9028,7 +9028,7 @@
       </c>
       <c r="C111" s="28" t="inlineStr">
         <is>
-          <t>0.30%</t>
+          <t>0.75%</t>
         </is>
       </c>
       <c r="D111" s="28" t="inlineStr">
@@ -9108,7 +9108,7 @@
       </c>
       <c r="C112" s="24" t="inlineStr">
         <is>
-          <t>0.30%</t>
+          <t>0.75%</t>
         </is>
       </c>
       <c r="D112" s="24" t="inlineStr">
@@ -9188,7 +9188,7 @@
       </c>
       <c r="C113" s="28" t="inlineStr">
         <is>
-          <t>0.30%</t>
+          <t>0.75%</t>
         </is>
       </c>
       <c r="D113" s="28" t="inlineStr">
@@ -9266,7 +9266,7 @@
       </c>
       <c r="C114" s="24" t="inlineStr">
         <is>
-          <t>0.30%</t>
+          <t>0.75%</t>
         </is>
       </c>
       <c r="D114" s="24" t="inlineStr">
@@ -9344,7 +9344,7 @@
       </c>
       <c r="C115" s="28" t="inlineStr">
         <is>
-          <t>0.30%</t>
+          <t>0.75%</t>
         </is>
       </c>
       <c r="D115" s="28" t="inlineStr">
@@ -9422,7 +9422,7 @@
       </c>
       <c r="C116" s="24" t="inlineStr">
         <is>
-          <t>0.30%</t>
+          <t>0.75%</t>
         </is>
       </c>
       <c r="D116" s="24" t="inlineStr">
@@ -9500,7 +9500,7 @@
       </c>
       <c r="C117" s="28" t="inlineStr">
         <is>
-          <t>0.30%</t>
+          <t>0.75%</t>
         </is>
       </c>
       <c r="D117" s="28" t="inlineStr">
@@ -9578,7 +9578,7 @@
       </c>
       <c r="C118" s="24" t="inlineStr">
         <is>
-          <t>0.30%</t>
+          <t>0.75%</t>
         </is>
       </c>
       <c r="D118" s="24" t="inlineStr">
@@ -9658,7 +9658,7 @@
       </c>
       <c r="C119" s="28" t="inlineStr">
         <is>
-          <t>0.30%</t>
+          <t>0.75%</t>
         </is>
       </c>
       <c r="D119" s="28" t="inlineStr">
@@ -9736,7 +9736,7 @@
       </c>
       <c r="C120" s="24" t="inlineStr">
         <is>
-          <t>0.30%</t>
+          <t>0.75%</t>
         </is>
       </c>
       <c r="D120" s="24" t="inlineStr">
@@ -9814,7 +9814,7 @@
       </c>
       <c r="C121" s="28" t="inlineStr">
         <is>
-          <t>0.30%</t>
+          <t>0.75%</t>
         </is>
       </c>
       <c r="D121" s="28" t="inlineStr">
@@ -9892,7 +9892,7 @@
       </c>
       <c r="C122" s="24" t="inlineStr">
         <is>
-          <t>0.30%</t>
+          <t>0.75%</t>
         </is>
       </c>
       <c r="D122" s="24" t="inlineStr">
@@ -9970,7 +9970,7 @@
       </c>
       <c r="C123" s="28" t="inlineStr">
         <is>
-          <t>0.30%</t>
+          <t>0.75%</t>
         </is>
       </c>
       <c r="D123" s="28" t="inlineStr">
@@ -10048,7 +10048,7 @@
       </c>
       <c r="C124" s="24" t="inlineStr">
         <is>
-          <t>0.30%</t>
+          <t>0.75%</t>
         </is>
       </c>
       <c r="D124" s="24" t="inlineStr">
@@ -10126,7 +10126,7 @@
       </c>
       <c r="C125" s="28" t="inlineStr">
         <is>
-          <t>0.30%</t>
+          <t>0.75%</t>
         </is>
       </c>
       <c r="D125" s="28" t="inlineStr">
@@ -10206,7 +10206,7 @@
       </c>
       <c r="C126" s="24" t="inlineStr">
         <is>
-          <t>0.30%</t>
+          <t>0.75%</t>
         </is>
       </c>
       <c r="D126" s="24" t="inlineStr">
@@ -10284,7 +10284,7 @@
       </c>
       <c r="C127" s="28" t="inlineStr">
         <is>
-          <t>0.30%</t>
+          <t>0.75%</t>
         </is>
       </c>
       <c r="D127" s="28" t="inlineStr">
@@ -10362,7 +10362,7 @@
       </c>
       <c r="C128" s="24" t="inlineStr">
         <is>
-          <t>0.30%</t>
+          <t>0.75%</t>
         </is>
       </c>
       <c r="D128" s="24" t="inlineStr">
@@ -10442,7 +10442,7 @@
       </c>
       <c r="C129" s="28" t="inlineStr">
         <is>
-          <t>0.30%</t>
+          <t>0.75%</t>
         </is>
       </c>
       <c r="D129" s="28" t="inlineStr">
@@ -10520,7 +10520,7 @@
       </c>
       <c r="C130" s="24" t="inlineStr">
         <is>
-          <t>0.30%</t>
+          <t>0.75%</t>
         </is>
       </c>
       <c r="D130" s="24" t="inlineStr">
@@ -10598,7 +10598,7 @@
       </c>
       <c r="C131" s="28" t="inlineStr">
         <is>
-          <t>0.30%</t>
+          <t>0.75%</t>
         </is>
       </c>
       <c r="D131" s="28" t="inlineStr">
@@ -10676,7 +10676,7 @@
       </c>
       <c r="C132" s="24" t="inlineStr">
         <is>
-          <t>0.30%</t>
+          <t>0.75%</t>
         </is>
       </c>
       <c r="D132" s="24" t="inlineStr">
@@ -10754,7 +10754,7 @@
       </c>
       <c r="C133" s="28" t="inlineStr">
         <is>
-          <t>0.30%</t>
+          <t>0.75%</t>
         </is>
       </c>
       <c r="D133" s="28" t="inlineStr">
@@ -10834,7 +10834,7 @@
       </c>
       <c r="C134" s="24" t="inlineStr">
         <is>
-          <t>0.30%</t>
+          <t>0.75%</t>
         </is>
       </c>
       <c r="D134" s="24" t="inlineStr">
@@ -10912,7 +10912,7 @@
       </c>
       <c r="C135" s="28" t="inlineStr">
         <is>
-          <t>0.30%</t>
+          <t>0.75%</t>
         </is>
       </c>
       <c r="D135" s="28" t="inlineStr">
@@ -10990,7 +10990,7 @@
       </c>
       <c r="C136" s="24" t="inlineStr">
         <is>
-          <t>0.30%</t>
+          <t>0.75%</t>
         </is>
       </c>
       <c r="D136" s="24" t="inlineStr">
@@ -11068,7 +11068,7 @@
       </c>
       <c r="C137" s="28" t="inlineStr">
         <is>
-          <t>0.30%</t>
+          <t>0.75%</t>
         </is>
       </c>
       <c r="D137" s="28" t="inlineStr">
@@ -11146,7 +11146,7 @@
       </c>
       <c r="C138" s="24" t="inlineStr">
         <is>
-          <t>0.30%</t>
+          <t>0.75%</t>
         </is>
       </c>
       <c r="D138" s="24" t="inlineStr">
@@ -11224,7 +11224,7 @@
       </c>
       <c r="C139" s="28" t="inlineStr">
         <is>
-          <t>0.30%</t>
+          <t>0.75%</t>
         </is>
       </c>
       <c r="D139" s="28" t="inlineStr">
@@ -11302,7 +11302,7 @@
       </c>
       <c r="C140" s="24" t="inlineStr">
         <is>
-          <t>0.30%</t>
+          <t>0.75%</t>
         </is>
       </c>
       <c r="D140" s="24" t="inlineStr">
@@ -11380,7 +11380,7 @@
       </c>
       <c r="C141" s="28" t="inlineStr">
         <is>
-          <t>0.30%</t>
+          <t>0.75%</t>
         </is>
       </c>
       <c r="D141" s="28" t="inlineStr">
@@ -11458,7 +11458,7 @@
       </c>
       <c r="C142" s="24" t="inlineStr">
         <is>
-          <t>0.30%</t>
+          <t>0.75%</t>
         </is>
       </c>
       <c r="D142" s="24" t="inlineStr">
@@ -11538,7 +11538,7 @@
       </c>
       <c r="C143" s="28" t="inlineStr">
         <is>
-          <t>0.30%</t>
+          <t>0.75%</t>
         </is>
       </c>
       <c r="D143" s="28" t="inlineStr">
@@ -11616,7 +11616,7 @@
       </c>
       <c r="C144" s="24" t="inlineStr">
         <is>
-          <t>0.30%</t>
+          <t>0.75%</t>
         </is>
       </c>
       <c r="D144" s="24" t="inlineStr">
@@ -11694,7 +11694,7 @@
       </c>
       <c r="C145" s="28" t="inlineStr">
         <is>
-          <t>0.30%</t>
+          <t>0.75%</t>
         </is>
       </c>
       <c r="D145" s="28" t="inlineStr">
@@ -11772,7 +11772,7 @@
       </c>
       <c r="C146" s="24" t="inlineStr">
         <is>
-          <t>0.30%</t>
+          <t>0.75%</t>
         </is>
       </c>
       <c r="D146" s="24" t="inlineStr">
@@ -11850,7 +11850,7 @@
       </c>
       <c r="C147" s="28" t="inlineStr">
         <is>
-          <t>0.30%</t>
+          <t>0.75%</t>
         </is>
       </c>
       <c r="D147" s="28" t="inlineStr">
@@ -11928,7 +11928,7 @@
       </c>
       <c r="C148" s="24" t="inlineStr">
         <is>
-          <t>0.30%</t>
+          <t>0.75%</t>
         </is>
       </c>
       <c r="D148" s="24" t="inlineStr">
@@ -12006,7 +12006,7 @@
       </c>
       <c r="C149" s="28" t="inlineStr">
         <is>
-          <t>0.30%</t>
+          <t>0.75%</t>
         </is>
       </c>
       <c r="D149" s="28" t="inlineStr">
@@ -12084,7 +12084,7 @@
       </c>
       <c r="C150" s="24" t="inlineStr">
         <is>
-          <t>0.30%</t>
+          <t>0.75%</t>
         </is>
       </c>
       <c r="D150" s="24" t="inlineStr">
@@ -12162,7 +12162,7 @@
       </c>
       <c r="C151" s="28" t="inlineStr">
         <is>
-          <t>0.30%</t>
+          <t>0.75%</t>
         </is>
       </c>
       <c r="D151" s="28" t="inlineStr">
@@ -12242,7 +12242,7 @@
       </c>
       <c r="C152" s="24" t="inlineStr">
         <is>
-          <t>0.30%</t>
+          <t>0.75%</t>
         </is>
       </c>
       <c r="D152" s="24" t="inlineStr">
@@ -12322,7 +12322,7 @@
       </c>
       <c r="C153" s="28" t="inlineStr">
         <is>
-          <t>0.30%</t>
+          <t>0.75%</t>
         </is>
       </c>
       <c r="D153" s="28" t="inlineStr">
@@ -12400,7 +12400,7 @@
       </c>
       <c r="C154" s="24" t="inlineStr">
         <is>
-          <t>0.30%</t>
+          <t>0.75%</t>
         </is>
       </c>
       <c r="D154" s="24" t="inlineStr">
@@ -12478,7 +12478,7 @@
       </c>
       <c r="C155" s="28" t="inlineStr">
         <is>
-          <t>0.30%</t>
+          <t>0.75%</t>
         </is>
       </c>
       <c r="D155" s="28" t="inlineStr">
@@ -12556,7 +12556,7 @@
       </c>
       <c r="C156" s="24" t="inlineStr">
         <is>
-          <t>0.30%</t>
+          <t>0.75%</t>
         </is>
       </c>
       <c r="D156" s="24" t="inlineStr">
@@ -12636,7 +12636,7 @@
       </c>
       <c r="C157" s="28" t="inlineStr">
         <is>
-          <t>0.30%</t>
+          <t>0.75%</t>
         </is>
       </c>
       <c r="D157" s="28" t="inlineStr">
@@ -12714,7 +12714,7 @@
       </c>
       <c r="C158" s="24" t="inlineStr">
         <is>
-          <t>0.30%</t>
+          <t>0.75%</t>
         </is>
       </c>
       <c r="D158" s="24" t="inlineStr">
@@ -12792,7 +12792,7 @@
       </c>
       <c r="C159" s="28" t="inlineStr">
         <is>
-          <t>0.30%</t>
+          <t>0.75%</t>
         </is>
       </c>
       <c r="D159" s="28" t="inlineStr">
@@ -12870,7 +12870,7 @@
       </c>
       <c r="C160" s="24" t="inlineStr">
         <is>
-          <t>0.30%</t>
+          <t>0.75%</t>
         </is>
       </c>
       <c r="D160" s="24" t="inlineStr">
@@ -12948,7 +12948,7 @@
       </c>
       <c r="C161" s="28" t="inlineStr">
         <is>
-          <t>0.30%</t>
+          <t>0.75%</t>
         </is>
       </c>
       <c r="D161" s="28" t="inlineStr">
@@ -13028,7 +13028,7 @@
       </c>
       <c r="C162" s="24" t="inlineStr">
         <is>
-          <t>0.30%</t>
+          <t>0.75%</t>
         </is>
       </c>
       <c r="D162" s="24" t="inlineStr">
@@ -13106,7 +13106,7 @@
       </c>
       <c r="C163" s="28" t="inlineStr">
         <is>
-          <t>0.30%</t>
+          <t>0.75%</t>
         </is>
       </c>
       <c r="D163" s="28" t="inlineStr">
@@ -13184,7 +13184,7 @@
       </c>
       <c r="C164" s="24" t="inlineStr">
         <is>
-          <t>0.30%</t>
+          <t>0.75%</t>
         </is>
       </c>
       <c r="D164" s="24" t="inlineStr">
@@ -13262,7 +13262,7 @@
       </c>
       <c r="C165" s="28" t="inlineStr">
         <is>
-          <t>0.30%</t>
+          <t>0.75%</t>
         </is>
       </c>
       <c r="D165" s="28" t="inlineStr">
@@ -13340,7 +13340,7 @@
       </c>
       <c r="C166" s="24" t="inlineStr">
         <is>
-          <t>0.30%</t>
+          <t>0.75%</t>
         </is>
       </c>
       <c r="D166" s="24" t="inlineStr">
@@ -13418,7 +13418,7 @@
       </c>
       <c r="C167" s="28" t="inlineStr">
         <is>
-          <t>0.30%</t>
+          <t>0.75%</t>
         </is>
       </c>
       <c r="D167" s="28" t="inlineStr">
@@ -13496,7 +13496,7 @@
       </c>
       <c r="C168" s="24" t="inlineStr">
         <is>
-          <t>0.30%</t>
+          <t>0.75%</t>
         </is>
       </c>
       <c r="D168" s="24" t="inlineStr">
@@ -13574,7 +13574,7 @@
       </c>
       <c r="C169" s="28" t="inlineStr">
         <is>
-          <t>0.30%</t>
+          <t>0.75%</t>
         </is>
       </c>
       <c r="D169" s="28" t="inlineStr">
@@ -13652,7 +13652,7 @@
       </c>
       <c r="C170" s="24" t="inlineStr">
         <is>
-          <t>0.30%</t>
+          <t>0.75%</t>
         </is>
       </c>
       <c r="D170" s="24" t="inlineStr">
@@ -13730,7 +13730,7 @@
       </c>
       <c r="C171" s="28" t="inlineStr">
         <is>
-          <t>0.30%</t>
+          <t>0.75%</t>
         </is>
       </c>
       <c r="D171" s="28" t="inlineStr">
@@ -13808,7 +13808,7 @@
       </c>
       <c r="C172" s="24" t="inlineStr">
         <is>
-          <t>0.30%</t>
+          <t>0.75%</t>
         </is>
       </c>
       <c r="D172" s="24" t="inlineStr">
@@ -13886,7 +13886,7 @@
       </c>
       <c r="C173" s="28" t="inlineStr">
         <is>
-          <t>0.30%</t>
+          <t>0.75%</t>
         </is>
       </c>
       <c r="D173" s="28" t="inlineStr">
@@ -13964,7 +13964,7 @@
       </c>
       <c r="C174" s="24" t="inlineStr">
         <is>
-          <t>0.30%</t>
+          <t>0.75%</t>
         </is>
       </c>
       <c r="D174" s="24" t="inlineStr">
@@ -14042,7 +14042,7 @@
       </c>
       <c r="C175" s="28" t="inlineStr">
         <is>
-          <t>0.30%</t>
+          <t>0.75%</t>
         </is>
       </c>
       <c r="D175" s="28" t="inlineStr">
@@ -14120,7 +14120,7 @@
       </c>
       <c r="C176" s="24" t="inlineStr">
         <is>
-          <t>0.30%</t>
+          <t>0.75%</t>
         </is>
       </c>
       <c r="D176" s="24" t="inlineStr">
@@ -14198,7 +14198,7 @@
       </c>
       <c r="C177" s="28" t="inlineStr">
         <is>
-          <t>0.30%</t>
+          <t>0.75%</t>
         </is>
       </c>
       <c r="D177" s="28" t="inlineStr">
@@ -14278,7 +14278,7 @@
       </c>
       <c r="C178" s="24" t="inlineStr">
         <is>
-          <t>0.30%</t>
+          <t>0.75%</t>
         </is>
       </c>
       <c r="D178" s="24" t="inlineStr">
@@ -14356,7 +14356,7 @@
       </c>
       <c r="C179" s="28" t="inlineStr">
         <is>
-          <t>0.30%</t>
+          <t>0.75%</t>
         </is>
       </c>
       <c r="D179" s="28" t="inlineStr">
@@ -14434,7 +14434,7 @@
       </c>
       <c r="C180" s="24" t="inlineStr">
         <is>
-          <t>0.30%</t>
+          <t>0.75%</t>
         </is>
       </c>
       <c r="D180" s="24" t="inlineStr">
@@ -14512,7 +14512,7 @@
       </c>
       <c r="C181" s="28" t="inlineStr">
         <is>
-          <t>0.30%</t>
+          <t>0.75%</t>
         </is>
       </c>
       <c r="D181" s="28" t="inlineStr">
@@ -14590,7 +14590,7 @@
       </c>
       <c r="C182" s="24" t="inlineStr">
         <is>
-          <t>0.30%</t>
+          <t>0.75%</t>
         </is>
       </c>
       <c r="D182" s="24" t="inlineStr">
@@ -14668,7 +14668,7 @@
       </c>
       <c r="C183" s="28" t="inlineStr">
         <is>
-          <t>0.30%</t>
+          <t>0.75%</t>
         </is>
       </c>
       <c r="D183" s="28" t="inlineStr">
@@ -14746,7 +14746,7 @@
       </c>
       <c r="C184" s="24" t="inlineStr">
         <is>
-          <t>0.30%</t>
+          <t>0.75%</t>
         </is>
       </c>
       <c r="D184" s="24" t="inlineStr">
@@ -14824,7 +14824,7 @@
       </c>
       <c r="C185" s="28" t="inlineStr">
         <is>
-          <t>0.30%</t>
+          <t>0.75%</t>
         </is>
       </c>
       <c r="D185" s="28" t="inlineStr">
@@ -14902,7 +14902,7 @@
       </c>
       <c r="C186" s="24" t="inlineStr">
         <is>
-          <t>0.30%</t>
+          <t>0.75%</t>
         </is>
       </c>
       <c r="D186" s="24" t="inlineStr">
@@ -14980,7 +14980,7 @@
       </c>
       <c r="C187" s="28" t="inlineStr">
         <is>
-          <t>0.30%</t>
+          <t>0.75%</t>
         </is>
       </c>
       <c r="D187" s="28" t="inlineStr">
@@ -15058,7 +15058,7 @@
       </c>
       <c r="C188" s="24" t="inlineStr">
         <is>
-          <t>0.30%</t>
+          <t>0.75%</t>
         </is>
       </c>
       <c r="D188" s="24" t="inlineStr">
@@ -15136,7 +15136,7 @@
       </c>
       <c r="C189" s="28" t="inlineStr">
         <is>
-          <t>0.30%</t>
+          <t>0.75%</t>
         </is>
       </c>
       <c r="D189" s="28" t="inlineStr">
@@ -15214,7 +15214,7 @@
       </c>
       <c r="C190" s="24" t="inlineStr">
         <is>
-          <t>0.30%</t>
+          <t>0.75%</t>
         </is>
       </c>
       <c r="D190" s="24" t="inlineStr">
@@ -15292,7 +15292,7 @@
       </c>
       <c r="C191" s="28" t="inlineStr">
         <is>
-          <t>0.30%</t>
+          <t>0.75%</t>
         </is>
       </c>
       <c r="D191" s="28" t="inlineStr">
@@ -15370,7 +15370,7 @@
       </c>
       <c r="C192" s="24" t="inlineStr">
         <is>
-          <t>0.30%</t>
+          <t>0.75%</t>
         </is>
       </c>
       <c r="D192" s="24" t="inlineStr">
@@ -15448,7 +15448,7 @@
       </c>
       <c r="C193" s="28" t="inlineStr">
         <is>
-          <t>0.30%</t>
+          <t>0.75%</t>
         </is>
       </c>
       <c r="D193" s="28" t="inlineStr">
@@ -15526,7 +15526,7 @@
       </c>
       <c r="C194" s="24" t="inlineStr">
         <is>
-          <t>0.30%</t>
+          <t>0.75%</t>
         </is>
       </c>
       <c r="D194" s="24" t="inlineStr">
@@ -15604,7 +15604,7 @@
       </c>
       <c r="C195" s="28" t="inlineStr">
         <is>
-          <t>0.30%</t>
+          <t>0.75%</t>
         </is>
       </c>
       <c r="D195" s="28" t="inlineStr">
@@ -15682,7 +15682,7 @@
       </c>
       <c r="C196" s="24" t="inlineStr">
         <is>
-          <t>0.30%</t>
+          <t>0.75%</t>
         </is>
       </c>
       <c r="D196" s="24" t="inlineStr">
@@ -15760,7 +15760,7 @@
       </c>
       <c r="C197" s="28" t="inlineStr">
         <is>
-          <t>0.30%</t>
+          <t>0.75%</t>
         </is>
       </c>
       <c r="D197" s="28" t="inlineStr">
@@ -15838,7 +15838,7 @@
       </c>
       <c r="C198" s="24" t="inlineStr">
         <is>
-          <t>0.30%</t>
+          <t>0.75%</t>
         </is>
       </c>
       <c r="D198" s="24" t="inlineStr">
@@ -15916,7 +15916,7 @@
       </c>
       <c r="C199" s="28" t="inlineStr">
         <is>
-          <t>0.30%</t>
+          <t>0.75%</t>
         </is>
       </c>
       <c r="D199" s="28" t="inlineStr">
@@ -15996,7 +15996,7 @@
       </c>
       <c r="C200" s="24" t="inlineStr">
         <is>
-          <t>0.30%</t>
+          <t>0.75%</t>
         </is>
       </c>
       <c r="D200" s="24" t="inlineStr">
@@ -16076,7 +16076,7 @@
       </c>
       <c r="C201" s="28" t="inlineStr">
         <is>
-          <t>0.30%</t>
+          <t>0.75%</t>
         </is>
       </c>
       <c r="D201" s="28" t="inlineStr">
@@ -16154,7 +16154,7 @@
       </c>
       <c r="C202" s="24" t="inlineStr">
         <is>
-          <t>0.30%</t>
+          <t>0.75%</t>
         </is>
       </c>
       <c r="D202" s="24" t="inlineStr">
@@ -16232,7 +16232,7 @@
       </c>
       <c r="C203" s="28" t="inlineStr">
         <is>
-          <t>0.30%</t>
+          <t>0.75%</t>
         </is>
       </c>
       <c r="D203" s="28" t="inlineStr">
@@ -16310,7 +16310,7 @@
       </c>
       <c r="C204" s="24" t="inlineStr">
         <is>
-          <t>0.30%</t>
+          <t>0.75%</t>
         </is>
       </c>
       <c r="D204" s="24" t="inlineStr">
@@ -16388,7 +16388,7 @@
       </c>
       <c r="C205" s="32" t="inlineStr">
         <is>
-          <t>0.30%</t>
+          <t>0.75%</t>
         </is>
       </c>
       <c r="D205" s="32" t="inlineStr">
@@ -16507,7 +16507,7 @@
     <row r="2" ht="22" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Long signal: Shareholder Yield + Gross Profitability + ROIC  |  Short signal: Net Ext. Financing + Leverage + F-Score + Gross Profitability  |  130% long top-100 / w_short = 130% × β_long/β_short (Vasicek-adj, 12m trailing)  |  Monthly rebalancing, ±5 pp sector neutrality, beta-neutral</t>
+          <t>Long signal: Shareholder Yield + Gross Profitability + ROIC  |  Short signal: Net Ext. Financing + Leverage + F-Score + Gross Profitability  |  175% long top-100 / w_short = 175% × β_long/β_short (Vasicek-adj, 12m trailing)  |  Monthly rebalancing, ±5% sector neutrality, beta-neutral</t>
         </is>
       </c>
     </row>
@@ -16637,7 +16637,7 @@
       </c>
       <c r="B6" s="16" t="inlineStr">
         <is>
-          <t>1.30%</t>
+          <t>1.75%</t>
         </is>
       </c>
       <c r="C6" s="16" t="inlineStr">
@@ -16710,7 +16710,7 @@
       </c>
       <c r="B7" s="20" t="inlineStr">
         <is>
-          <t>1.30%</t>
+          <t>1.75%</t>
         </is>
       </c>
       <c r="C7" s="20" t="inlineStr">
@@ -16783,7 +16783,7 @@
       </c>
       <c r="B8" s="16" t="inlineStr">
         <is>
-          <t>1.30%</t>
+          <t>1.75%</t>
         </is>
       </c>
       <c r="C8" s="16" t="inlineStr">
@@ -16856,7 +16856,7 @@
       </c>
       <c r="B9" s="20" t="inlineStr">
         <is>
-          <t>1.30%</t>
+          <t>1.75%</t>
         </is>
       </c>
       <c r="C9" s="20" t="inlineStr">
@@ -16929,7 +16929,7 @@
       </c>
       <c r="B10" s="16" t="inlineStr">
         <is>
-          <t>1.30%</t>
+          <t>1.75%</t>
         </is>
       </c>
       <c r="C10" s="16" t="inlineStr">
@@ -17002,7 +17002,7 @@
       </c>
       <c r="B11" s="20" t="inlineStr">
         <is>
-          <t>1.30%</t>
+          <t>1.75%</t>
         </is>
       </c>
       <c r="C11" s="20" t="inlineStr">
@@ -17075,7 +17075,7 @@
       </c>
       <c r="B12" s="16" t="inlineStr">
         <is>
-          <t>1.30%</t>
+          <t>1.75%</t>
         </is>
       </c>
       <c r="C12" s="16" t="inlineStr">
@@ -17148,7 +17148,7 @@
       </c>
       <c r="B13" s="20" t="inlineStr">
         <is>
-          <t>1.30%</t>
+          <t>1.75%</t>
         </is>
       </c>
       <c r="C13" s="20" t="inlineStr">
@@ -17221,7 +17221,7 @@
       </c>
       <c r="B14" s="16" t="inlineStr">
         <is>
-          <t>1.30%</t>
+          <t>1.75%</t>
         </is>
       </c>
       <c r="C14" s="16" t="inlineStr">
@@ -17294,7 +17294,7 @@
       </c>
       <c r="B15" s="20" t="inlineStr">
         <is>
-          <t>1.30%</t>
+          <t>1.75%</t>
         </is>
       </c>
       <c r="C15" s="20" t="inlineStr">
@@ -17367,7 +17367,7 @@
       </c>
       <c r="B16" s="16" t="inlineStr">
         <is>
-          <t>1.30%</t>
+          <t>1.75%</t>
         </is>
       </c>
       <c r="C16" s="16" t="inlineStr">
@@ -17440,7 +17440,7 @@
       </c>
       <c r="B17" s="20" t="inlineStr">
         <is>
-          <t>1.30%</t>
+          <t>1.75%</t>
         </is>
       </c>
       <c r="C17" s="20" t="inlineStr">
@@ -17513,7 +17513,7 @@
       </c>
       <c r="B18" s="16" t="inlineStr">
         <is>
-          <t>1.30%</t>
+          <t>1.75%</t>
         </is>
       </c>
       <c r="C18" s="16" t="inlineStr">
@@ -17586,7 +17586,7 @@
       </c>
       <c r="B19" s="20" t="inlineStr">
         <is>
-          <t>1.30%</t>
+          <t>1.75%</t>
         </is>
       </c>
       <c r="C19" s="20" t="inlineStr">
@@ -17659,7 +17659,7 @@
       </c>
       <c r="B20" s="16" t="inlineStr">
         <is>
-          <t>1.30%</t>
+          <t>1.75%</t>
         </is>
       </c>
       <c r="C20" s="16" t="inlineStr">
@@ -17732,7 +17732,7 @@
       </c>
       <c r="B21" s="20" t="inlineStr">
         <is>
-          <t>1.30%</t>
+          <t>1.75%</t>
         </is>
       </c>
       <c r="C21" s="20" t="inlineStr">
@@ -17805,7 +17805,7 @@
       </c>
       <c r="B22" s="16" t="inlineStr">
         <is>
-          <t>1.30%</t>
+          <t>1.75%</t>
         </is>
       </c>
       <c r="C22" s="16" t="inlineStr">
@@ -17878,7 +17878,7 @@
       </c>
       <c r="B23" s="20" t="inlineStr">
         <is>
-          <t>1.30%</t>
+          <t>1.75%</t>
         </is>
       </c>
       <c r="C23" s="20" t="inlineStr">
@@ -17951,7 +17951,7 @@
       </c>
       <c r="B24" s="16" t="inlineStr">
         <is>
-          <t>1.30%</t>
+          <t>1.75%</t>
         </is>
       </c>
       <c r="C24" s="16" t="inlineStr">
@@ -18024,7 +18024,7 @@
       </c>
       <c r="B25" s="20" t="inlineStr">
         <is>
-          <t>1.30%</t>
+          <t>1.75%</t>
         </is>
       </c>
       <c r="C25" s="20" t="inlineStr">
@@ -18097,7 +18097,7 @@
       </c>
       <c r="B26" s="16" t="inlineStr">
         <is>
-          <t>1.30%</t>
+          <t>1.75%</t>
         </is>
       </c>
       <c r="C26" s="16" t="inlineStr">
@@ -18170,7 +18170,7 @@
       </c>
       <c r="B27" s="20" t="inlineStr">
         <is>
-          <t>1.30%</t>
+          <t>1.75%</t>
         </is>
       </c>
       <c r="C27" s="20" t="inlineStr">
@@ -18243,7 +18243,7 @@
       </c>
       <c r="B28" s="16" t="inlineStr">
         <is>
-          <t>1.30%</t>
+          <t>1.75%</t>
         </is>
       </c>
       <c r="C28" s="16" t="inlineStr">
@@ -18316,7 +18316,7 @@
       </c>
       <c r="B29" s="20" t="inlineStr">
         <is>
-          <t>1.30%</t>
+          <t>1.75%</t>
         </is>
       </c>
       <c r="C29" s="20" t="inlineStr">
@@ -18389,7 +18389,7 @@
       </c>
       <c r="B30" s="16" t="inlineStr">
         <is>
-          <t>1.30%</t>
+          <t>1.75%</t>
         </is>
       </c>
       <c r="C30" s="16" t="inlineStr">
@@ -18462,7 +18462,7 @@
       </c>
       <c r="B31" s="20" t="inlineStr">
         <is>
-          <t>1.30%</t>
+          <t>1.75%</t>
         </is>
       </c>
       <c r="C31" s="20" t="inlineStr">
@@ -18535,7 +18535,7 @@
       </c>
       <c r="B32" s="16" t="inlineStr">
         <is>
-          <t>1.30%</t>
+          <t>1.75%</t>
         </is>
       </c>
       <c r="C32" s="16" t="inlineStr">
@@ -18608,7 +18608,7 @@
       </c>
       <c r="B33" s="20" t="inlineStr">
         <is>
-          <t>1.30%</t>
+          <t>1.75%</t>
         </is>
       </c>
       <c r="C33" s="20" t="inlineStr">
@@ -18681,7 +18681,7 @@
       </c>
       <c r="B34" s="16" t="inlineStr">
         <is>
-          <t>1.30%</t>
+          <t>1.75%</t>
         </is>
       </c>
       <c r="C34" s="16" t="inlineStr">
@@ -18754,7 +18754,7 @@
       </c>
       <c r="B35" s="20" t="inlineStr">
         <is>
-          <t>1.30%</t>
+          <t>1.75%</t>
         </is>
       </c>
       <c r="C35" s="20" t="inlineStr">
@@ -18827,7 +18827,7 @@
       </c>
       <c r="B36" s="16" t="inlineStr">
         <is>
-          <t>1.30%</t>
+          <t>1.75%</t>
         </is>
       </c>
       <c r="C36" s="16" t="inlineStr">
@@ -18900,7 +18900,7 @@
       </c>
       <c r="B37" s="20" t="inlineStr">
         <is>
-          <t>1.30%</t>
+          <t>1.75%</t>
         </is>
       </c>
       <c r="C37" s="20" t="inlineStr">
@@ -18973,7 +18973,7 @@
       </c>
       <c r="B38" s="16" t="inlineStr">
         <is>
-          <t>1.30%</t>
+          <t>1.75%</t>
         </is>
       </c>
       <c r="C38" s="16" t="inlineStr">
@@ -19046,7 +19046,7 @@
       </c>
       <c r="B39" s="20" t="inlineStr">
         <is>
-          <t>1.30%</t>
+          <t>1.75%</t>
         </is>
       </c>
       <c r="C39" s="20" t="inlineStr">
@@ -19119,7 +19119,7 @@
       </c>
       <c r="B40" s="16" t="inlineStr">
         <is>
-          <t>1.30%</t>
+          <t>1.75%</t>
         </is>
       </c>
       <c r="C40" s="16" t="inlineStr">
@@ -19192,7 +19192,7 @@
       </c>
       <c r="B41" s="20" t="inlineStr">
         <is>
-          <t>1.30%</t>
+          <t>1.75%</t>
         </is>
       </c>
       <c r="C41" s="20" t="inlineStr">
@@ -19265,7 +19265,7 @@
       </c>
       <c r="B42" s="16" t="inlineStr">
         <is>
-          <t>1.30%</t>
+          <t>1.75%</t>
         </is>
       </c>
       <c r="C42" s="16" t="inlineStr">
@@ -19338,7 +19338,7 @@
       </c>
       <c r="B43" s="20" t="inlineStr">
         <is>
-          <t>1.30%</t>
+          <t>1.75%</t>
         </is>
       </c>
       <c r="C43" s="20" t="inlineStr">
@@ -19411,7 +19411,7 @@
       </c>
       <c r="B44" s="16" t="inlineStr">
         <is>
-          <t>1.30%</t>
+          <t>1.75%</t>
         </is>
       </c>
       <c r="C44" s="16" t="inlineStr">
@@ -19484,7 +19484,7 @@
       </c>
       <c r="B45" s="20" t="inlineStr">
         <is>
-          <t>1.30%</t>
+          <t>1.75%</t>
         </is>
       </c>
       <c r="C45" s="20" t="inlineStr">
@@ -19557,7 +19557,7 @@
       </c>
       <c r="B46" s="16" t="inlineStr">
         <is>
-          <t>1.30%</t>
+          <t>1.75%</t>
         </is>
       </c>
       <c r="C46" s="16" t="inlineStr">
@@ -19630,7 +19630,7 @@
       </c>
       <c r="B47" s="20" t="inlineStr">
         <is>
-          <t>1.30%</t>
+          <t>1.75%</t>
         </is>
       </c>
       <c r="C47" s="20" t="inlineStr">
@@ -19703,7 +19703,7 @@
       </c>
       <c r="B48" s="16" t="inlineStr">
         <is>
-          <t>1.30%</t>
+          <t>1.75%</t>
         </is>
       </c>
       <c r="C48" s="16" t="inlineStr">
@@ -19776,7 +19776,7 @@
       </c>
       <c r="B49" s="20" t="inlineStr">
         <is>
-          <t>1.30%</t>
+          <t>1.75%</t>
         </is>
       </c>
       <c r="C49" s="20" t="inlineStr">
@@ -19849,7 +19849,7 @@
       </c>
       <c r="B50" s="16" t="inlineStr">
         <is>
-          <t>1.30%</t>
+          <t>1.75%</t>
         </is>
       </c>
       <c r="C50" s="16" t="inlineStr">
@@ -19922,7 +19922,7 @@
       </c>
       <c r="B51" s="20" t="inlineStr">
         <is>
-          <t>1.30%</t>
+          <t>1.75%</t>
         </is>
       </c>
       <c r="C51" s="20" t="inlineStr">
@@ -19995,7 +19995,7 @@
       </c>
       <c r="B52" s="16" t="inlineStr">
         <is>
-          <t>1.30%</t>
+          <t>1.75%</t>
         </is>
       </c>
       <c r="C52" s="16" t="inlineStr">
@@ -20068,7 +20068,7 @@
       </c>
       <c r="B53" s="20" t="inlineStr">
         <is>
-          <t>1.30%</t>
+          <t>1.75%</t>
         </is>
       </c>
       <c r="C53" s="20" t="inlineStr">
@@ -20141,7 +20141,7 @@
       </c>
       <c r="B54" s="16" t="inlineStr">
         <is>
-          <t>1.30%</t>
+          <t>1.75%</t>
         </is>
       </c>
       <c r="C54" s="16" t="inlineStr">
@@ -20214,7 +20214,7 @@
       </c>
       <c r="B55" s="20" t="inlineStr">
         <is>
-          <t>1.30%</t>
+          <t>1.75%</t>
         </is>
       </c>
       <c r="C55" s="20" t="inlineStr">
@@ -20289,7 +20289,7 @@
       </c>
       <c r="B56" s="16" t="inlineStr">
         <is>
-          <t>1.30%</t>
+          <t>1.75%</t>
         </is>
       </c>
       <c r="C56" s="16" t="inlineStr">
@@ -20362,7 +20362,7 @@
       </c>
       <c r="B57" s="20" t="inlineStr">
         <is>
-          <t>1.30%</t>
+          <t>1.75%</t>
         </is>
       </c>
       <c r="C57" s="20" t="inlineStr">
@@ -20435,7 +20435,7 @@
       </c>
       <c r="B58" s="16" t="inlineStr">
         <is>
-          <t>1.30%</t>
+          <t>1.75%</t>
         </is>
       </c>
       <c r="C58" s="16" t="inlineStr">
@@ -20508,7 +20508,7 @@
       </c>
       <c r="B59" s="20" t="inlineStr">
         <is>
-          <t>1.30%</t>
+          <t>1.75%</t>
         </is>
       </c>
       <c r="C59" s="20" t="inlineStr">
@@ -20581,7 +20581,7 @@
       </c>
       <c r="B60" s="16" t="inlineStr">
         <is>
-          <t>1.30%</t>
+          <t>1.75%</t>
         </is>
       </c>
       <c r="C60" s="16" t="inlineStr">
@@ -20654,7 +20654,7 @@
       </c>
       <c r="B61" s="20" t="inlineStr">
         <is>
-          <t>1.30%</t>
+          <t>1.75%</t>
         </is>
       </c>
       <c r="C61" s="20" t="inlineStr">
@@ -20727,7 +20727,7 @@
       </c>
       <c r="B62" s="16" t="inlineStr">
         <is>
-          <t>1.30%</t>
+          <t>1.75%</t>
         </is>
       </c>
       <c r="C62" s="16" t="inlineStr">
@@ -20802,7 +20802,7 @@
       </c>
       <c r="B63" s="20" t="inlineStr">
         <is>
-          <t>1.30%</t>
+          <t>1.75%</t>
         </is>
       </c>
       <c r="C63" s="20" t="inlineStr">
@@ -20875,7 +20875,7 @@
       </c>
       <c r="B64" s="16" t="inlineStr">
         <is>
-          <t>1.30%</t>
+          <t>1.75%</t>
         </is>
       </c>
       <c r="C64" s="16" t="inlineStr">
@@ -20948,7 +20948,7 @@
       </c>
       <c r="B65" s="20" t="inlineStr">
         <is>
-          <t>1.30%</t>
+          <t>1.75%</t>
         </is>
       </c>
       <c r="C65" s="20" t="inlineStr">
@@ -21023,7 +21023,7 @@
       </c>
       <c r="B66" s="16" t="inlineStr">
         <is>
-          <t>1.30%</t>
+          <t>1.75%</t>
         </is>
       </c>
       <c r="C66" s="16" t="inlineStr">
@@ -21096,7 +21096,7 @@
       </c>
       <c r="B67" s="20" t="inlineStr">
         <is>
-          <t>1.30%</t>
+          <t>1.75%</t>
         </is>
       </c>
       <c r="C67" s="20" t="inlineStr">
@@ -21171,7 +21171,7 @@
       </c>
       <c r="B68" s="16" t="inlineStr">
         <is>
-          <t>1.30%</t>
+          <t>1.75%</t>
         </is>
       </c>
       <c r="C68" s="16" t="inlineStr">
@@ -21246,7 +21246,7 @@
       </c>
       <c r="B69" s="20" t="inlineStr">
         <is>
-          <t>1.30%</t>
+          <t>1.75%</t>
         </is>
       </c>
       <c r="C69" s="20" t="inlineStr">
@@ -21319,7 +21319,7 @@
       </c>
       <c r="B70" s="16" t="inlineStr">
         <is>
-          <t>1.30%</t>
+          <t>1.75%</t>
         </is>
       </c>
       <c r="C70" s="16" t="inlineStr">
@@ -21392,7 +21392,7 @@
       </c>
       <c r="B71" s="20" t="inlineStr">
         <is>
-          <t>1.30%</t>
+          <t>1.75%</t>
         </is>
       </c>
       <c r="C71" s="20" t="inlineStr">
@@ -21465,7 +21465,7 @@
       </c>
       <c r="B72" s="16" t="inlineStr">
         <is>
-          <t>1.30%</t>
+          <t>1.75%</t>
         </is>
       </c>
       <c r="C72" s="16" t="inlineStr">
@@ -21538,7 +21538,7 @@
       </c>
       <c r="B73" s="20" t="inlineStr">
         <is>
-          <t>1.30%</t>
+          <t>1.75%</t>
         </is>
       </c>
       <c r="C73" s="20" t="inlineStr">
@@ -21611,7 +21611,7 @@
       </c>
       <c r="B74" s="16" t="inlineStr">
         <is>
-          <t>1.30%</t>
+          <t>1.75%</t>
         </is>
       </c>
       <c r="C74" s="16" t="inlineStr">
@@ -21684,7 +21684,7 @@
       </c>
       <c r="B75" s="20" t="inlineStr">
         <is>
-          <t>1.30%</t>
+          <t>1.75%</t>
         </is>
       </c>
       <c r="C75" s="20" t="inlineStr">
@@ -21757,7 +21757,7 @@
       </c>
       <c r="B76" s="16" t="inlineStr">
         <is>
-          <t>1.30%</t>
+          <t>1.75%</t>
         </is>
       </c>
       <c r="C76" s="16" t="inlineStr">
@@ -21830,7 +21830,7 @@
       </c>
       <c r="B77" s="20" t="inlineStr">
         <is>
-          <t>1.30%</t>
+          <t>1.75%</t>
         </is>
       </c>
       <c r="C77" s="20" t="inlineStr">
@@ -21903,7 +21903,7 @@
       </c>
       <c r="B78" s="16" t="inlineStr">
         <is>
-          <t>1.30%</t>
+          <t>1.75%</t>
         </is>
       </c>
       <c r="C78" s="16" t="inlineStr">
@@ -21976,7 +21976,7 @@
       </c>
       <c r="B79" s="20" t="inlineStr">
         <is>
-          <t>1.30%</t>
+          <t>1.75%</t>
         </is>
       </c>
       <c r="C79" s="20" t="inlineStr">
@@ -22049,7 +22049,7 @@
       </c>
       <c r="B80" s="16" t="inlineStr">
         <is>
-          <t>1.30%</t>
+          <t>1.75%</t>
         </is>
       </c>
       <c r="C80" s="16" t="inlineStr">
@@ -22122,7 +22122,7 @@
       </c>
       <c r="B81" s="20" t="inlineStr">
         <is>
-          <t>1.30%</t>
+          <t>1.75%</t>
         </is>
       </c>
       <c r="C81" s="20" t="inlineStr">
@@ -22195,7 +22195,7 @@
       </c>
       <c r="B82" s="16" t="inlineStr">
         <is>
-          <t>1.30%</t>
+          <t>1.75%</t>
         </is>
       </c>
       <c r="C82" s="16" t="inlineStr">
@@ -22270,7 +22270,7 @@
       </c>
       <c r="B83" s="20" t="inlineStr">
         <is>
-          <t>1.30%</t>
+          <t>1.75%</t>
         </is>
       </c>
       <c r="C83" s="20" t="inlineStr">
@@ -22343,7 +22343,7 @@
       </c>
       <c r="B84" s="16" t="inlineStr">
         <is>
-          <t>1.30%</t>
+          <t>1.75%</t>
         </is>
       </c>
       <c r="C84" s="16" t="inlineStr">
@@ -22416,7 +22416,7 @@
       </c>
       <c r="B85" s="20" t="inlineStr">
         <is>
-          <t>1.30%</t>
+          <t>1.75%</t>
         </is>
       </c>
       <c r="C85" s="20" t="inlineStr">
@@ -22489,7 +22489,7 @@
       </c>
       <c r="B86" s="16" t="inlineStr">
         <is>
-          <t>1.30%</t>
+          <t>1.75%</t>
         </is>
       </c>
       <c r="C86" s="16" t="inlineStr">
@@ -22562,7 +22562,7 @@
       </c>
       <c r="B87" s="20" t="inlineStr">
         <is>
-          <t>1.30%</t>
+          <t>1.75%</t>
         </is>
       </c>
       <c r="C87" s="20" t="inlineStr">
@@ -22637,7 +22637,7 @@
       </c>
       <c r="B88" s="16" t="inlineStr">
         <is>
-          <t>1.30%</t>
+          <t>1.75%</t>
         </is>
       </c>
       <c r="C88" s="16" t="inlineStr">
@@ -22710,7 +22710,7 @@
       </c>
       <c r="B89" s="20" t="inlineStr">
         <is>
-          <t>1.30%</t>
+          <t>1.75%</t>
         </is>
       </c>
       <c r="C89" s="20" t="inlineStr">
@@ -22783,7 +22783,7 @@
       </c>
       <c r="B90" s="16" t="inlineStr">
         <is>
-          <t>1.30%</t>
+          <t>1.75%</t>
         </is>
       </c>
       <c r="C90" s="16" t="inlineStr">
@@ -22856,7 +22856,7 @@
       </c>
       <c r="B91" s="20" t="inlineStr">
         <is>
-          <t>1.30%</t>
+          <t>1.75%</t>
         </is>
       </c>
       <c r="C91" s="20" t="inlineStr">
@@ -22929,7 +22929,7 @@
       </c>
       <c r="B92" s="16" t="inlineStr">
         <is>
-          <t>1.30%</t>
+          <t>1.75%</t>
         </is>
       </c>
       <c r="C92" s="16" t="inlineStr">
@@ -23002,7 +23002,7 @@
       </c>
       <c r="B93" s="20" t="inlineStr">
         <is>
-          <t>1.30%</t>
+          <t>1.75%</t>
         </is>
       </c>
       <c r="C93" s="20" t="inlineStr">
@@ -23077,7 +23077,7 @@
       </c>
       <c r="B94" s="16" t="inlineStr">
         <is>
-          <t>1.30%</t>
+          <t>1.75%</t>
         </is>
       </c>
       <c r="C94" s="16" t="inlineStr">
@@ -23150,7 +23150,7 @@
       </c>
       <c r="B95" s="20" t="inlineStr">
         <is>
-          <t>1.30%</t>
+          <t>1.75%</t>
         </is>
       </c>
       <c r="C95" s="20" t="inlineStr">
@@ -23223,7 +23223,7 @@
       </c>
       <c r="B96" s="16" t="inlineStr">
         <is>
-          <t>1.30%</t>
+          <t>1.75%</t>
         </is>
       </c>
       <c r="C96" s="16" t="inlineStr">
@@ -23296,7 +23296,7 @@
       </c>
       <c r="B97" s="20" t="inlineStr">
         <is>
-          <t>1.30%</t>
+          <t>1.75%</t>
         </is>
       </c>
       <c r="C97" s="20" t="inlineStr">
@@ -23369,7 +23369,7 @@
       </c>
       <c r="B98" s="16" t="inlineStr">
         <is>
-          <t>1.30%</t>
+          <t>1.75%</t>
         </is>
       </c>
       <c r="C98" s="16" t="inlineStr">
@@ -23442,7 +23442,7 @@
       </c>
       <c r="B99" s="20" t="inlineStr">
         <is>
-          <t>1.30%</t>
+          <t>1.75%</t>
         </is>
       </c>
       <c r="C99" s="20" t="inlineStr">
@@ -23515,7 +23515,7 @@
       </c>
       <c r="B100" s="16" t="inlineStr">
         <is>
-          <t>1.30%</t>
+          <t>1.75%</t>
         </is>
       </c>
       <c r="C100" s="16" t="inlineStr">
@@ -23588,7 +23588,7 @@
       </c>
       <c r="B101" s="20" t="inlineStr">
         <is>
-          <t>1.30%</t>
+          <t>1.75%</t>
         </is>
       </c>
       <c r="C101" s="20" t="inlineStr">
@@ -23661,7 +23661,7 @@
       </c>
       <c r="B102" s="16" t="inlineStr">
         <is>
-          <t>1.30%</t>
+          <t>1.75%</t>
         </is>
       </c>
       <c r="C102" s="16" t="inlineStr">
@@ -23734,7 +23734,7 @@
       </c>
       <c r="B103" s="20" t="inlineStr">
         <is>
-          <t>1.30%</t>
+          <t>1.75%</t>
         </is>
       </c>
       <c r="C103" s="20" t="inlineStr">
@@ -23807,7 +23807,7 @@
       </c>
       <c r="B104" s="16" t="inlineStr">
         <is>
-          <t>1.30%</t>
+          <t>1.75%</t>
         </is>
       </c>
       <c r="C104" s="16" t="inlineStr">
@@ -23880,7 +23880,7 @@
       </c>
       <c r="B105" s="36" t="inlineStr">
         <is>
-          <t>1.30%</t>
+          <t>1.75%</t>
         </is>
       </c>
       <c r="C105" s="36" t="inlineStr">
@@ -23999,7 +23999,7 @@
     <row r="2" ht="22" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Long signal: Shareholder Yield + Gross Profitability + ROIC  |  Short signal: Net Ext. Financing + Leverage + F-Score + Gross Profitability  |  130% long top-100 / w_short = 130% × β_long/β_short (Vasicek-adj, 12m trailing)  |  Monthly rebalancing, ±5 pp sector neutrality, beta-neutral</t>
+          <t>Long signal: Shareholder Yield + Gross Profitability + ROIC  |  Short signal: Net Ext. Financing + Leverage + F-Score + Gross Profitability  |  175% long top-100 / w_short = 175% × β_long/β_short (Vasicek-adj, 12m trailing)  |  Monthly rebalancing, ±5% sector neutrality, beta-neutral</t>
         </is>
       </c>
     </row>
@@ -24129,7 +24129,7 @@
       </c>
       <c r="B6" s="24" t="inlineStr">
         <is>
-          <t>0.30%</t>
+          <t>0.75%</t>
         </is>
       </c>
       <c r="C6" s="24" t="inlineStr">
@@ -24202,7 +24202,7 @@
       </c>
       <c r="B7" s="28" t="inlineStr">
         <is>
-          <t>0.30%</t>
+          <t>0.75%</t>
         </is>
       </c>
       <c r="C7" s="28" t="inlineStr">
@@ -24275,7 +24275,7 @@
       </c>
       <c r="B8" s="24" t="inlineStr">
         <is>
-          <t>0.30%</t>
+          <t>0.75%</t>
         </is>
       </c>
       <c r="C8" s="24" t="inlineStr">
@@ -24348,7 +24348,7 @@
       </c>
       <c r="B9" s="28" t="inlineStr">
         <is>
-          <t>0.30%</t>
+          <t>0.75%</t>
         </is>
       </c>
       <c r="C9" s="28" t="inlineStr">
@@ -24421,7 +24421,7 @@
       </c>
       <c r="B10" s="24" t="inlineStr">
         <is>
-          <t>0.30%</t>
+          <t>0.75%</t>
         </is>
       </c>
       <c r="C10" s="24" t="inlineStr">
@@ -24494,7 +24494,7 @@
       </c>
       <c r="B11" s="28" t="inlineStr">
         <is>
-          <t>0.30%</t>
+          <t>0.75%</t>
         </is>
       </c>
       <c r="C11" s="28" t="inlineStr">
@@ -24569,7 +24569,7 @@
       </c>
       <c r="B12" s="24" t="inlineStr">
         <is>
-          <t>0.30%</t>
+          <t>0.75%</t>
         </is>
       </c>
       <c r="C12" s="24" t="inlineStr">
@@ -24644,7 +24644,7 @@
       </c>
       <c r="B13" s="28" t="inlineStr">
         <is>
-          <t>0.30%</t>
+          <t>0.75%</t>
         </is>
       </c>
       <c r="C13" s="28" t="inlineStr">
@@ -24717,7 +24717,7 @@
       </c>
       <c r="B14" s="24" t="inlineStr">
         <is>
-          <t>0.30%</t>
+          <t>0.75%</t>
         </is>
       </c>
       <c r="C14" s="24" t="inlineStr">
@@ -24790,7 +24790,7 @@
       </c>
       <c r="B15" s="28" t="inlineStr">
         <is>
-          <t>0.30%</t>
+          <t>0.75%</t>
         </is>
       </c>
       <c r="C15" s="28" t="inlineStr">
@@ -24863,7 +24863,7 @@
       </c>
       <c r="B16" s="24" t="inlineStr">
         <is>
-          <t>0.30%</t>
+          <t>0.75%</t>
         </is>
       </c>
       <c r="C16" s="24" t="inlineStr">
@@ -24936,7 +24936,7 @@
       </c>
       <c r="B17" s="28" t="inlineStr">
         <is>
-          <t>0.30%</t>
+          <t>0.75%</t>
         </is>
       </c>
       <c r="C17" s="28" t="inlineStr">
@@ -25009,7 +25009,7 @@
       </c>
       <c r="B18" s="24" t="inlineStr">
         <is>
-          <t>0.30%</t>
+          <t>0.75%</t>
         </is>
       </c>
       <c r="C18" s="24" t="inlineStr">
@@ -25084,7 +25084,7 @@
       </c>
       <c r="B19" s="28" t="inlineStr">
         <is>
-          <t>0.30%</t>
+          <t>0.75%</t>
         </is>
       </c>
       <c r="C19" s="28" t="inlineStr">
@@ -25157,7 +25157,7 @@
       </c>
       <c r="B20" s="24" t="inlineStr">
         <is>
-          <t>0.30%</t>
+          <t>0.75%</t>
         </is>
       </c>
       <c r="C20" s="24" t="inlineStr">
@@ -25230,7 +25230,7 @@
       </c>
       <c r="B21" s="28" t="inlineStr">
         <is>
-          <t>0.30%</t>
+          <t>0.75%</t>
         </is>
       </c>
       <c r="C21" s="28" t="inlineStr">
@@ -25303,7 +25303,7 @@
       </c>
       <c r="B22" s="24" t="inlineStr">
         <is>
-          <t>0.30%</t>
+          <t>0.75%</t>
         </is>
       </c>
       <c r="C22" s="24" t="inlineStr">
@@ -25376,7 +25376,7 @@
       </c>
       <c r="B23" s="28" t="inlineStr">
         <is>
-          <t>0.30%</t>
+          <t>0.75%</t>
         </is>
       </c>
       <c r="C23" s="28" t="inlineStr">
@@ -25449,7 +25449,7 @@
       </c>
       <c r="B24" s="24" t="inlineStr">
         <is>
-          <t>0.30%</t>
+          <t>0.75%</t>
         </is>
       </c>
       <c r="C24" s="24" t="inlineStr">
@@ -25522,7 +25522,7 @@
       </c>
       <c r="B25" s="28" t="inlineStr">
         <is>
-          <t>0.30%</t>
+          <t>0.75%</t>
         </is>
       </c>
       <c r="C25" s="28" t="inlineStr">
@@ -25597,7 +25597,7 @@
       </c>
       <c r="B26" s="24" t="inlineStr">
         <is>
-          <t>0.30%</t>
+          <t>0.75%</t>
         </is>
       </c>
       <c r="C26" s="24" t="inlineStr">
@@ -25670,7 +25670,7 @@
       </c>
       <c r="B27" s="28" t="inlineStr">
         <is>
-          <t>0.30%</t>
+          <t>0.75%</t>
         </is>
       </c>
       <c r="C27" s="28" t="inlineStr">
@@ -25743,7 +25743,7 @@
       </c>
       <c r="B28" s="24" t="inlineStr">
         <is>
-          <t>0.30%</t>
+          <t>0.75%</t>
         </is>
       </c>
       <c r="C28" s="24" t="inlineStr">
@@ -25818,7 +25818,7 @@
       </c>
       <c r="B29" s="28" t="inlineStr">
         <is>
-          <t>0.30%</t>
+          <t>0.75%</t>
         </is>
       </c>
       <c r="C29" s="28" t="inlineStr">
@@ -25891,7 +25891,7 @@
       </c>
       <c r="B30" s="24" t="inlineStr">
         <is>
-          <t>0.30%</t>
+          <t>0.75%</t>
         </is>
       </c>
       <c r="C30" s="24" t="inlineStr">
@@ -25964,7 +25964,7 @@
       </c>
       <c r="B31" s="28" t="inlineStr">
         <is>
-          <t>0.30%</t>
+          <t>0.75%</t>
         </is>
       </c>
       <c r="C31" s="28" t="inlineStr">
@@ -26037,7 +26037,7 @@
       </c>
       <c r="B32" s="24" t="inlineStr">
         <is>
-          <t>0.30%</t>
+          <t>0.75%</t>
         </is>
       </c>
       <c r="C32" s="24" t="inlineStr">
@@ -26110,7 +26110,7 @@
       </c>
       <c r="B33" s="28" t="inlineStr">
         <is>
-          <t>0.30%</t>
+          <t>0.75%</t>
         </is>
       </c>
       <c r="C33" s="28" t="inlineStr">
@@ -26185,7 +26185,7 @@
       </c>
       <c r="B34" s="24" t="inlineStr">
         <is>
-          <t>0.30%</t>
+          <t>0.75%</t>
         </is>
       </c>
       <c r="C34" s="24" t="inlineStr">
@@ -26258,7 +26258,7 @@
       </c>
       <c r="B35" s="28" t="inlineStr">
         <is>
-          <t>0.30%</t>
+          <t>0.75%</t>
         </is>
       </c>
       <c r="C35" s="28" t="inlineStr">
@@ -26331,7 +26331,7 @@
       </c>
       <c r="B36" s="24" t="inlineStr">
         <is>
-          <t>0.30%</t>
+          <t>0.75%</t>
         </is>
       </c>
       <c r="C36" s="24" t="inlineStr">
@@ -26404,7 +26404,7 @@
       </c>
       <c r="B37" s="28" t="inlineStr">
         <is>
-          <t>0.30%</t>
+          <t>0.75%</t>
         </is>
       </c>
       <c r="C37" s="28" t="inlineStr">
@@ -26477,7 +26477,7 @@
       </c>
       <c r="B38" s="24" t="inlineStr">
         <is>
-          <t>0.30%</t>
+          <t>0.75%</t>
         </is>
       </c>
       <c r="C38" s="24" t="inlineStr">
@@ -26550,7 +26550,7 @@
       </c>
       <c r="B39" s="28" t="inlineStr">
         <is>
-          <t>0.30%</t>
+          <t>0.75%</t>
         </is>
       </c>
       <c r="C39" s="28" t="inlineStr">
@@ -26623,7 +26623,7 @@
       </c>
       <c r="B40" s="24" t="inlineStr">
         <is>
-          <t>0.30%</t>
+          <t>0.75%</t>
         </is>
       </c>
       <c r="C40" s="24" t="inlineStr">
@@ -26696,7 +26696,7 @@
       </c>
       <c r="B41" s="28" t="inlineStr">
         <is>
-          <t>0.30%</t>
+          <t>0.75%</t>
         </is>
       </c>
       <c r="C41" s="28" t="inlineStr">
@@ -26769,7 +26769,7 @@
       </c>
       <c r="B42" s="24" t="inlineStr">
         <is>
-          <t>0.30%</t>
+          <t>0.75%</t>
         </is>
       </c>
       <c r="C42" s="24" t="inlineStr">
@@ -26844,7 +26844,7 @@
       </c>
       <c r="B43" s="28" t="inlineStr">
         <is>
-          <t>0.30%</t>
+          <t>0.75%</t>
         </is>
       </c>
       <c r="C43" s="28" t="inlineStr">
@@ -26917,7 +26917,7 @@
       </c>
       <c r="B44" s="24" t="inlineStr">
         <is>
-          <t>0.30%</t>
+          <t>0.75%</t>
         </is>
       </c>
       <c r="C44" s="24" t="inlineStr">
@@ -26990,7 +26990,7 @@
       </c>
       <c r="B45" s="28" t="inlineStr">
         <is>
-          <t>0.30%</t>
+          <t>0.75%</t>
         </is>
       </c>
       <c r="C45" s="28" t="inlineStr">
@@ -27063,7 +27063,7 @@
       </c>
       <c r="B46" s="24" t="inlineStr">
         <is>
-          <t>0.30%</t>
+          <t>0.75%</t>
         </is>
       </c>
       <c r="C46" s="24" t="inlineStr">
@@ -27136,7 +27136,7 @@
       </c>
       <c r="B47" s="28" t="inlineStr">
         <is>
-          <t>0.30%</t>
+          <t>0.75%</t>
         </is>
       </c>
       <c r="C47" s="28" t="inlineStr">
@@ -27209,7 +27209,7 @@
       </c>
       <c r="B48" s="24" t="inlineStr">
         <is>
-          <t>0.30%</t>
+          <t>0.75%</t>
         </is>
       </c>
       <c r="C48" s="24" t="inlineStr">
@@ -27282,7 +27282,7 @@
       </c>
       <c r="B49" s="28" t="inlineStr">
         <is>
-          <t>0.30%</t>
+          <t>0.75%</t>
         </is>
       </c>
       <c r="C49" s="28" t="inlineStr">
@@ -27355,7 +27355,7 @@
       </c>
       <c r="B50" s="24" t="inlineStr">
         <is>
-          <t>0.30%</t>
+          <t>0.75%</t>
         </is>
       </c>
       <c r="C50" s="24" t="inlineStr">
@@ -27428,7 +27428,7 @@
       </c>
       <c r="B51" s="28" t="inlineStr">
         <is>
-          <t>0.30%</t>
+          <t>0.75%</t>
         </is>
       </c>
       <c r="C51" s="28" t="inlineStr">
@@ -27503,7 +27503,7 @@
       </c>
       <c r="B52" s="24" t="inlineStr">
         <is>
-          <t>0.30%</t>
+          <t>0.75%</t>
         </is>
       </c>
       <c r="C52" s="24" t="inlineStr">
@@ -27578,7 +27578,7 @@
       </c>
       <c r="B53" s="28" t="inlineStr">
         <is>
-          <t>0.30%</t>
+          <t>0.75%</t>
         </is>
       </c>
       <c r="C53" s="28" t="inlineStr">
@@ -27651,7 +27651,7 @@
       </c>
       <c r="B54" s="24" t="inlineStr">
         <is>
-          <t>0.30%</t>
+          <t>0.75%</t>
         </is>
       </c>
       <c r="C54" s="24" t="inlineStr">
@@ -27724,7 +27724,7 @@
       </c>
       <c r="B55" s="28" t="inlineStr">
         <is>
-          <t>0.30%</t>
+          <t>0.75%</t>
         </is>
       </c>
       <c r="C55" s="28" t="inlineStr">
@@ -27797,7 +27797,7 @@
       </c>
       <c r="B56" s="24" t="inlineStr">
         <is>
-          <t>0.30%</t>
+          <t>0.75%</t>
         </is>
       </c>
       <c r="C56" s="24" t="inlineStr">
@@ -27872,7 +27872,7 @@
       </c>
       <c r="B57" s="28" t="inlineStr">
         <is>
-          <t>0.30%</t>
+          <t>0.75%</t>
         </is>
       </c>
       <c r="C57" s="28" t="inlineStr">
@@ -27945,7 +27945,7 @@
       </c>
       <c r="B58" s="24" t="inlineStr">
         <is>
-          <t>0.30%</t>
+          <t>0.75%</t>
         </is>
       </c>
       <c r="C58" s="24" t="inlineStr">
@@ -28018,7 +28018,7 @@
       </c>
       <c r="B59" s="28" t="inlineStr">
         <is>
-          <t>0.30%</t>
+          <t>0.75%</t>
         </is>
       </c>
       <c r="C59" s="28" t="inlineStr">
@@ -28091,7 +28091,7 @@
       </c>
       <c r="B60" s="24" t="inlineStr">
         <is>
-          <t>0.30%</t>
+          <t>0.75%</t>
         </is>
       </c>
       <c r="C60" s="24" t="inlineStr">
@@ -28164,7 +28164,7 @@
       </c>
       <c r="B61" s="28" t="inlineStr">
         <is>
-          <t>0.30%</t>
+          <t>0.75%</t>
         </is>
       </c>
       <c r="C61" s="28" t="inlineStr">
@@ -28239,7 +28239,7 @@
       </c>
       <c r="B62" s="24" t="inlineStr">
         <is>
-          <t>0.30%</t>
+          <t>0.75%</t>
         </is>
       </c>
       <c r="C62" s="24" t="inlineStr">
@@ -28312,7 +28312,7 @@
       </c>
       <c r="B63" s="28" t="inlineStr">
         <is>
-          <t>0.30%</t>
+          <t>0.75%</t>
         </is>
       </c>
       <c r="C63" s="28" t="inlineStr">
@@ -28385,7 +28385,7 @@
       </c>
       <c r="B64" s="24" t="inlineStr">
         <is>
-          <t>0.30%</t>
+          <t>0.75%</t>
         </is>
       </c>
       <c r="C64" s="24" t="inlineStr">
@@ -28458,7 +28458,7 @@
       </c>
       <c r="B65" s="28" t="inlineStr">
         <is>
-          <t>0.30%</t>
+          <t>0.75%</t>
         </is>
       </c>
       <c r="C65" s="28" t="inlineStr">
@@ -28531,7 +28531,7 @@
       </c>
       <c r="B66" s="24" t="inlineStr">
         <is>
-          <t>0.30%</t>
+          <t>0.75%</t>
         </is>
       </c>
       <c r="C66" s="24" t="inlineStr">
@@ -28604,7 +28604,7 @@
       </c>
       <c r="B67" s="28" t="inlineStr">
         <is>
-          <t>0.30%</t>
+          <t>0.75%</t>
         </is>
       </c>
       <c r="C67" s="28" t="inlineStr">
@@ -28677,7 +28677,7 @@
       </c>
       <c r="B68" s="24" t="inlineStr">
         <is>
-          <t>0.30%</t>
+          <t>0.75%</t>
         </is>
       </c>
       <c r="C68" s="24" t="inlineStr">
@@ -28750,7 +28750,7 @@
       </c>
       <c r="B69" s="28" t="inlineStr">
         <is>
-          <t>0.30%</t>
+          <t>0.75%</t>
         </is>
       </c>
       <c r="C69" s="28" t="inlineStr">
@@ -28823,7 +28823,7 @@
       </c>
       <c r="B70" s="24" t="inlineStr">
         <is>
-          <t>0.30%</t>
+          <t>0.75%</t>
         </is>
       </c>
       <c r="C70" s="24" t="inlineStr">
@@ -28896,7 +28896,7 @@
       </c>
       <c r="B71" s="28" t="inlineStr">
         <is>
-          <t>0.30%</t>
+          <t>0.75%</t>
         </is>
       </c>
       <c r="C71" s="28" t="inlineStr">
@@ -28969,7 +28969,7 @@
       </c>
       <c r="B72" s="24" t="inlineStr">
         <is>
-          <t>0.30%</t>
+          <t>0.75%</t>
         </is>
       </c>
       <c r="C72" s="24" t="inlineStr">
@@ -29042,7 +29042,7 @@
       </c>
       <c r="B73" s="28" t="inlineStr">
         <is>
-          <t>0.30%</t>
+          <t>0.75%</t>
         </is>
       </c>
       <c r="C73" s="28" t="inlineStr">
@@ -29115,7 +29115,7 @@
       </c>
       <c r="B74" s="24" t="inlineStr">
         <is>
-          <t>0.30%</t>
+          <t>0.75%</t>
         </is>
       </c>
       <c r="C74" s="24" t="inlineStr">
@@ -29188,7 +29188,7 @@
       </c>
       <c r="B75" s="28" t="inlineStr">
         <is>
-          <t>0.30%</t>
+          <t>0.75%</t>
         </is>
       </c>
       <c r="C75" s="28" t="inlineStr">
@@ -29261,7 +29261,7 @@
       </c>
       <c r="B76" s="24" t="inlineStr">
         <is>
-          <t>0.30%</t>
+          <t>0.75%</t>
         </is>
       </c>
       <c r="C76" s="24" t="inlineStr">
@@ -29334,7 +29334,7 @@
       </c>
       <c r="B77" s="28" t="inlineStr">
         <is>
-          <t>0.30%</t>
+          <t>0.75%</t>
         </is>
       </c>
       <c r="C77" s="28" t="inlineStr">
@@ -29409,7 +29409,7 @@
       </c>
       <c r="B78" s="24" t="inlineStr">
         <is>
-          <t>0.30%</t>
+          <t>0.75%</t>
         </is>
       </c>
       <c r="C78" s="24" t="inlineStr">
@@ -29482,7 +29482,7 @@
       </c>
       <c r="B79" s="28" t="inlineStr">
         <is>
-          <t>0.30%</t>
+          <t>0.75%</t>
         </is>
       </c>
       <c r="C79" s="28" t="inlineStr">
@@ -29555,7 +29555,7 @@
       </c>
       <c r="B80" s="24" t="inlineStr">
         <is>
-          <t>0.30%</t>
+          <t>0.75%</t>
         </is>
       </c>
       <c r="C80" s="24" t="inlineStr">
@@ -29628,7 +29628,7 @@
       </c>
       <c r="B81" s="28" t="inlineStr">
         <is>
-          <t>0.30%</t>
+          <t>0.75%</t>
         </is>
       </c>
       <c r="C81" s="28" t="inlineStr">
@@ -29701,7 +29701,7 @@
       </c>
       <c r="B82" s="24" t="inlineStr">
         <is>
-          <t>0.30%</t>
+          <t>0.75%</t>
         </is>
       </c>
       <c r="C82" s="24" t="inlineStr">
@@ -29774,7 +29774,7 @@
       </c>
       <c r="B83" s="28" t="inlineStr">
         <is>
-          <t>0.30%</t>
+          <t>0.75%</t>
         </is>
       </c>
       <c r="C83" s="28" t="inlineStr">
@@ -29847,7 +29847,7 @@
       </c>
       <c r="B84" s="24" t="inlineStr">
         <is>
-          <t>0.30%</t>
+          <t>0.75%</t>
         </is>
       </c>
       <c r="C84" s="24" t="inlineStr">
@@ -29920,7 +29920,7 @@
       </c>
       <c r="B85" s="28" t="inlineStr">
         <is>
-          <t>0.30%</t>
+          <t>0.75%</t>
         </is>
       </c>
       <c r="C85" s="28" t="inlineStr">
@@ -29993,7 +29993,7 @@
       </c>
       <c r="B86" s="24" t="inlineStr">
         <is>
-          <t>0.30%</t>
+          <t>0.75%</t>
         </is>
       </c>
       <c r="C86" s="24" t="inlineStr">
@@ -30066,7 +30066,7 @@
       </c>
       <c r="B87" s="28" t="inlineStr">
         <is>
-          <t>0.30%</t>
+          <t>0.75%</t>
         </is>
       </c>
       <c r="C87" s="28" t="inlineStr">
@@ -30139,7 +30139,7 @@
       </c>
       <c r="B88" s="24" t="inlineStr">
         <is>
-          <t>0.30%</t>
+          <t>0.75%</t>
         </is>
       </c>
       <c r="C88" s="24" t="inlineStr">
@@ -30212,7 +30212,7 @@
       </c>
       <c r="B89" s="28" t="inlineStr">
         <is>
-          <t>0.30%</t>
+          <t>0.75%</t>
         </is>
       </c>
       <c r="C89" s="28" t="inlineStr">
@@ -30285,7 +30285,7 @@
       </c>
       <c r="B90" s="24" t="inlineStr">
         <is>
-          <t>0.30%</t>
+          <t>0.75%</t>
         </is>
       </c>
       <c r="C90" s="24" t="inlineStr">
@@ -30358,7 +30358,7 @@
       </c>
       <c r="B91" s="28" t="inlineStr">
         <is>
-          <t>0.30%</t>
+          <t>0.75%</t>
         </is>
       </c>
       <c r="C91" s="28" t="inlineStr">
@@ -30431,7 +30431,7 @@
       </c>
       <c r="B92" s="24" t="inlineStr">
         <is>
-          <t>0.30%</t>
+          <t>0.75%</t>
         </is>
       </c>
       <c r="C92" s="24" t="inlineStr">
@@ -30504,7 +30504,7 @@
       </c>
       <c r="B93" s="28" t="inlineStr">
         <is>
-          <t>0.30%</t>
+          <t>0.75%</t>
         </is>
       </c>
       <c r="C93" s="28" t="inlineStr">
@@ -30577,7 +30577,7 @@
       </c>
       <c r="B94" s="24" t="inlineStr">
         <is>
-          <t>0.30%</t>
+          <t>0.75%</t>
         </is>
       </c>
       <c r="C94" s="24" t="inlineStr">
@@ -30650,7 +30650,7 @@
       </c>
       <c r="B95" s="28" t="inlineStr">
         <is>
-          <t>0.30%</t>
+          <t>0.75%</t>
         </is>
       </c>
       <c r="C95" s="28" t="inlineStr">
@@ -30723,7 +30723,7 @@
       </c>
       <c r="B96" s="24" t="inlineStr">
         <is>
-          <t>0.30%</t>
+          <t>0.75%</t>
         </is>
       </c>
       <c r="C96" s="24" t="inlineStr">
@@ -30796,7 +30796,7 @@
       </c>
       <c r="B97" s="28" t="inlineStr">
         <is>
-          <t>0.30%</t>
+          <t>0.75%</t>
         </is>
       </c>
       <c r="C97" s="28" t="inlineStr">
@@ -30869,7 +30869,7 @@
       </c>
       <c r="B98" s="24" t="inlineStr">
         <is>
-          <t>0.30%</t>
+          <t>0.75%</t>
         </is>
       </c>
       <c r="C98" s="24" t="inlineStr">
@@ -30942,7 +30942,7 @@
       </c>
       <c r="B99" s="28" t="inlineStr">
         <is>
-          <t>0.30%</t>
+          <t>0.75%</t>
         </is>
       </c>
       <c r="C99" s="28" t="inlineStr">
@@ -31017,7 +31017,7 @@
       </c>
       <c r="B100" s="24" t="inlineStr">
         <is>
-          <t>0.30%</t>
+          <t>0.75%</t>
         </is>
       </c>
       <c r="C100" s="24" t="inlineStr">
@@ -31092,7 +31092,7 @@
       </c>
       <c r="B101" s="28" t="inlineStr">
         <is>
-          <t>0.30%</t>
+          <t>0.75%</t>
         </is>
       </c>
       <c r="C101" s="28" t="inlineStr">
@@ -31165,7 +31165,7 @@
       </c>
       <c r="B102" s="24" t="inlineStr">
         <is>
-          <t>0.30%</t>
+          <t>0.75%</t>
         </is>
       </c>
       <c r="C102" s="24" t="inlineStr">
@@ -31238,7 +31238,7 @@
       </c>
       <c r="B103" s="28" t="inlineStr">
         <is>
-          <t>0.30%</t>
+          <t>0.75%</t>
         </is>
       </c>
       <c r="C103" s="28" t="inlineStr">
@@ -31311,7 +31311,7 @@
       </c>
       <c r="B104" s="24" t="inlineStr">
         <is>
-          <t>0.30%</t>
+          <t>0.75%</t>
         </is>
       </c>
       <c r="C104" s="24" t="inlineStr">
@@ -31384,7 +31384,7 @@
       </c>
       <c r="B105" s="32" t="inlineStr">
         <is>
-          <t>0.30%</t>
+          <t>0.75%</t>
         </is>
       </c>
       <c r="C105" s="32" t="inlineStr">
